--- a/docs/hebrew-review.xlsx
+++ b/docs/hebrew-review.xlsx
@@ -7889,16 +7889,26 @@
     <t>email.verifyEmail.text</t>
   </si>
   <si>
-    <t>Hello Dana,
+    <t>Verify your email
+Hi Dana,
 To finish signing up, please verify your email address.
-Verify email: https://events.example.com/…
-This link works for 24 hours. If you didn't sign up for Event Planner, you can ignore this email.</t>
-  </si>
-  <si>
-    <t>שלום Dana,
+Verify Email: https://events.example.com/…
+This link works for 24 hours.
+Thanks,
+Event Planner
+This email was sent securely by Event Planner.
+If you didn't sign up for Event Planner, you can safely ignore this email.</t>
+  </si>
+  <si>
+    <t>אימות כתובת האימייל
+שלום ⁨Dana⁩,
 כדי להשלים את ההרשמה, יש לאמת את כתובת האימייל שלך.
 אימות האימייל: https://events.example.com/…
-הקישור תקף ל-24 שעות. אם לא נרשמת ל-Event Planner, אפשר להתעלם מהודעה זו.</t>
+הקישור תקף ל-24 שעות.
+תודה,
+Event Planner
+ההודעה נשלחה באופן מאובטח על ידי Event Planner.
+אם לא נרשמת ל-Event Planner, אפשר להתעלם מהודעה זו בבטחה.</t>
   </si>
   <si>
     <t>email.resetPassword.subject</t>
@@ -7913,16 +7923,26 @@
     <t>email.resetPassword.text</t>
   </si>
   <si>
-    <t>Hello Dana,
+    <t>Reset your password
+Hi Dana,
 We received a request to reset the password of your account.
-Choose a new password: https://events.example.com/…
-This link works for 60 minutes, once. If you didn't ask to reset your password, you can ignore this email; your password stays the same.</t>
-  </si>
-  <si>
-    <t>שלום Dana,
+Choose a New Password: https://events.example.com/…
+This link works for 60 minutes, once.
+Thanks,
+Event Planner
+This email was sent securely by Event Planner.
+If you didn't ask to reset your password, you can safely ignore this email; your password stays the same.</t>
+  </si>
+  <si>
+    <t>איפוס הסיסמה
+שלום ⁨Dana⁩,
 התקבלה בקשה לאפס את הסיסמה של החשבון שלך.
 בחירת סיסמה חדשה: https://events.example.com/…
-הקישור תקף ל-60 דקות ולשימוש אחד. אם לא ביקשת לאפס את הסיסמה, אפשר להתעלם מהודעה זו; הסיסמה לא תשתנה.</t>
+הקישור תקף ל-60 דקות ולשימוש אחד.
+תודה,
+Event Planner
+ההודעה נשלחה באופן מאובטח על ידי Event Planner.
+אם לא ביקשת לאפס את הסיסמה, אפשר להתעלם מהודעה זו בבטחה; הסיסמה לא תשתנה.</t>
   </si>
   <si>
     <t>email.invitation.subject</t>
@@ -7931,22 +7951,38 @@
     <t>You're invited to "Garden Party" on Event Planner</t>
   </si>
   <si>
-    <t>הוזמנת לאירוע "Garden Party" ב-Event Planner</t>
+    <t>הוזמנת לאירוע "⁨Garden Party⁩" ב-Event Planner</t>
   </si>
   <si>
     <t>email.invitation.text</t>
   </si>
   <si>
-    <t>Riley invited you to the event "Garden Party" as Admin.
-To get access, sign up to Event Planner with this email address.
-Sign up: https://events.example.com/…
-If you weren't expecting this invitation, you can ignore this email.</t>
-  </si>
-  <si>
-    <t>Riley הזמין/ה אותך לאירוע "Garden Party" בהרשאת מנהל.
-כדי לקבל גישה, יש להירשם ל-Event Planner עם כתובת האימייל הזו.
-הרשמה: https://events.example.com/…
-אם לא ציפית להזמנה הזו, אפשר להתעלם מהודעה זו.</t>
+    <t>You're invited to Garden Party
+Hi,
+Riley invited you to collaborate on Garden Party.
+Role: Admin
+Date: October 24, 2026
+Accept Invitation: https://events.example.com/…
+Once accepted, the event will appear in your My Events page.
+If you don't have an account yet, you can create one using this email address.
+Thanks,
+Event Planner
+This invitation was sent securely by Event Planner.
+If you weren't expecting this, you can safely ignore this email.</t>
+  </si>
+  <si>
+    <t>הוזמנת לאירוע ⁨Garden Party⁩
+שלום,
+⁨Riley⁩ הזמין/ה אותך להצטרף לניהול האירוע ⁨Garden Party⁩.
+הרשאה: מנהל
+תאריך: 24 באוקטובר 2026
+קבלת ההזמנה: https://events.example.com/…
+לאחר קבלת ההזמנה, האירוע יופיע בדף "האירועים שלי".
+אם עדיין אין לך חשבון, אפשר ליצור אותו עם כתובת האימייל הזו.
+תודה,
+Event Planner
+ההזמנה נשלחה באופן מאובטח על ידי Event Planner.
+אם לא ציפית להודעה הזו, אפשר להתעלם ממנה בבטחה.</t>
   </si>
   <si>
     <t>email.accessGranted.subject</t>
@@ -7955,20 +7991,36 @@
     <t>You now have access to "Garden Party"</t>
   </si>
   <si>
-    <t>קיבלת גישה לאירוע "Garden Party"</t>
+    <t>קיבלת גישה לאירוע "⁨Garden Party⁩"</t>
   </si>
   <si>
     <t>email.accessGranted.text</t>
   </si>
   <si>
-    <t>Riley gave you access to the event "Garden Party" as Admin.
-Open the event: https://events.example.com/…
-The event now appears in your list of events.</t>
-  </si>
-  <si>
-    <t>Riley נתן/ה לך גישה לאירוע "Garden Party" בהרשאת מנהל.
+    <t>You now have access to Garden Party
+Hi Dana,
+Riley gave you access to Garden Party.
+Role: Admin
+Date: October 24, 2026
+Open Event: https://events.example.com/…
+The event now appears in your My Events page.
+Thanks,
+Event Planner
+This email was sent securely by Event Planner.
+If you weren't expecting this, you can safely ignore this email.</t>
+  </si>
+  <si>
+    <t>קיבלת גישה לאירוע ⁨Garden Party⁩
+שלום ⁨Dana⁩,
+⁨Riley⁩ נתן/ה לך גישה לאירוע ⁨Garden Party⁩.
+הרשאה: מנהל
+תאריך: 24 באוקטובר 2026
 פתיחת האירוע: https://events.example.com/…
-האירוע מופיע עכשיו ברשימת האירועים שלך.</t>
+האירוע מופיע עכשיו בדף "האירועים שלי".
+תודה,
+Event Planner
+ההודעה נשלחה באופן מאובטח על ידי Event Planner.
+אם לא ציפית להודעה הזו, אפשר להתעלם ממנה בבטחה.</t>
   </si>
   <si>
     <t>email.testEmail.subject</t>
@@ -7983,13 +8035,21 @@
     <t>email.testEmail.text</t>
   </si>
   <si>
-    <t>This is a test email. If it arrived, sending email works.
+    <t>Sending email works
+This is a test email. If it arrived, sending email works.
 Open Event Planner: https://events.example.com/…
+Thanks,
+Event Planner
+This email was sent securely by Event Planner.
 Sent from the System page by a Super User.</t>
   </si>
   <si>
-    <t>זהו אימייל בדיקה. אם הוא הגיע, שליחת האימיילים עובדת.
+    <t>שליחת אימיילים עובדת
+זהו אימייל בדיקה. אם הוא הגיע, שליחת האימיילים עובדת.
 פתיחת Event Planner: https://events.example.com/…
+תודה,
+Event Planner
+ההודעה נשלחה באופן מאובטח על ידי Event Planner.
 נשלח מדף המערכת על ידי משתמש-על.</t>
   </si>
   <si>

--- a/docs/hebrew-review.xlsx
+++ b/docs/hebrew-review.xlsx
@@ -1679,6 +1679,42 @@
     <t>ההדגמה עודכנה, ולכן נתוני הדוגמה רועננו.</t>
   </si>
   <si>
+    <t>demo.ended.title</t>
+  </si>
+  <si>
+    <t>Your demo has ended</t>
+  </si>
+  <si>
+    <t>ההדגמה הסתיימה</t>
+  </si>
+  <si>
+    <t>demo.ended.lifetime</t>
+  </si>
+  <si>
+    <t>A demo lasts 3 days, so its sample data was cleared. Try Demo starts a fresh one.</t>
+  </si>
+  <si>
+    <t>הדגמה נמשכת 3 ימים, ולכן נתוני הדוגמה נמחקו. נסו את הדמו כדי להתחיל הדגמה חדשה.</t>
+  </si>
+  <si>
+    <t>demo.ended.idle</t>
+  </si>
+  <si>
+    <t>The demo was not used for 12 hours, so its sample data was cleared. Try Demo starts a fresh one.</t>
+  </si>
+  <si>
+    <t>לא היה שימוש בהדגמה במשך 12 שעות, ולכן נתוני הדוגמה נמחקו. נסו את הדמו כדי להתחיל הדגמה חדשה.</t>
+  </si>
+  <si>
+    <t>demo.endsAt</t>
+  </si>
+  <si>
+    <t>The demo ends on {{date}} at {{time}}, or after 12 hours without activity.</t>
+  </si>
+  <si>
+    <t>ההדגמה תסתיים ב־{{date}} בשעה {{time}}, או אחרי 12 שעות ללא פעילות.</t>
+  </si>
+  <si>
     <t>events.subtitle</t>
   </si>
   <si>
@@ -8260,7 +8296,7 @@
     <t>{{name}}, {{count}} and similar marks are filled in by the application; keep them in the correction.</t>
   </si>
   <si>
-    <t>998 texts in all.</t>
+    <t>1002 texts in all.</t>
   </si>
 </sst>
 </file>
@@ -10972,7 +11008,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="B190" t="s">
         <v>554</v>
@@ -10986,7 +11022,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="B191" t="s">
         <v>557</v>
@@ -11000,7 +11036,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="B192" t="s">
         <v>560</v>
@@ -11014,7 +11050,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="B193" t="s">
         <v>563</v>
@@ -11090,10 +11126,10 @@
         <v>578</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199">
@@ -11101,13 +11137,13 @@
         <v>20</v>
       </c>
       <c r="B199" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="200">
@@ -11115,13 +11151,13 @@
         <v>20</v>
       </c>
       <c r="B200" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="201">
@@ -11129,13 +11165,13 @@
         <v>20</v>
       </c>
       <c r="B201" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="202">
@@ -11143,13 +11179,13 @@
         <v>20</v>
       </c>
       <c r="B202" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="203">
@@ -11157,13 +11193,13 @@
         <v>20</v>
       </c>
       <c r="B203" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="204">
@@ -11171,13 +11207,13 @@
         <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="205">
@@ -11185,13 +11221,13 @@
         <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206">
@@ -11199,13 +11235,13 @@
         <v>20</v>
       </c>
       <c r="B206" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="207">
@@ -11213,13 +11249,13 @@
         <v>20</v>
       </c>
       <c r="B207" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="208">
@@ -11227,13 +11263,13 @@
         <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="209">
@@ -11241,13 +11277,13 @@
         <v>20</v>
       </c>
       <c r="B209" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210">
@@ -11255,10 +11291,10 @@
         <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>611</v>
@@ -11373,7 +11409,7 @@
         <v>634</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="219">
@@ -11381,13 +11417,13 @@
         <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="220">
@@ -11395,13 +11431,13 @@
         <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="221">
@@ -11409,13 +11445,13 @@
         <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="222">
@@ -11423,10 +11459,10 @@
         <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>644</v>
@@ -11437,13 +11473,13 @@
         <v>20</v>
       </c>
       <c r="B223" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="224">
@@ -11608,10 +11644,10 @@
         <v>681</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="236">
@@ -11619,13 +11655,13 @@
         <v>20</v>
       </c>
       <c r="B236" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="237">
@@ -11633,13 +11669,13 @@
         <v>20</v>
       </c>
       <c r="B237" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="238">
@@ -11647,13 +11683,13 @@
         <v>20</v>
       </c>
       <c r="B238" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="239">
@@ -11661,13 +11697,13 @@
         <v>20</v>
       </c>
       <c r="B239" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="240">
@@ -11846,10 +11882,10 @@
         <v>730</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="253">
@@ -11857,13 +11893,13 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="254">
@@ -11871,13 +11907,13 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="255">
@@ -11885,13 +11921,13 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="256">
@@ -11899,13 +11935,13 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
+        <v>742</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="C256" s="2" t="s">
+      <c r="D256" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="257">
@@ -12022,7 +12058,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B265" t="s">
         <v>767</v>
@@ -12036,7 +12072,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B266" t="s">
         <v>770</v>
@@ -12050,7 +12086,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B267" t="s">
         <v>773</v>
@@ -12064,7 +12100,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B268" t="s">
         <v>776</v>
@@ -12101,7 +12137,7 @@
         <v>783</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>360</v>
+        <v>784</v>
       </c>
     </row>
     <row r="271">
@@ -12109,13 +12145,13 @@
         <v>23</v>
       </c>
       <c r="B271" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="272">
@@ -12123,13 +12159,13 @@
         <v>23</v>
       </c>
       <c r="B272" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="273">
@@ -12137,13 +12173,13 @@
         <v>23</v>
       </c>
       <c r="B273" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="274">
@@ -12151,13 +12187,13 @@
         <v>23</v>
       </c>
       <c r="B274" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>795</v>
+        <v>360</v>
       </c>
     </row>
     <row r="275">
@@ -12185,7 +12221,7 @@
         <v>800</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>369</v>
+        <v>801</v>
       </c>
     </row>
     <row r="277">
@@ -12193,13 +12229,13 @@
         <v>23</v>
       </c>
       <c r="B277" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="278">
@@ -12207,13 +12243,13 @@
         <v>23</v>
       </c>
       <c r="B278" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="279">
@@ -12221,13 +12257,13 @@
         <v>23</v>
       </c>
       <c r="B279" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="280">
@@ -12235,13 +12271,13 @@
         <v>23</v>
       </c>
       <c r="B280" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>812</v>
+        <v>369</v>
       </c>
     </row>
     <row r="281">
@@ -12409,7 +12445,7 @@
         <v>847</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>809</v>
+        <v>848</v>
       </c>
     </row>
     <row r="293">
@@ -12417,13 +12453,13 @@
         <v>23</v>
       </c>
       <c r="B293" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="294">
@@ -12431,13 +12467,13 @@
         <v>23</v>
       </c>
       <c r="B294" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="295">
@@ -12445,13 +12481,13 @@
         <v>23</v>
       </c>
       <c r="B295" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="296">
@@ -12459,13 +12495,13 @@
         <v>23</v>
       </c>
       <c r="B296" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>26</v>
+        <v>859</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>27</v>
+        <v>821</v>
       </c>
     </row>
     <row r="297">
@@ -12473,13 +12509,13 @@
         <v>23</v>
       </c>
       <c r="B297" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="298">
@@ -12487,13 +12523,13 @@
         <v>23</v>
       </c>
       <c r="B298" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>357</v>
+        <v>864</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>357</v>
+        <v>865</v>
       </c>
     </row>
     <row r="299">
@@ -12501,13 +12537,13 @@
         <v>23</v>
       </c>
       <c r="B299" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="300">
@@ -12515,7 +12551,7 @@
         <v>23</v>
       </c>
       <c r="B300" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>26</v>
@@ -12529,13 +12565,13 @@
         <v>23</v>
       </c>
       <c r="B301" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="302">
@@ -12543,13 +12579,13 @@
         <v>23</v>
       </c>
       <c r="B302" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="303">
@@ -12557,13 +12593,13 @@
         <v>23</v>
       </c>
       <c r="B303" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>368</v>
+        <v>875</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>369</v>
+        <v>876</v>
       </c>
     </row>
     <row r="304">
@@ -12571,13 +12607,13 @@
         <v>23</v>
       </c>
       <c r="B304" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>872</v>
+        <v>26</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>798</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305">
@@ -12585,13 +12621,13 @@
         <v>23</v>
       </c>
       <c r="B305" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>791</v>
+        <v>879</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>792</v>
+        <v>880</v>
       </c>
     </row>
     <row r="306">
@@ -12599,13 +12635,13 @@
         <v>23</v>
       </c>
       <c r="B306" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>875</v>
+        <v>362</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>876</v>
+        <v>363</v>
       </c>
     </row>
     <row r="307">
@@ -12613,13 +12649,13 @@
         <v>23</v>
       </c>
       <c r="B307" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>878</v>
+        <v>368</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>879</v>
+        <v>369</v>
       </c>
     </row>
     <row r="308">
@@ -12627,13 +12663,13 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>882</v>
+        <v>810</v>
       </c>
     </row>
     <row r="309">
@@ -12641,13 +12677,13 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>884</v>
+        <v>803</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>885</v>
+        <v>804</v>
       </c>
     </row>
     <row r="310">
@@ -12672,10 +12708,10 @@
         <v>889</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>802</v>
+        <v>890</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>803</v>
+        <v>891</v>
       </c>
     </row>
     <row r="312">
@@ -12683,13 +12719,13 @@
         <v>23</v>
       </c>
       <c r="B312" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="313">
@@ -12697,13 +12733,13 @@
         <v>23</v>
       </c>
       <c r="B313" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="314">
@@ -12711,13 +12747,13 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="315">
@@ -12725,13 +12761,13 @@
         <v>23</v>
       </c>
       <c r="B315" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>899</v>
+        <v>814</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>900</v>
+        <v>815</v>
       </c>
     </row>
     <row r="316">
@@ -12739,13 +12775,13 @@
         <v>23</v>
       </c>
       <c r="B316" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="317">
@@ -12753,10 +12789,10 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>906</v>
@@ -12857,7 +12893,7 @@
         <v>926</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="325">
@@ -12865,13 +12901,13 @@
         <v>23</v>
       </c>
       <c r="B325" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="326">
@@ -12879,13 +12915,13 @@
         <v>23</v>
       </c>
       <c r="B326" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="327">
@@ -12893,13 +12929,13 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="328">
@@ -12907,10 +12943,10 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>938</v>
@@ -12927,7 +12963,7 @@
         <v>940</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>322</v>
+        <v>941</v>
       </c>
     </row>
     <row r="330">
@@ -12935,13 +12971,13 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="331">
@@ -12949,13 +12985,13 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="332">
@@ -12963,13 +12999,13 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="333">
@@ -12977,13 +13013,13 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>139</v>
+        <v>952</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>951</v>
+        <v>322</v>
       </c>
     </row>
     <row r="334">
@@ -12991,13 +13027,13 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="335">
@@ -13005,13 +13041,13 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="336">
@@ -13019,24 +13055,24 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>962</v>
+        <v>139</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>963</v>
@@ -13044,7 +13080,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B338" t="s">
         <v>964</v>
@@ -13058,7 +13094,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B339" t="s">
         <v>967</v>
@@ -13072,7 +13108,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B340" t="s">
         <v>970</v>
@@ -13134,10 +13170,10 @@
         <v>982</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>783</v>
+        <v>983</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>360</v>
+        <v>984</v>
       </c>
     </row>
     <row r="345">
@@ -13145,13 +13181,13 @@
         <v>26</v>
       </c>
       <c r="B345" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>785</v>
+        <v>986</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>786</v>
+        <v>987</v>
       </c>
     </row>
     <row r="346">
@@ -13159,13 +13195,13 @@
         <v>26</v>
       </c>
       <c r="B346" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>875</v>
+        <v>989</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="347">
@@ -13173,13 +13209,13 @@
         <v>26</v>
       </c>
       <c r="B347" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>362</v>
+        <v>992</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>363</v>
+        <v>993</v>
       </c>
     </row>
     <row r="348">
@@ -13187,13 +13223,13 @@
         <v>26</v>
       </c>
       <c r="B348" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>872</v>
+        <v>795</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>798</v>
+        <v>360</v>
       </c>
     </row>
     <row r="349">
@@ -13201,13 +13237,13 @@
         <v>26</v>
       </c>
       <c r="B349" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>368</v>
+        <v>797</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>369</v>
+        <v>798</v>
       </c>
     </row>
     <row r="350">
@@ -13215,13 +13251,13 @@
         <v>26</v>
       </c>
       <c r="B350" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>990</v>
+        <v>887</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="351">
@@ -13229,13 +13265,13 @@
         <v>26</v>
       </c>
       <c r="B351" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>993</v>
+        <v>362</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>994</v>
+        <v>363</v>
       </c>
     </row>
     <row r="352">
@@ -13243,13 +13279,13 @@
         <v>26</v>
       </c>
       <c r="B352" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>26</v>
+        <v>884</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>27</v>
+        <v>810</v>
       </c>
     </row>
     <row r="353">
@@ -13257,13 +13293,13 @@
         <v>26</v>
       </c>
       <c r="B353" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>997</v>
+        <v>368</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>998</v>
+        <v>369</v>
       </c>
     </row>
     <row r="354">
@@ -13271,13 +13307,13 @@
         <v>26</v>
       </c>
       <c r="B354" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>875</v>
+        <v>1002</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>876</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="355">
@@ -13285,13 +13321,13 @@
         <v>26</v>
       </c>
       <c r="B355" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>791</v>
+        <v>1005</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="356">
@@ -13299,13 +13335,13 @@
         <v>26</v>
       </c>
       <c r="B356" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>1003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="357">
@@ -13313,13 +13349,13 @@
         <v>26</v>
       </c>
       <c r="B357" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>872</v>
+        <v>1009</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="358">
@@ -13327,13 +13363,13 @@
         <v>26</v>
       </c>
       <c r="B358" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>368</v>
+        <v>887</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>1007</v>
+        <v>888</v>
       </c>
     </row>
     <row r="359">
@@ -13341,13 +13377,13 @@
         <v>26</v>
       </c>
       <c r="B359" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1009</v>
+        <v>803</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="360">
@@ -13355,13 +13391,13 @@
         <v>26</v>
       </c>
       <c r="B360" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>362</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="361">
@@ -13369,13 +13405,13 @@
         <v>26</v>
       </c>
       <c r="B361" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="362">
@@ -13383,13 +13419,13 @@
         <v>26</v>
       </c>
       <c r="B362" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>368</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="363">
@@ -13397,13 +13433,13 @@
         <v>26</v>
       </c>
       <c r="B363" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="364">
@@ -13411,13 +13447,13 @@
         <v>26</v>
       </c>
       <c r="B364" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1018</v>
+        <v>362</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="365">
@@ -13425,13 +13461,13 @@
         <v>26</v>
       </c>
       <c r="B365" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="366">
@@ -13439,13 +13475,13 @@
         <v>26</v>
       </c>
       <c r="B366" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1023</v>
+        <v>368</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="367">
@@ -13453,13 +13489,13 @@
         <v>26</v>
       </c>
       <c r="B367" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="368">
@@ -13467,13 +13503,13 @@
         <v>26</v>
       </c>
       <c r="B368" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="369">
@@ -13481,10 +13517,10 @@
         <v>26</v>
       </c>
       <c r="B369" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1032</v>
+        <v>864</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>1033</v>
@@ -13736,10 +13772,10 @@
         <v>1085</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>852</v>
+        <v>1086</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="388">
@@ -13747,13 +13783,13 @@
         <v>26</v>
       </c>
       <c r="B388" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>785</v>
+        <v>1089</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>786</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="389">
@@ -13761,13 +13797,13 @@
         <v>26</v>
       </c>
       <c r="B389" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1038</v>
+        <v>1092</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1039</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="390">
@@ -13775,13 +13811,13 @@
         <v>26</v>
       </c>
       <c r="B390" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="391">
@@ -13789,13 +13825,13 @@
         <v>26</v>
       </c>
       <c r="B391" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1050</v>
+        <v>864</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1051</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="392">
@@ -13803,13 +13839,13 @@
         <v>26</v>
       </c>
       <c r="B392" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>26</v>
+        <v>797</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>27</v>
+        <v>798</v>
       </c>
     </row>
     <row r="393">
@@ -13817,13 +13853,13 @@
         <v>26</v>
       </c>
       <c r="B393" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1095</v>
+        <v>1050</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1096</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="394">
@@ -13831,13 +13867,13 @@
         <v>26</v>
       </c>
       <c r="B394" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="395">
@@ -13845,13 +13881,13 @@
         <v>26</v>
       </c>
       <c r="B395" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>1102</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="396">
@@ -13859,13 +13895,13 @@
         <v>26</v>
       </c>
       <c r="B396" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1104</v>
+        <v>26</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1105</v>
+        <v>27</v>
       </c>
     </row>
     <row r="397">
@@ -13893,7 +13929,7 @@
         <v>1110</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="399">
@@ -13901,13 +13937,13 @@
         <v>26</v>
       </c>
       <c r="B399" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="400">
@@ -13915,13 +13951,13 @@
         <v>26</v>
       </c>
       <c r="B400" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="401">
@@ -13929,13 +13965,13 @@
         <v>26</v>
       </c>
       <c r="B401" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="402">
@@ -13943,10 +13979,10 @@
         <v>26</v>
       </c>
       <c r="B402" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>1122</v>
@@ -13988,10 +14024,10 @@
         <v>1129</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>607</v>
+        <v>1130</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>608</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="406">
@@ -13999,13 +14035,13 @@
         <v>26</v>
       </c>
       <c r="B406" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="407">
@@ -14013,13 +14049,13 @@
         <v>26</v>
       </c>
       <c r="B407" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="408">
@@ -14027,13 +14063,13 @@
         <v>26</v>
       </c>
       <c r="B408" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="409">
@@ -14041,13 +14077,13 @@
         <v>26</v>
       </c>
       <c r="B409" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1140</v>
+        <v>619</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>1141</v>
+        <v>620</v>
       </c>
     </row>
     <row r="410">
@@ -14212,10 +14248,10 @@
         <v>1175</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="422">
@@ -14223,13 +14259,13 @@
         <v>26</v>
       </c>
       <c r="B422" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="423">
@@ -14237,13 +14273,13 @@
         <v>26</v>
       </c>
       <c r="B423" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="424">
@@ -14251,13 +14287,13 @@
         <v>26</v>
       </c>
       <c r="B424" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="425">
@@ -14265,13 +14301,13 @@
         <v>26</v>
       </c>
       <c r="B425" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C425" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="C425" s="2" t="s">
-        <v>1173</v>
-      </c>
       <c r="D425" s="2" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="426">
@@ -14279,13 +14315,13 @@
         <v>26</v>
       </c>
       <c r="B426" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="427">
@@ -14293,13 +14329,13 @@
         <v>26</v>
       </c>
       <c r="B427" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="428">
@@ -14307,13 +14343,13 @@
         <v>26</v>
       </c>
       <c r="B428" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="429">
@@ -14321,13 +14357,13 @@
         <v>26</v>
       </c>
       <c r="B429" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1197</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="430">
@@ -14338,10 +14374,10 @@
         <v>1198</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>977</v>
+        <v>1199</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>978</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="431">
@@ -14349,13 +14385,13 @@
         <v>26</v>
       </c>
       <c r="B431" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1118</v>
+        <v>1202</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1119</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="432">
@@ -14363,13 +14399,13 @@
         <v>26</v>
       </c>
       <c r="B432" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="433">
@@ -14377,13 +14413,13 @@
         <v>26</v>
       </c>
       <c r="B433" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="434">
@@ -14391,13 +14427,13 @@
         <v>26</v>
       </c>
       <c r="B434" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1207</v>
+        <v>989</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1208</v>
+        <v>990</v>
       </c>
     </row>
     <row r="435">
@@ -14405,13 +14441,13 @@
         <v>26</v>
       </c>
       <c r="B435" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1210</v>
+        <v>1130</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1211</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="436">
@@ -14422,10 +14458,10 @@
         <v>1212</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1080</v>
+        <v>1213</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1081</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="437">
@@ -14433,13 +14469,13 @@
         <v>26</v>
       </c>
       <c r="B437" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>698</v>
+        <v>1216</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>699</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="438">
@@ -14447,13 +14483,13 @@
         <v>26</v>
       </c>
       <c r="B438" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>977</v>
+        <v>1219</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>978</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="439">
@@ -14461,13 +14497,13 @@
         <v>26</v>
       </c>
       <c r="B439" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="440">
@@ -14475,13 +14511,13 @@
         <v>26</v>
       </c>
       <c r="B440" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1219</v>
+        <v>1092</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1220</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="441">
@@ -14489,13 +14525,13 @@
         <v>26</v>
       </c>
       <c r="B441" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1222</v>
+        <v>710</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1223</v>
+        <v>711</v>
       </c>
     </row>
     <row r="442">
@@ -14503,13 +14539,13 @@
         <v>26</v>
       </c>
       <c r="B442" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1225</v>
+        <v>989</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1226</v>
+        <v>990</v>
       </c>
     </row>
     <row r="443">
@@ -14520,10 +14556,10 @@
         <v>1227</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>230</v>
+        <v>1228</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="444">
@@ -14531,13 +14567,13 @@
         <v>26</v>
       </c>
       <c r="B444" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>233</v>
+        <v>1231</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="445">
@@ -14545,13 +14581,13 @@
         <v>26</v>
       </c>
       <c r="B445" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>728</v>
+        <v>1234</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>729</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="446">
@@ -14559,13 +14595,13 @@
         <v>26</v>
       </c>
       <c r="B446" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="447">
@@ -14573,13 +14609,13 @@
         <v>26</v>
       </c>
       <c r="B447" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1050</v>
+        <v>230</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1051</v>
+        <v>231</v>
       </c>
     </row>
     <row r="448">
@@ -14587,13 +14623,13 @@
         <v>26</v>
       </c>
       <c r="B448" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1236</v>
+        <v>233</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="449">
@@ -14601,13 +14637,13 @@
         <v>26</v>
       </c>
       <c r="B449" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1038</v>
+        <v>740</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1039</v>
+        <v>741</v>
       </c>
     </row>
     <row r="450">
@@ -14615,13 +14651,13 @@
         <v>26</v>
       </c>
       <c r="B450" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="451">
@@ -14629,13 +14665,13 @@
         <v>26</v>
       </c>
       <c r="B451" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1243</v>
+        <v>1062</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1244</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="452">
@@ -14643,13 +14679,13 @@
         <v>26</v>
       </c>
       <c r="B452" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="453">
@@ -14657,13 +14693,13 @@
         <v>26</v>
       </c>
       <c r="B453" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1249</v>
+        <v>1050</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1250</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="454">
@@ -14702,10 +14738,10 @@
         <v>1257</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1127</v>
+        <v>1258</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1128</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="457">
@@ -14713,13 +14749,13 @@
         <v>26</v>
       </c>
       <c r="B457" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="458">
@@ -14727,13 +14763,13 @@
         <v>26</v>
       </c>
       <c r="B458" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>802</v>
+        <v>1264</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>803</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="459">
@@ -14741,13 +14777,13 @@
         <v>26</v>
       </c>
       <c r="B459" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="460">
@@ -14755,13 +14791,13 @@
         <v>26</v>
       </c>
       <c r="B460" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1266</v>
+        <v>1139</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1267</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="461">
@@ -14769,13 +14805,13 @@
         <v>26</v>
       </c>
       <c r="B461" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="462">
@@ -14783,13 +14819,13 @@
         <v>26</v>
       </c>
       <c r="B462" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1272</v>
+        <v>814</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1273</v>
+        <v>815</v>
       </c>
     </row>
     <row r="463">
@@ -14884,10 +14920,10 @@
         <v>1292</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>607</v>
+        <v>1293</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>608</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="470">
@@ -14895,13 +14931,13 @@
         <v>26</v>
       </c>
       <c r="B470" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="471">
@@ -14909,13 +14945,13 @@
         <v>26</v>
       </c>
       <c r="B471" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="472">
@@ -14923,13 +14959,13 @@
         <v>26</v>
       </c>
       <c r="B472" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="473">
@@ -14937,13 +14973,13 @@
         <v>26</v>
       </c>
       <c r="B473" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1303</v>
+        <v>619</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1304</v>
+        <v>620</v>
       </c>
     </row>
     <row r="474">
@@ -14996,10 +15032,10 @@
         <v>1314</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>878</v>
+        <v>1315</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>879</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="478">
@@ -15007,13 +15043,13 @@
         <v>26</v>
       </c>
       <c r="B478" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="479">
@@ -15021,13 +15057,13 @@
         <v>26</v>
       </c>
       <c r="B479" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="480">
@@ -15035,13 +15071,13 @@
         <v>26</v>
       </c>
       <c r="B480" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="481">
@@ -15049,13 +15085,13 @@
         <v>26</v>
       </c>
       <c r="B481" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>762</v>
+        <v>890</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>763</v>
+        <v>891</v>
       </c>
     </row>
     <row r="482">
@@ -15063,13 +15099,13 @@
         <v>26</v>
       </c>
       <c r="B482" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="483">
@@ -15077,13 +15113,13 @@
         <v>26</v>
       </c>
       <c r="B483" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>26</v>
+        <v>1331</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>27</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="484">
@@ -15091,13 +15127,13 @@
         <v>26</v>
       </c>
       <c r="B484" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="485">
@@ -15105,13 +15141,13 @@
         <v>26</v>
       </c>
       <c r="B485" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1201</v>
+        <v>774</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1202</v>
+        <v>775</v>
       </c>
     </row>
     <row r="486">
@@ -15119,13 +15155,13 @@
         <v>26</v>
       </c>
       <c r="B486" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1204</v>
+        <v>1338</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1205</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="487">
@@ -15133,13 +15169,13 @@
         <v>26</v>
       </c>
       <c r="B487" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1074</v>
+        <v>26</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1075</v>
+        <v>27</v>
       </c>
     </row>
     <row r="488">
@@ -15147,13 +15183,13 @@
         <v>26</v>
       </c>
       <c r="B488" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1077</v>
+        <v>1342</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1078</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="489">
@@ -15161,13 +15197,13 @@
         <v>26</v>
       </c>
       <c r="B489" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1080</v>
+        <v>1213</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1081</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="490">
@@ -15175,13 +15211,13 @@
         <v>26</v>
       </c>
       <c r="B490" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>802</v>
+        <v>1216</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>803</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="491">
@@ -15189,13 +15225,13 @@
         <v>26</v>
       </c>
       <c r="B491" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>852</v>
+        <v>1086</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="492">
@@ -15203,13 +15239,13 @@
         <v>26</v>
       </c>
       <c r="B492" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>785</v>
+        <v>1089</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>786</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="493">
@@ -15217,13 +15253,13 @@
         <v>26</v>
       </c>
       <c r="B493" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1038</v>
+        <v>1092</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1039</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="494">
@@ -15231,13 +15267,13 @@
         <v>26</v>
       </c>
       <c r="B494" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1050</v>
+        <v>814</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1051</v>
+        <v>815</v>
       </c>
     </row>
     <row r="495">
@@ -15245,13 +15281,13 @@
         <v>26</v>
       </c>
       <c r="B495" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1343</v>
+        <v>864</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>966</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="496">
@@ -15259,13 +15295,13 @@
         <v>26</v>
       </c>
       <c r="B496" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1345</v>
+        <v>797</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1346</v>
+        <v>798</v>
       </c>
     </row>
     <row r="497">
@@ -15273,13 +15309,13 @@
         <v>26</v>
       </c>
       <c r="B497" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1348</v>
+        <v>1050</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1349</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="498">
@@ -15287,13 +15323,13 @@
         <v>26</v>
       </c>
       <c r="B498" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1351</v>
+        <v>1062</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1352</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="499">
@@ -15301,13 +15337,13 @@
         <v>26</v>
       </c>
       <c r="B499" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1355</v>
+        <v>978</v>
       </c>
     </row>
     <row r="500">
@@ -15640,10 +15676,10 @@
         <v>1425</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1201</v>
+        <v>1426</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1202</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="524">
@@ -15651,13 +15687,13 @@
         <v>26</v>
       </c>
       <c r="B524" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1204</v>
+        <v>1429</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1205</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="525">
@@ -15665,13 +15701,13 @@
         <v>26</v>
       </c>
       <c r="B525" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1207</v>
+        <v>1432</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>1208</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="526">
@@ -15679,13 +15715,13 @@
         <v>26</v>
       </c>
       <c r="B526" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1080</v>
+        <v>1435</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>1081</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="527">
@@ -15693,13 +15729,13 @@
         <v>26</v>
       </c>
       <c r="B527" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1050</v>
+        <v>1213</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="528">
@@ -15707,13 +15743,13 @@
         <v>26</v>
       </c>
       <c r="B528" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1431</v>
+        <v>1216</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1432</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="529">
@@ -15721,13 +15757,13 @@
         <v>26</v>
       </c>
       <c r="B529" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1434</v>
+        <v>1219</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>1435</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="530">
@@ -15735,13 +15771,13 @@
         <v>26</v>
       </c>
       <c r="B530" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1437</v>
+        <v>1092</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>1438</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="531">
@@ -15749,13 +15785,13 @@
         <v>26</v>
       </c>
       <c r="B531" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1440</v>
+        <v>1062</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1441</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="532">
@@ -16144,10 +16180,10 @@
         <v>1523</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1500</v>
+        <v>1524</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1501</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="560">
@@ -16155,13 +16191,13 @@
         <v>26</v>
       </c>
       <c r="B560" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="561">
@@ -16169,13 +16205,13 @@
         <v>26</v>
       </c>
       <c r="B561" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="562">
@@ -16183,13 +16219,13 @@
         <v>26</v>
       </c>
       <c r="B562" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="563">
@@ -16197,13 +16233,13 @@
         <v>26</v>
       </c>
       <c r="B563" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1532</v>
+        <v>1512</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1533</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="564">
@@ -16211,13 +16247,13 @@
         <v>26</v>
       </c>
       <c r="B564" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="565">
@@ -16225,13 +16261,13 @@
         <v>26</v>
       </c>
       <c r="B565" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1538</v>
+        <v>1515</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1539</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="566">
@@ -16315,7 +16351,7 @@
         <v>1556</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>991</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="572">
@@ -16323,13 +16359,13 @@
         <v>26</v>
       </c>
       <c r="B572" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="573">
@@ -16337,46 +16373,46 @@
         <v>26</v>
       </c>
       <c r="B573" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1491</v>
+        <v>1562</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1562</v>
+        <v>26</v>
       </c>
       <c r="B574" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1562</v>
+        <v>26</v>
       </c>
       <c r="B575" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1568</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>1562</v>
+        <v>26</v>
       </c>
       <c r="B576" t="s">
         <v>1569</v>
@@ -16390,97 +16426,97 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>1562</v>
+        <v>26</v>
       </c>
       <c r="B577" t="s">
         <v>1572</v>
       </c>
       <c r="C577" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>1573</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B578" t="s">
         <v>1575</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1387</v>
+        <v>1576</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1388</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B579" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1216</v>
+        <v>1579</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B580" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B581" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B582" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1585</v>
+        <v>1399</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>1586</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B583" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1588</v>
+        <v>1228</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>1589</v>
@@ -16488,7 +16524,7 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B584" t="s">
         <v>1590</v>
@@ -16502,7 +16538,7 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B585" t="s">
         <v>1593</v>
@@ -16516,7 +16552,7 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B586" t="s">
         <v>1596</v>
@@ -16530,7 +16566,7 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B587" t="s">
         <v>1599</v>
@@ -16544,7 +16580,7 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B588" t="s">
         <v>1602</v>
@@ -16558,7 +16594,7 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B589" t="s">
         <v>1605</v>
@@ -16572,7 +16608,7 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B590" t="s">
         <v>1608</v>
@@ -16586,7 +16622,7 @@
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B591" t="s">
         <v>1611</v>
@@ -16600,7 +16636,7 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B592" t="s">
         <v>1614</v>
@@ -16614,7 +16650,7 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B593" t="s">
         <v>1617</v>
@@ -16628,7 +16664,7 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B594" t="s">
         <v>1620</v>
@@ -16642,7 +16678,7 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B595" t="s">
         <v>1623</v>
@@ -16656,7 +16692,7 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B596" t="s">
         <v>1626</v>
@@ -16670,7 +16706,7 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B597" t="s">
         <v>1629</v>
@@ -16684,7 +16720,7 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B598" t="s">
         <v>1632</v>
@@ -16698,7 +16734,7 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B599" t="s">
         <v>1635</v>
@@ -16712,7 +16748,7 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B600" t="s">
         <v>1638</v>
@@ -16726,7 +16762,7 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B601" t="s">
         <v>1641</v>
@@ -16740,7 +16776,7 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B602" t="s">
         <v>1644</v>
@@ -16754,7 +16790,7 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B603" t="s">
         <v>1647</v>
@@ -16768,7 +16804,7 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B604" t="s">
         <v>1650</v>
@@ -16782,7 +16818,7 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B605" t="s">
         <v>1653</v>
@@ -16791,124 +16827,124 @@
         <v>1654</v>
       </c>
       <c r="D605" s="2" t="s">
-        <v>677</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B606" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B607" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="D607" s="2" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B608" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B609" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D609" s="2" t="s">
-        <v>1388</v>
+        <v>689</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B610" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B611" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B612" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="D612" s="2" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B613" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="D613" s="2" t="s">
-        <v>1677</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B614" t="s">
         <v>1678</v>
@@ -16922,7 +16958,7 @@
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B615" t="s">
         <v>1681</v>
@@ -16936,7 +16972,7 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B616" t="s">
         <v>1684</v>
@@ -16950,7 +16986,7 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B617" t="s">
         <v>1687</v>
@@ -16964,7 +17000,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B618" t="s">
         <v>1690</v>
@@ -16978,7 +17014,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B619" t="s">
         <v>1693</v>
@@ -16992,7 +17028,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B620" t="s">
         <v>1696</v>
@@ -17006,7 +17042,7 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B621" t="s">
         <v>1699</v>
@@ -17020,7 +17056,7 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B622" t="s">
         <v>1702</v>
@@ -17034,7 +17070,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B623" t="s">
         <v>1705</v>
@@ -17048,7 +17084,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B624" t="s">
         <v>1708</v>
@@ -17062,119 +17098,119 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B625" t="s">
         <v>1711</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1077</v>
+        <v>1712</v>
       </c>
       <c r="D625" s="2" t="s">
-        <v>1078</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B626" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>863</v>
+        <v>1715</v>
       </c>
       <c r="D626" s="2" t="s">
-        <v>864</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B627" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1665</v>
+        <v>1718</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B628" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1090</v>
+        <v>1721</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>1091</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B629" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1717</v>
+        <v>1089</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>1718</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B630" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1720</v>
+        <v>875</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>1721</v>
+        <v>876</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B631" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1723</v>
+        <v>1677</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B632" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1726</v>
+        <v>1102</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1727</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B633" t="s">
         <v>1728</v>
@@ -17183,138 +17219,138 @@
         <v>1729</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>511</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B634" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B635" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B636" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B637" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>1741</v>
+        <v>511</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B638" t="s">
         <v>1742</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>926</v>
+        <v>1743</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>926</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B639" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B640" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B641" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B642" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1753</v>
+        <v>938</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>1754</v>
+        <v>938</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B643" t="s">
         <v>1755</v>
@@ -17328,7 +17364,7 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B644" t="s">
         <v>1758</v>
@@ -17342,7 +17378,7 @@
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B645" t="s">
         <v>1761</v>
@@ -17356,7 +17392,7 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B646" t="s">
         <v>1764</v>
@@ -17370,7 +17406,7 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1562</v>
+        <v>1574</v>
       </c>
       <c r="B647" t="s">
         <v>1767</v>
@@ -17379,63 +17415,63 @@
         <v>1768</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>1574</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>139</v>
+        <v>1574</v>
       </c>
       <c r="B648" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>139</v>
+        <v>1574</v>
       </c>
       <c r="B649" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1216</v>
+        <v>1774</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>1577</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>139</v>
+        <v>1574</v>
       </c>
       <c r="B650" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>139</v>
+        <v>1574</v>
       </c>
       <c r="B651" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>1778</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="652">
@@ -17443,13 +17479,13 @@
         <v>139</v>
       </c>
       <c r="B652" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="653">
@@ -17457,13 +17493,13 @@
         <v>139</v>
       </c>
       <c r="B653" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1783</v>
+        <v>1228</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>1784</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="654">
@@ -17502,10 +17538,10 @@
         <v>1791</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1387</v>
+        <v>1792</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>1388</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="657">
@@ -17513,13 +17549,13 @@
         <v>139</v>
       </c>
       <c r="B657" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="658">
@@ -17527,13 +17563,13 @@
         <v>139</v>
       </c>
       <c r="B658" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="659">
@@ -17541,13 +17577,13 @@
         <v>139</v>
       </c>
       <c r="B659" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>1794</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="660">
@@ -17555,13 +17591,13 @@
         <v>139</v>
       </c>
       <c r="B660" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1801</v>
+        <v>1399</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>1802</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="661">
@@ -17569,13 +17605,13 @@
         <v>139</v>
       </c>
       <c r="B661" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="662">
@@ -17583,13 +17619,13 @@
         <v>139</v>
       </c>
       <c r="B662" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="663">
@@ -17597,13 +17633,13 @@
         <v>139</v>
       </c>
       <c r="B663" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="664">
@@ -17855,7 +17891,7 @@
         <v>1864</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>736</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="682">
@@ -17863,13 +17899,13 @@
         <v>139</v>
       </c>
       <c r="B682" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>739</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="683">
@@ -17877,13 +17913,13 @@
         <v>139</v>
       </c>
       <c r="B683" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>742</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="684">
@@ -17891,13 +17927,13 @@
         <v>139</v>
       </c>
       <c r="B684" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="685">
@@ -17905,13 +17941,13 @@
         <v>139</v>
       </c>
       <c r="B685" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="D685" s="2" t="s">
-        <v>1874</v>
+        <v>748</v>
       </c>
     </row>
     <row r="686">
@@ -17919,13 +17955,13 @@
         <v>139</v>
       </c>
       <c r="B686" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>1877</v>
+        <v>751</v>
       </c>
     </row>
     <row r="687">
@@ -17933,13 +17969,13 @@
         <v>139</v>
       </c>
       <c r="B687" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>1880</v>
+        <v>754</v>
       </c>
     </row>
     <row r="688">
@@ -18174,10 +18210,10 @@
         <v>1929</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>683</v>
+        <v>1930</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>684</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="705">
@@ -18185,13 +18221,13 @@
         <v>139</v>
       </c>
       <c r="B705" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>686</v>
+        <v>1933</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>687</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="706">
@@ -18199,13 +18235,13 @@
         <v>139</v>
       </c>
       <c r="B706" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>713</v>
+        <v>1936</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>714</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="707">
@@ -18213,13 +18249,13 @@
         <v>139</v>
       </c>
       <c r="B707" t="s">
-        <v>1932</v>
+        <v>1938</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>1934</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="708">
@@ -18227,13 +18263,13 @@
         <v>139</v>
       </c>
       <c r="B708" t="s">
-        <v>1935</v>
+        <v>1941</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1936</v>
+        <v>695</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>1937</v>
+        <v>696</v>
       </c>
     </row>
     <row r="709">
@@ -18241,13 +18277,13 @@
         <v>139</v>
       </c>
       <c r="B709" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1939</v>
+        <v>698</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>1940</v>
+        <v>699</v>
       </c>
     </row>
     <row r="710">
@@ -18255,13 +18291,13 @@
         <v>139</v>
       </c>
       <c r="B710" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1942</v>
+        <v>725</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>1943</v>
+        <v>726</v>
       </c>
     </row>
     <row r="711">
@@ -18359,7 +18395,7 @@
         <v>1963</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>1388</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="718">
@@ -18367,13 +18403,13 @@
         <v>139</v>
       </c>
       <c r="B718" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="D718" s="2" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="719">
@@ -18381,13 +18417,13 @@
         <v>139</v>
       </c>
       <c r="B719" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D719" s="2" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="720">
@@ -18395,13 +18431,13 @@
         <v>139</v>
       </c>
       <c r="B720" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="D720" s="2" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="721">
@@ -18409,13 +18445,13 @@
         <v>139</v>
       </c>
       <c r="B721" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>362</v>
+        <v>1975</v>
       </c>
       <c r="D721" s="2" t="s">
-        <v>363</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="722">
@@ -18423,13 +18459,13 @@
         <v>139</v>
       </c>
       <c r="B722" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>368</v>
+        <v>1977</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="723">
@@ -18437,13 +18473,13 @@
         <v>139</v>
       </c>
       <c r="B723" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>872</v>
+        <v>1980</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="724">
@@ -18451,13 +18487,13 @@
         <v>139</v>
       </c>
       <c r="B724" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="725">
@@ -18465,13 +18501,13 @@
         <v>139</v>
       </c>
       <c r="B725" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1982</v>
+        <v>362</v>
       </c>
       <c r="D725" s="2" t="s">
-        <v>1983</v>
+        <v>363</v>
       </c>
     </row>
     <row r="726">
@@ -18479,13 +18515,13 @@
         <v>139</v>
       </c>
       <c r="B726" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1985</v>
+        <v>368</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="727">
@@ -18493,10 +18529,10 @@
         <v>139</v>
       </c>
       <c r="B727" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1988</v>
+        <v>884</v>
       </c>
       <c r="D727" s="2" t="s">
         <v>1989</v>
@@ -18532,91 +18568,91 @@
     </row>
     <row r="730">
       <c r="A730" t="s">
+        <v>139</v>
+      </c>
+      <c r="B730" t="s">
         <v>1996</v>
       </c>
-      <c r="B730" t="s">
+      <c r="C730" s="2" t="s">
         <v>1997</v>
       </c>
-      <c r="C730" s="2" t="s">
+      <c r="D730" s="2" t="s">
         <v>1998</v>
-      </c>
-      <c r="D730" s="2" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1996</v>
+        <v>139</v>
       </c>
       <c r="B731" t="s">
         <v>1999</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1207</v>
+        <v>2000</v>
       </c>
       <c r="D731" s="2" t="s">
-        <v>1208</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1996</v>
+        <v>139</v>
       </c>
       <c r="B732" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D732" s="2" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1996</v>
+        <v>139</v>
       </c>
       <c r="B733" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D733" s="2" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B734" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D734" s="2" t="s">
-        <v>2008</v>
+        <v>414</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B735" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>2010</v>
+        <v>1219</v>
       </c>
       <c r="D735" s="2" t="s">
-        <v>2011</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B736" t="s">
         <v>2012</v>
@@ -18630,7 +18666,7 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B737" t="s">
         <v>2015</v>
@@ -18644,7 +18680,7 @@
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B738" t="s">
         <v>2018</v>
@@ -18658,7 +18694,7 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B739" t="s">
         <v>2021</v>
@@ -18672,7 +18708,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B740" t="s">
         <v>2024</v>
@@ -18686,7 +18722,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B741" t="s">
         <v>2027</v>
@@ -18700,83 +18736,83 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B742" t="s">
         <v>2030</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>425</v>
+        <v>2031</v>
       </c>
       <c r="D742" s="2" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B743" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>230</v>
+        <v>2034</v>
       </c>
       <c r="D743" s="2" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B744" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="D744" s="2" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B745" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="D745" s="2" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B746" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2041</v>
+        <v>425</v>
       </c>
       <c r="D746" s="2" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B747" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>2044</v>
+        <v>230</v>
       </c>
       <c r="D747" s="2" t="s">
         <v>2045</v>
@@ -18784,7 +18820,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B748" t="s">
         <v>2046</v>
@@ -18798,7 +18834,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B749" t="s">
         <v>2049</v>
@@ -18812,7 +18848,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B750" t="s">
         <v>2052</v>
@@ -18826,7 +18862,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B751" t="s">
         <v>2055</v>
@@ -18840,7 +18876,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B752" t="s">
         <v>2058</v>
@@ -18854,7 +18890,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B753" t="s">
         <v>2061</v>
@@ -18868,7 +18904,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B754" t="s">
         <v>2064</v>
@@ -18882,7 +18918,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B755" t="s">
         <v>2067</v>
@@ -18896,7 +18932,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="B756" t="s">
         <v>2070</v>
@@ -18910,91 +18946,91 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B757" t="s">
         <v>2073</v>
       </c>
-      <c r="B757" t="s">
+      <c r="C757" s="2" t="s">
         <v>2074</v>
       </c>
-      <c r="C757" s="2" t="s">
+      <c r="D757" s="2" t="s">
         <v>2075</v>
-      </c>
-      <c r="D757" s="2" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>2073</v>
+        <v>2008</v>
       </c>
       <c r="B758" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C758" s="2" t="s">
         <v>2077</v>
       </c>
-      <c r="C758" s="2" t="s">
-        <v>1044</v>
-      </c>
       <c r="D758" s="2" t="s">
-        <v>1045</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>2073</v>
+        <v>2008</v>
       </c>
       <c r="B759" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="D759" s="2" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>2073</v>
+        <v>2008</v>
       </c>
       <c r="B760" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="D760" s="2" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B761" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D761" s="2" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B762" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>2088</v>
+        <v>1056</v>
       </c>
       <c r="D762" s="2" t="s">
-        <v>2089</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B763" t="s">
         <v>2090</v>
@@ -19008,7 +19044,7 @@
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B764" t="s">
         <v>2093</v>
@@ -19022,7 +19058,7 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B765" t="s">
         <v>2096</v>
@@ -19036,7 +19072,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B766" t="s">
         <v>2099</v>
@@ -19050,7 +19086,7 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B767" t="s">
         <v>2102</v>
@@ -19064,77 +19100,77 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B768" t="s">
         <v>2105</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>805</v>
+        <v>2106</v>
       </c>
       <c r="D768" s="2" t="s">
-        <v>806</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B769" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B770" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D770" s="2" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B771" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="D771" s="2" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B772" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>2116</v>
+        <v>817</v>
       </c>
       <c r="D772" s="2" t="s">
-        <v>2117</v>
+        <v>818</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B773" t="s">
         <v>2118</v>
@@ -19148,7 +19184,7 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B774" t="s">
         <v>2121</v>
@@ -19162,7 +19198,7 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B775" t="s">
         <v>2124</v>
@@ -19176,7 +19212,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B776" t="s">
         <v>2127</v>
@@ -19190,7 +19226,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B777" t="s">
         <v>2130</v>
@@ -19204,97 +19240,97 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B778" t="s">
         <v>2133</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2094</v>
+        <v>2134</v>
       </c>
       <c r="D778" s="2" t="s">
-        <v>2095</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B779" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>2094</v>
+        <v>2137</v>
       </c>
       <c r="D779" s="2" t="s">
-        <v>2095</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B780" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="D780" s="2" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B781" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
       <c r="D781" s="2" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B782" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>2141</v>
+        <v>2106</v>
       </c>
       <c r="D782" s="2" t="s">
-        <v>2142</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B783" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2144</v>
+        <v>2106</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>2145</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B784" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="D784" s="2" t="s">
         <v>2148</v>
@@ -19302,133 +19338,133 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B785" t="s">
         <v>2149</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>863</v>
+        <v>2150</v>
       </c>
       <c r="D785" s="2" t="s">
-        <v>864</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B786" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>1090</v>
+        <v>2153</v>
       </c>
       <c r="D786" s="2" t="s">
-        <v>1091</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B787" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
       <c r="D787" s="2" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B788" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="D788" s="2" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B789" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>2138</v>
+        <v>875</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>2139</v>
+        <v>876</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B790" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>2159</v>
+        <v>1102</v>
       </c>
       <c r="D790" s="2" t="s">
-        <v>2160</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B791" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B792" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="D792" s="2" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B793" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>2168</v>
+        <v>2150</v>
       </c>
       <c r="D793" s="2" t="s">
-        <v>2169</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B794" t="s">
         <v>2170</v>
@@ -19442,7 +19478,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B795" t="s">
         <v>2173</v>
@@ -19456,7 +19492,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B796" t="s">
         <v>2176</v>
@@ -19470,7 +19506,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B797" t="s">
         <v>2179</v>
@@ -19484,7 +19520,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B798" t="s">
         <v>2182</v>
@@ -19498,7 +19534,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B799" t="s">
         <v>2185</v>
@@ -19512,7 +19548,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B800" t="s">
         <v>2188</v>
@@ -19526,7 +19562,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B801" t="s">
         <v>2191</v>
@@ -19540,7 +19576,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B802" t="s">
         <v>2194</v>
@@ -19554,77 +19590,77 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B803" t="s">
         <v>2197</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>1121</v>
+        <v>2198</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>1122</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B804" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="D804" s="2" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B805" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B806" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="D806" s="2" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B807" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2208</v>
+        <v>1133</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>2209</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B808" t="s">
         <v>2210</v>
@@ -19638,7 +19674,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B809" t="s">
         <v>2213</v>
@@ -19652,7 +19688,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B810" t="s">
         <v>2216</v>
@@ -19666,7 +19702,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B811" t="s">
         <v>2219</v>
@@ -19680,7 +19716,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B812" t="s">
         <v>2222</v>
@@ -19694,7 +19730,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B813" t="s">
         <v>2225</v>
@@ -19708,7 +19744,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B814" t="s">
         <v>2228</v>
@@ -19722,7 +19758,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B815" t="s">
         <v>2231</v>
@@ -19736,245 +19772,245 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B816" t="s">
         <v>2234</v>
       </c>
       <c r="C816" s="2" t="s">
-        <v>940</v>
+        <v>2235</v>
       </c>
       <c r="D816" s="2" t="s">
-        <v>322</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B817" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="C817" s="2" t="s">
-        <v>2085</v>
+        <v>2238</v>
       </c>
       <c r="D817" s="2" t="s">
-        <v>2086</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B818" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="D818" s="2" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B819" t="s">
-        <v>2239</v>
+        <v>2243</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="D819" s="2" t="s">
-        <v>2241</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B820" t="s">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>2141</v>
+        <v>952</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>2142</v>
+        <v>322</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B821" t="s">
-        <v>2243</v>
+        <v>2247</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>2244</v>
+        <v>2097</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2245</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B822" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="C822" s="2" t="s">
-        <v>2138</v>
+        <v>2249</v>
       </c>
       <c r="D822" s="2" t="s">
-        <v>2139</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B823" t="s">
-        <v>2247</v>
+        <v>2251</v>
       </c>
       <c r="C823" s="2" t="s">
-        <v>2085</v>
+        <v>2252</v>
       </c>
       <c r="D823" s="2" t="s">
-        <v>2086</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B824" t="s">
-        <v>2248</v>
+        <v>2254</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>1216</v>
+        <v>2153</v>
       </c>
       <c r="D824" s="2" t="s">
-        <v>1577</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B825" t="s">
-        <v>2249</v>
+        <v>2255</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="D825" s="2" t="s">
-        <v>2251</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B826" t="s">
-        <v>2252</v>
+        <v>2258</v>
       </c>
       <c r="C826" s="2" t="s">
-        <v>2253</v>
+        <v>2150</v>
       </c>
       <c r="D826" s="2" t="s">
-        <v>2254</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B827" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="C827" s="2" t="s">
-        <v>2256</v>
+        <v>2097</v>
       </c>
       <c r="D827" s="2" t="s">
-        <v>2257</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B828" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C828" s="2" t="s">
-        <v>245</v>
+        <v>1228</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>246</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B829" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="C829" s="2" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="D829" s="2" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B830" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="C830" s="2" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B831" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="C831" s="2" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="D831" s="2" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B832" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="C832" s="2" t="s">
-        <v>2269</v>
+        <v>245</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>2270</v>
+        <v>246</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B833" t="s">
         <v>2271</v>
@@ -19988,7 +20024,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B834" t="s">
         <v>2274</v>
@@ -20002,77 +20038,77 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B835" t="s">
         <v>2277</v>
       </c>
       <c r="C835" s="2" t="s">
-        <v>2199</v>
+        <v>2278</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>2200</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B836" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="C836" s="2" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B837" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="C837" s="2" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B838" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="C838" s="2" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B839" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="C839" s="2" t="s">
-        <v>2288</v>
+        <v>2211</v>
       </c>
       <c r="D839" s="2" t="s">
-        <v>2289</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B840" t="s">
         <v>2290</v>
@@ -20086,7 +20122,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B841" t="s">
         <v>2293</v>
@@ -20100,7 +20136,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B842" t="s">
         <v>2296</v>
@@ -20114,7 +20150,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B843" t="s">
         <v>2299</v>
@@ -20128,7 +20164,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B844" t="s">
         <v>2302</v>
@@ -20142,7 +20178,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B845" t="s">
         <v>2305</v>
@@ -20156,7 +20192,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B846" t="s">
         <v>2308</v>
@@ -20170,7 +20206,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B847" t="s">
         <v>2311</v>
@@ -20184,77 +20220,77 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B848" t="s">
         <v>2314</v>
       </c>
       <c r="C848" s="2" t="s">
-        <v>1107</v>
+        <v>2315</v>
       </c>
       <c r="D848" s="2" t="s">
-        <v>1108</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B849" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="C849" s="2" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="D849" s="2" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B850" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="C850" s="2" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D850" s="2" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B851" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="D851" s="2" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B852" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="C852" s="2" t="s">
-        <v>2325</v>
+        <v>1119</v>
       </c>
       <c r="D852" s="2" t="s">
-        <v>2326</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B853" t="s">
         <v>2327</v>
@@ -20268,7 +20304,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B854" t="s">
         <v>2330</v>
@@ -20282,7 +20318,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B855" t="s">
         <v>2333</v>
@@ -20296,7 +20332,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B856" t="s">
         <v>2336</v>
@@ -20310,198 +20346,198 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B857" t="s">
         <v>2339</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>1476</v>
+        <v>2340</v>
       </c>
       <c r="D857" s="2" t="s">
-        <v>1477</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B858" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="C858" s="2" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D858" s="2" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B859" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="C859" s="2" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="D859" s="2" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B860" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>1330</v>
+        <v>2349</v>
       </c>
       <c r="D860" s="2" t="s">
-        <v>1331</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B861" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
       <c r="C861" s="2" t="s">
-        <v>1201</v>
+        <v>1488</v>
       </c>
       <c r="D861" s="2" t="s">
-        <v>1202</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B862" t="s">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>1204</v>
+        <v>2353</v>
       </c>
       <c r="D862" s="2" t="s">
-        <v>1205</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B863" t="s">
-        <v>2349</v>
+        <v>2355</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>1074</v>
+        <v>2356</v>
       </c>
       <c r="D863" s="2" t="s">
-        <v>1075</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B864" t="s">
-        <v>2350</v>
+        <v>2358</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>1077</v>
+        <v>1342</v>
       </c>
       <c r="D864" s="2" t="s">
-        <v>1078</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B865" t="s">
-        <v>2351</v>
+        <v>2359</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>2004</v>
+        <v>1213</v>
       </c>
       <c r="D865" s="2" t="s">
-        <v>2005</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>2073</v>
+        <v>2085</v>
       </c>
       <c r="B866" t="s">
-        <v>2352</v>
+        <v>2360</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>2240</v>
+        <v>1216</v>
       </c>
       <c r="D866" s="2" t="s">
-        <v>2241</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>38</v>
+        <v>2085</v>
       </c>
       <c r="B867" t="s">
-        <v>2353</v>
+        <v>2361</v>
       </c>
       <c r="C867" s="2" t="s">
-        <v>2354</v>
+        <v>1086</v>
       </c>
       <c r="D867" s="2" t="s">
-        <v>2355</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>38</v>
+        <v>2085</v>
       </c>
       <c r="B868" t="s">
-        <v>2356</v>
+        <v>2362</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>1216</v>
+        <v>1089</v>
       </c>
       <c r="D868" s="2" t="s">
-        <v>1577</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>38</v>
+        <v>2085</v>
       </c>
       <c r="B869" t="s">
-        <v>2357</v>
+        <v>2363</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>2358</v>
+        <v>2016</v>
       </c>
       <c r="D869" s="2" t="s">
-        <v>2359</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>38</v>
+        <v>2085</v>
       </c>
       <c r="B870" t="s">
-        <v>2360</v>
+        <v>2364</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>2361</v>
+        <v>2252</v>
       </c>
       <c r="D870" s="2" t="s">
-        <v>2362</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="871">
@@ -20509,13 +20545,13 @@
         <v>38</v>
       </c>
       <c r="B871" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D871" s="2" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="872">
@@ -20523,13 +20559,13 @@
         <v>38</v>
       </c>
       <c r="B872" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>676</v>
+        <v>1228</v>
       </c>
       <c r="D872" s="2" t="s">
-        <v>677</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="873">
@@ -20537,13 +20573,13 @@
         <v>38</v>
       </c>
       <c r="B873" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="C873" s="2" t="s">
-        <v>713</v>
+        <v>2370</v>
       </c>
       <c r="D873" s="2" t="s">
-        <v>714</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="874">
@@ -20551,13 +20587,13 @@
         <v>38</v>
       </c>
       <c r="B874" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="C874" s="2" t="s">
-        <v>2369</v>
+        <v>2373</v>
       </c>
       <c r="D874" s="2" t="s">
-        <v>2370</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="875">
@@ -20565,13 +20601,13 @@
         <v>38</v>
       </c>
       <c r="B875" t="s">
-        <v>2371</v>
+        <v>2375</v>
       </c>
       <c r="C875" s="2" t="s">
-        <v>695</v>
+        <v>2376</v>
       </c>
       <c r="D875" s="2" t="s">
-        <v>696</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="876">
@@ -20579,13 +20615,13 @@
         <v>38</v>
       </c>
       <c r="B876" t="s">
-        <v>2372</v>
+        <v>2378</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>2373</v>
+        <v>688</v>
       </c>
       <c r="D876" s="2" t="s">
-        <v>2374</v>
+        <v>689</v>
       </c>
     </row>
     <row r="877">
@@ -20593,13 +20629,13 @@
         <v>38</v>
       </c>
       <c r="B877" t="s">
-        <v>2375</v>
+        <v>2379</v>
       </c>
       <c r="C877" s="2" t="s">
-        <v>2376</v>
+        <v>725</v>
       </c>
       <c r="D877" s="2" t="s">
-        <v>2377</v>
+        <v>726</v>
       </c>
     </row>
     <row r="878">
@@ -20607,13 +20643,13 @@
         <v>38</v>
       </c>
       <c r="B878" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="C878" s="2" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D878" s="2" t="s">
-        <v>1657</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="879">
@@ -20621,13 +20657,13 @@
         <v>38</v>
       </c>
       <c r="B879" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="C879" s="2" t="s">
-        <v>2381</v>
+        <v>707</v>
       </c>
       <c r="D879" s="2" t="s">
-        <v>1660</v>
+        <v>708</v>
       </c>
     </row>
     <row r="880">
@@ -20635,13 +20671,13 @@
         <v>38</v>
       </c>
       <c r="B880" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="C880" s="2" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="D880" s="2" t="s">
-        <v>690</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="881">
@@ -20649,13 +20685,13 @@
         <v>38</v>
       </c>
       <c r="B881" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D881" s="2" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="882">
@@ -20663,13 +20699,13 @@
         <v>38</v>
       </c>
       <c r="B882" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C882" s="2" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D882" s="2" t="s">
-        <v>2389</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="883">
@@ -20677,13 +20713,13 @@
         <v>38</v>
       </c>
       <c r="B883" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="C883" s="2" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="D883" s="2" t="s">
-        <v>2392</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="884">
@@ -20691,13 +20727,13 @@
         <v>38</v>
       </c>
       <c r="B884" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="C884" s="2" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="D884" s="2" t="s">
-        <v>2395</v>
+        <v>702</v>
       </c>
     </row>
     <row r="885">
@@ -20778,10 +20814,10 @@
         <v>2411</v>
       </c>
       <c r="C890" s="2" t="s">
-        <v>139</v>
+        <v>2412</v>
       </c>
       <c r="D890" s="2" t="s">
-        <v>140</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="891">
@@ -20789,13 +20825,13 @@
         <v>38</v>
       </c>
       <c r="B891" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="C891" s="2" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D891" s="2" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="892">
@@ -20803,13 +20839,13 @@
         <v>38</v>
       </c>
       <c r="B892" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C892" s="2" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="D892" s="2" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="893">
@@ -20817,13 +20853,13 @@
         <v>38</v>
       </c>
       <c r="B893" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="D893" s="2" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="894">
@@ -20831,13 +20867,13 @@
         <v>38</v>
       </c>
       <c r="B894" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="C894" s="2" t="s">
-        <v>2422</v>
+        <v>139</v>
       </c>
       <c r="D894" s="2" t="s">
-        <v>2423</v>
+        <v>140</v>
       </c>
     </row>
     <row r="895">
@@ -20890,10 +20926,10 @@
         <v>2433</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>695</v>
+        <v>2434</v>
       </c>
       <c r="D898" s="2" t="s">
-        <v>696</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="899">
@@ -20901,13 +20937,13 @@
         <v>38</v>
       </c>
       <c r="B899" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="C899" s="2" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D899" s="2" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="900">
@@ -20915,13 +20951,13 @@
         <v>38</v>
       </c>
       <c r="B900" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="C900" s="2" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D900" s="2" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="901">
@@ -20929,13 +20965,13 @@
         <v>38</v>
       </c>
       <c r="B901" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="D901" s="2" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="902">
@@ -20943,13 +20979,13 @@
         <v>38</v>
       </c>
       <c r="B902" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="C902" s="2" t="s">
-        <v>2444</v>
+        <v>707</v>
       </c>
       <c r="D902" s="2" t="s">
-        <v>2445</v>
+        <v>708</v>
       </c>
     </row>
     <row r="903">
@@ -21108,7 +21144,7 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B914" t="s">
         <v>2479</v>
@@ -21122,7 +21158,7 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B915" t="s">
         <v>2482</v>
@@ -21136,7 +21172,7 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B916" t="s">
         <v>2485</v>
@@ -21150,7 +21186,7 @@
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B917" t="s">
         <v>2488</v>
@@ -21170,10 +21206,10 @@
         <v>2491</v>
       </c>
       <c r="C918" s="2" t="s">
-        <v>192</v>
+        <v>2492</v>
       </c>
       <c r="D918" s="2" t="s">
-        <v>193</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="919">
@@ -21181,13 +21217,13 @@
         <v>41</v>
       </c>
       <c r="B919" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="C919" s="2" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D919" s="2" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="920">
@@ -21195,13 +21231,13 @@
         <v>41</v>
       </c>
       <c r="B920" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="C920" s="2" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D920" s="2" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="921">
@@ -21209,13 +21245,13 @@
         <v>41</v>
       </c>
       <c r="B921" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="C921" s="2" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="D921" s="2" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="922">
@@ -21223,13 +21259,13 @@
         <v>41</v>
       </c>
       <c r="B922" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="C922" s="2" t="s">
-        <v>2502</v>
+        <v>192</v>
       </c>
       <c r="D922" s="2" t="s">
-        <v>2503</v>
+        <v>193</v>
       </c>
     </row>
     <row r="923">
@@ -21271,7 +21307,7 @@
         <v>2511</v>
       </c>
       <c r="D925" s="2" t="s">
-        <v>77</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="926">
@@ -21279,13 +21315,13 @@
         <v>41</v>
       </c>
       <c r="B926" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="C926" s="2" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D926" s="2" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="927">
@@ -21293,13 +21329,13 @@
         <v>41</v>
       </c>
       <c r="B927" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="C927" s="2" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D927" s="2" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="928">
@@ -21307,13 +21343,13 @@
         <v>41</v>
       </c>
       <c r="B928" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="C928" s="2" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="D928" s="2" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="929">
@@ -21321,13 +21357,13 @@
         <v>41</v>
       </c>
       <c r="B929" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C929" s="2" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="D929" s="2" t="s">
-        <v>2520</v>
+        <v>77</v>
       </c>
     </row>
     <row r="930">
@@ -21335,13 +21371,13 @@
         <v>41</v>
       </c>
       <c r="B930" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="C930" s="2" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D930" s="2" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="931">
@@ -21349,13 +21385,13 @@
         <v>41</v>
       </c>
       <c r="B931" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C931" s="2" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D931" s="2" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="932">
@@ -21363,13 +21399,13 @@
         <v>41</v>
       </c>
       <c r="B932" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C932" s="2" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D932" s="2" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="933">
@@ -21377,13 +21413,13 @@
         <v>41</v>
       </c>
       <c r="B933" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C933" s="2" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D933" s="2" t="s">
         <v>2532</v>
-      </c>
-      <c r="C933" s="2" t="s">
-        <v>2533</v>
-      </c>
-      <c r="D933" s="2" t="s">
-        <v>2534</v>
       </c>
     </row>
     <row r="934">
@@ -21394,10 +21430,10 @@
         <v>2535</v>
       </c>
       <c r="C934" s="2" t="s">
-        <v>1071</v>
+        <v>2536</v>
       </c>
       <c r="D934" s="2" t="s">
-        <v>1072</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="935">
@@ -21405,13 +21441,13 @@
         <v>41</v>
       </c>
       <c r="B935" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="C935" s="2" t="s">
-        <v>416</v>
+        <v>2539</v>
       </c>
       <c r="D935" s="2" t="s">
-        <v>417</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="936">
@@ -21419,13 +21455,13 @@
         <v>41</v>
       </c>
       <c r="B936" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="C936" s="2" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="D936" s="2" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="937">
@@ -21433,13 +21469,13 @@
         <v>41</v>
       </c>
       <c r="B937" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="C937" s="2" t="s">
-        <v>1090</v>
+        <v>2545</v>
       </c>
       <c r="D937" s="2" t="s">
-        <v>1091</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="938">
@@ -21447,13 +21483,13 @@
         <v>41</v>
       </c>
       <c r="B938" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="C938" s="2" t="s">
-        <v>2542</v>
+        <v>1083</v>
       </c>
       <c r="D938" s="2" t="s">
-        <v>2543</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="939">
@@ -21461,13 +21497,13 @@
         <v>41</v>
       </c>
       <c r="B939" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="C939" s="2" t="s">
-        <v>2545</v>
+        <v>416</v>
       </c>
       <c r="D939" s="2" t="s">
-        <v>2546</v>
+        <v>417</v>
       </c>
     </row>
     <row r="940">
@@ -21475,13 +21511,13 @@
         <v>41</v>
       </c>
       <c r="B940" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="C940" s="2" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="D940" s="2" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="941">
@@ -21489,13 +21525,13 @@
         <v>41</v>
       </c>
       <c r="B941" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="C941" s="2" t="s">
-        <v>2551</v>
+        <v>1102</v>
       </c>
       <c r="D941" s="2" t="s">
-        <v>2552</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="942">
@@ -21646,10 +21682,10 @@
         <v>2583</v>
       </c>
       <c r="C952" s="2" t="s">
-        <v>2483</v>
+        <v>2584</v>
       </c>
       <c r="D952" s="2" t="s">
-        <v>2484</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="953">
@@ -21657,13 +21693,13 @@
         <v>41</v>
       </c>
       <c r="B953" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="C953" s="2" t="s">
-        <v>416</v>
+        <v>2587</v>
       </c>
       <c r="D953" s="2" t="s">
-        <v>417</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="954">
@@ -21671,13 +21707,13 @@
         <v>41</v>
       </c>
       <c r="B954" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="C954" s="2" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="D954" s="2" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="955">
@@ -21685,13 +21721,13 @@
         <v>41</v>
       </c>
       <c r="B955" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="C955" s="2" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="D955" s="2" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="956">
@@ -21699,13 +21735,13 @@
         <v>41</v>
       </c>
       <c r="B956" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="C956" s="2" t="s">
-        <v>2592</v>
+        <v>2495</v>
       </c>
       <c r="D956" s="2" t="s">
-        <v>2593</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="957">
@@ -21713,13 +21749,13 @@
         <v>41</v>
       </c>
       <c r="B957" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="C957" s="2" t="s">
-        <v>2595</v>
+        <v>416</v>
       </c>
       <c r="D957" s="2" t="s">
-        <v>2596</v>
+        <v>417</v>
       </c>
     </row>
     <row r="958">
@@ -21730,10 +21766,10 @@
         <v>2597</v>
       </c>
       <c r="C958" s="2" t="s">
-        <v>428</v>
+        <v>2598</v>
       </c>
       <c r="D958" s="2" t="s">
-        <v>429</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="959">
@@ -21741,13 +21777,13 @@
         <v>41</v>
       </c>
       <c r="B959" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="C959" s="2" t="s">
-        <v>254</v>
+        <v>2601</v>
       </c>
       <c r="D959" s="2" t="s">
-        <v>255</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="960">
@@ -21755,13 +21791,13 @@
         <v>41</v>
       </c>
       <c r="B960" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="C960" s="2" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="D960" s="2" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="961">
@@ -21769,13 +21805,13 @@
         <v>41</v>
       </c>
       <c r="B961" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="C961" s="2" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="D961" s="2" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="962">
@@ -21783,13 +21819,13 @@
         <v>41</v>
       </c>
       <c r="B962" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="C962" s="2" t="s">
-        <v>2606</v>
+        <v>428</v>
       </c>
       <c r="D962" s="2" t="s">
-        <v>2607</v>
+        <v>429</v>
       </c>
     </row>
     <row r="963">
@@ -21797,13 +21833,13 @@
         <v>41</v>
       </c>
       <c r="B963" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="C963" s="2" t="s">
-        <v>2551</v>
+        <v>254</v>
       </c>
       <c r="D963" s="2" t="s">
-        <v>2552</v>
+        <v>255</v>
       </c>
     </row>
     <row r="964">
@@ -21811,13 +21847,13 @@
         <v>41</v>
       </c>
       <c r="B964" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
       <c r="C964" s="2" t="s">
-        <v>2610</v>
+        <v>2612</v>
       </c>
       <c r="D964" s="2" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="965">
@@ -21825,13 +21861,13 @@
         <v>41</v>
       </c>
       <c r="B965" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="C965" s="2" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="D965" s="2" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="966">
@@ -21839,13 +21875,13 @@
         <v>41</v>
       </c>
       <c r="B966" t="s">
-        <v>2615</v>
+        <v>2617</v>
       </c>
       <c r="C966" s="2" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="D966" s="2" t="s">
-        <v>2617</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="967">
@@ -21853,13 +21889,13 @@
         <v>41</v>
       </c>
       <c r="B967" t="s">
-        <v>2618</v>
+        <v>2620</v>
       </c>
       <c r="C967" s="2" t="s">
-        <v>2619</v>
+        <v>2563</v>
       </c>
       <c r="D967" s="2" t="s">
-        <v>2620</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="968">
@@ -21870,10 +21906,10 @@
         <v>2621</v>
       </c>
       <c r="C968" s="2" t="s">
-        <v>2294</v>
+        <v>2622</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>2295</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="969">
@@ -21881,13 +21917,13 @@
         <v>41</v>
       </c>
       <c r="B969" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="C969" s="2" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
       <c r="D969" s="2" t="s">
-        <v>2624</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="970">
@@ -21895,13 +21931,13 @@
         <v>41</v>
       </c>
       <c r="B970" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="C970" s="2" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="D970" s="2" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="971">
@@ -21909,13 +21945,13 @@
         <v>41</v>
       </c>
       <c r="B971" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="C971" s="2" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="D971" s="2" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="972">
@@ -21923,13 +21959,13 @@
         <v>41</v>
       </c>
       <c r="B972" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="C972" s="2" t="s">
-        <v>2632</v>
+        <v>2306</v>
       </c>
       <c r="D972" s="2" t="s">
-        <v>2633</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="973">
@@ -21948,97 +21984,97 @@
     </row>
     <row r="974">
       <c r="A974" t="s">
+        <v>41</v>
+      </c>
+      <c r="B974" t="s">
         <v>2637</v>
       </c>
-      <c r="B974" t="s">
+      <c r="C974" s="2" t="s">
         <v>2638</v>
       </c>
-      <c r="C974" s="2" t="s">
+      <c r="D974" s="2" t="s">
         <v>2639</v>
-      </c>
-      <c r="D974" s="2" t="s">
-        <v>2640</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>2637</v>
+        <v>41</v>
       </c>
       <c r="B975" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C975" s="2" t="s">
         <v>2641</v>
       </c>
-      <c r="C975" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="D975" s="2" t="s">
-        <v>417</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>2637</v>
+        <v>41</v>
       </c>
       <c r="B976" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C976" s="2" t="s">
-        <v>863</v>
+        <v>2644</v>
       </c>
       <c r="D976" s="2" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>2637</v>
+        <v>41</v>
       </c>
       <c r="B977" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="C977" s="2" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="D977" s="2" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B978" t="s">
-        <v>2647</v>
+        <v>2650</v>
       </c>
       <c r="C978" s="2" t="s">
-        <v>2648</v>
+        <v>2651</v>
       </c>
       <c r="D978" s="2" t="s">
-        <v>2649</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B979" t="s">
-        <v>2650</v>
+        <v>2653</v>
       </c>
       <c r="C979" s="2" t="s">
-        <v>2651</v>
+        <v>416</v>
       </c>
       <c r="D979" s="2" t="s">
-        <v>2652</v>
+        <v>417</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B980" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="C980" s="2" t="s">
-        <v>2654</v>
+        <v>875</v>
       </c>
       <c r="D980" s="2" t="s">
         <v>2655</v>
@@ -22046,7 +22082,7 @@
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B981" t="s">
         <v>2656</v>
@@ -22060,7 +22096,7 @@
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B982" t="s">
         <v>2659</v>
@@ -22074,7 +22110,7 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B983" t="s">
         <v>2662</v>
@@ -22088,7 +22124,7 @@
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B984" t="s">
         <v>2665</v>
@@ -22102,7 +22138,7 @@
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B985" t="s">
         <v>2668</v>
@@ -22116,7 +22152,7 @@
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B986" t="s">
         <v>2671</v>
@@ -22130,7 +22166,7 @@
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B987" t="s">
         <v>2674</v>
@@ -22144,7 +22180,7 @@
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B988" t="s">
         <v>2677</v>
@@ -22158,7 +22194,7 @@
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>2637</v>
+        <v>2649</v>
       </c>
       <c r="B989" t="s">
         <v>2680</v>
@@ -22172,63 +22208,63 @@
     </row>
     <row r="990">
       <c r="A990" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B990" t="s">
         <v>2683</v>
       </c>
-      <c r="B990" t="s">
+      <c r="C990" s="2" t="s">
         <v>2684</v>
       </c>
-      <c r="C990" s="2" t="s">
+      <c r="D990" s="2" t="s">
         <v>2685</v>
-      </c>
-      <c r="D990" s="2" t="s">
-        <v>2686</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>2683</v>
+        <v>2649</v>
       </c>
       <c r="B991" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C991" s="2" t="s">
         <v>2687</v>
       </c>
-      <c r="C991" s="2" t="s">
+      <c r="D991" s="2" t="s">
         <v>2688</v>
-      </c>
-      <c r="D991" s="2" t="s">
-        <v>2689</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>2683</v>
+        <v>2649</v>
       </c>
       <c r="B992" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C992" s="2" t="s">
         <v>2690</v>
       </c>
-      <c r="C992" s="2" t="s">
+      <c r="D992" s="2" t="s">
         <v>2691</v>
-      </c>
-      <c r="D992" s="2" t="s">
-        <v>2692</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>2683</v>
+        <v>2649</v>
       </c>
       <c r="B993" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C993" s="2" t="s">
         <v>2693</v>
       </c>
-      <c r="C993" s="2" t="s">
+      <c r="D993" s="2" t="s">
         <v>2694</v>
-      </c>
-      <c r="D993" s="2" t="s">
-        <v>2695</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B994" t="s">
         <v>2696</v>
@@ -22242,7 +22278,7 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B995" t="s">
         <v>2699</v>
@@ -22256,7 +22292,7 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B996" t="s">
         <v>2702</v>
@@ -22270,7 +22306,7 @@
     </row>
     <row r="997">
       <c r="A997" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B997" t="s">
         <v>2705</v>
@@ -22284,7 +22320,7 @@
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B998" t="s">
         <v>2708</v>
@@ -22298,7 +22334,7 @@
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="B999" t="s">
         <v>2711</v>
@@ -22308,6 +22344,62 @@
       </c>
       <c r="D999" s="2" t="s">
         <v>2713</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C1000" s="2" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D1000" s="2" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1001" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D1001" s="2" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1002" s="2" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D1002" s="2" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C1003" s="2" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D1003" s="2" t="s">
+        <v>2725</v>
       </c>
     </row>
   </sheetData>
@@ -22322,32 +22414,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2714</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2715</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2716</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2717</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2718</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2719</v>
+        <v>2731</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hebrew-review.xlsx
+++ b/docs/hebrew-review.xlsx
@@ -6734,10 +6734,10 @@
     <t>layout.warnings.none</t>
   </si>
   <si>
-    <t>No capacity warnings.</t>
-  </si>
-  <si>
-    <t>אין אזהרות קיבולת.</t>
+    <t>No tables over capacity.</t>
+  </si>
+  <si>
+    <t>אין שולחנות בחריגה מהקיבולת.</t>
   </si>
   <si>
     <t>layout.selected.title</t>
@@ -7211,10 +7211,10 @@
     <t>בר</t>
   </si>
   <si>
-    <t>layout.objects.STEPS</t>
-  </si>
-  <si>
-    <t>Steps</t>
+    <t>layout.objects.STAIRS</t>
+  </si>
+  <si>
+    <t>Stairs</t>
   </si>
   <si>
     <t>מדרגות</t>
@@ -7583,10 +7583,10 @@
     <t>layout.arrangement.inspector.labelHint</t>
   </si>
   <si>
-    <t>Shown instead of the kind, such as Dance floor.</t>
-  </si>
-  <si>
-    <t>מוצגת במקום סוג הפריט, למשל רחבת ריקודים.</t>
+    <t>Shown instead of the kind, such as Dance floor or Stairs to the balcony.</t>
+  </si>
+  <si>
+    <t>מוצגת במקום סוג הפריט, למשל רחבת ריקודים או מדרגות ליציע.</t>
   </si>
   <si>
     <t>layout.arrangement.inspector.unplace</t>

--- a/docs/hebrew-review.xlsx
+++ b/docs/hebrew-review.xlsx
@@ -6467,18 +6467,6 @@
     <t>layout.list.caption</t>
   </si>
   <si>
-    <t>layout.list.selectAll</t>
-  </si>
-  <si>
-    <t>Select all tables on this page</t>
-  </si>
-  <si>
-    <t>בחירת כל השולחנות בעמוד זה</t>
-  </si>
-  <si>
-    <t>layout.list.selectRow</t>
-  </si>
-  <si>
     <t>layout.columns.number</t>
   </si>
   <si>
@@ -6722,24 +6710,6 @@
     <t>נסו מספר אחר או צורה אחרת.</t>
   </si>
   <si>
-    <t>layout.warnings.title</t>
-  </si>
-  <si>
-    <t>Capacity Warnings</t>
-  </si>
-  <si>
-    <t>אזהרות קיבולת</t>
-  </si>
-  <si>
-    <t>layout.warnings.none</t>
-  </si>
-  <si>
-    <t>No tables over capacity.</t>
-  </si>
-  <si>
-    <t>אין שולחנות בחריגה מהקיבולת.</t>
-  </si>
-  <si>
     <t>layout.selected.title</t>
   </si>
   <si>
@@ -6770,6 +6740,15 @@
     <t>layout.selected.manage</t>
   </si>
   <si>
+    <t>layout.selected.hintList</t>
+  </si>
+  <si>
+    <t>Select a table in the list to see its guests here.</t>
+  </si>
+  <si>
+    <t>בחרו שולחן ברשימה כדי לראות כאן את האורחים שלו.</t>
+  </si>
+  <si>
     <t>layout.form.addTitle</t>
   </si>
   <si>
@@ -6908,45 +6887,6 @@
     <t>שולחן {{number}} נמחק.</t>
   </si>
   <si>
-    <t>layout.delete.titleMany</t>
-  </si>
-  <si>
-    <t>Delete {{count}} Tables</t>
-  </si>
-  <si>
-    <t>מחיקת {{count}} שולחנות</t>
-  </si>
-  <si>
-    <t>layout.delete.bodyMany</t>
-  </si>
-  <si>
-    <t>Tables {{numbers}} will be deleted. No guest is deleted.</t>
-  </si>
-  <si>
-    <t>השולחנות {{numbers}} יימחקו. אף אורח לא יימחק.</t>
-  </si>
-  <si>
-    <t>layout.delete.seatedMany</t>
-  </si>
-  <si>
-    <t>Guest parties at these tables: {{parties}} (attendees: {{attendees}}). They will be left without a table.</t>
-  </si>
-  <si>
-    <t>קבוצות אורחים בשולחנות אלה: {{parties}} (משתתפים: {{attendees}}). הן יישארו ללא שולחן.</t>
-  </si>
-  <si>
-    <t>layout.delete.confirmMany</t>
-  </si>
-  <si>
-    <t>layout.delete.doneMany</t>
-  </si>
-  <si>
-    <t>{{count}} tables were deleted.</t>
-  </si>
-  <si>
-    <t>{{count}} שולחנות נמחקו.</t>
-  </si>
-  <si>
     <t>layout.manage.title</t>
   </si>
   <si>
@@ -7163,27 +7103,6 @@
     <t>layout.export.headings.tableNumber</t>
   </si>
   <si>
-    <t>layout.bulk.label</t>
-  </si>
-  <si>
-    <t>Selected tables</t>
-  </si>
-  <si>
-    <t>שולחנות שנבחרו</t>
-  </si>
-  <si>
-    <t>layout.bulk.selected</t>
-  </si>
-  <si>
-    <t>layout.bulk.export</t>
-  </si>
-  <si>
-    <t>layout.bulk.delete</t>
-  </si>
-  <si>
-    <t>layout.bulk.clear</t>
-  </si>
-  <si>
     <t>layout.objects.WALL</t>
   </si>
   <si>
@@ -7245,24 +7164,6 @@
   </si>
   <si>
     <t>עציץ</t>
-  </si>
-  <si>
-    <t>layout.preview.title</t>
-  </si>
-  <si>
-    <t>Arrangement Preview</t>
-  </si>
-  <si>
-    <t>תצוגה מקדימה של הסידור</t>
-  </si>
-  <si>
-    <t>layout.preview.open</t>
-  </si>
-  <si>
-    <t>Open Arrangement</t>
-  </si>
-  <si>
-    <t>פתיחת הסידור</t>
   </si>
   <si>
     <t>layout.arrangement.title</t>
@@ -8878,7 +8779,7 @@
     <t>{{name}}, {{count}} and similar marks are filled in by the application; keep them in the correction.</t>
   </si>
   <si>
-    <t>1075 texts in all.</t>
+    <t>1060 texts in all.</t>
   </si>
 </sst>
 </file>
@@ -19929,7 +19830,7 @@
         <v>2151</v>
       </c>
       <c r="D785" s="2" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="786">
@@ -19937,13 +19838,13 @@
         <v>2088</v>
       </c>
       <c r="B786" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C786" s="2" t="s">
         <v>2153</v>
       </c>
-      <c r="C786" s="2" t="s">
-        <v>1116</v>
-      </c>
       <c r="D786" s="2" t="s">
-        <v>1117</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="787">
@@ -19951,13 +19852,13 @@
         <v>2088</v>
       </c>
       <c r="B787" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="D787" s="2" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="788">
@@ -19965,13 +19866,13 @@
         <v>2088</v>
       </c>
       <c r="B788" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="D788" s="2" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="789">
@@ -19979,13 +19880,13 @@
         <v>2088</v>
       </c>
       <c r="B789" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="790">
@@ -19993,13 +19894,13 @@
         <v>2088</v>
       </c>
       <c r="B790" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>2163</v>
+        <v>878</v>
       </c>
       <c r="D790" s="2" t="s">
-        <v>2164</v>
+        <v>879</v>
       </c>
     </row>
     <row r="791">
@@ -20010,10 +19911,10 @@
         <v>2165</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>2166</v>
+        <v>1105</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>2167</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="792">
@@ -20021,13 +19922,13 @@
         <v>2088</v>
       </c>
       <c r="B792" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C792" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D792" s="2" t="s">
         <v>2168</v>
-      </c>
-      <c r="C792" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="D792" s="2" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="793">
@@ -20038,10 +19939,10 @@
         <v>2169</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>1105</v>
+        <v>2170</v>
       </c>
       <c r="D793" s="2" t="s">
-        <v>1106</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="794">
@@ -20049,13 +19950,13 @@
         <v>2088</v>
       </c>
       <c r="B794" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>2171</v>
+        <v>2153</v>
       </c>
       <c r="D794" s="2" t="s">
-        <v>2172</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="795">
@@ -20080,10 +19981,10 @@
         <v>2176</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>2157</v>
+        <v>2177</v>
       </c>
       <c r="D796" s="2" t="s">
-        <v>2158</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="797">
@@ -20091,13 +19992,13 @@
         <v>2088</v>
       </c>
       <c r="B797" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="D797" s="2" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="798">
@@ -20105,13 +20006,13 @@
         <v>2088</v>
       </c>
       <c r="B798" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="D798" s="2" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="799">
@@ -20119,13 +20020,13 @@
         <v>2088</v>
       </c>
       <c r="B799" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="D799" s="2" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="800">
@@ -20133,13 +20034,13 @@
         <v>2088</v>
       </c>
       <c r="B800" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="D800" s="2" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="801">
@@ -20147,13 +20048,13 @@
         <v>2088</v>
       </c>
       <c r="B801" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="D801" s="2" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="802">
@@ -20161,13 +20062,13 @@
         <v>2088</v>
       </c>
       <c r="B802" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="D802" s="2" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="803">
@@ -20175,13 +20076,13 @@
         <v>2088</v>
       </c>
       <c r="B803" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="804">
@@ -20189,13 +20090,13 @@
         <v>2088</v>
       </c>
       <c r="B804" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="D804" s="2" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="805">
@@ -20203,13 +20104,13 @@
         <v>2088</v>
       </c>
       <c r="B805" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="806">
@@ -20217,13 +20118,13 @@
         <v>2088</v>
       </c>
       <c r="B806" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="D806" s="2" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="807">
@@ -20231,13 +20132,13 @@
         <v>2088</v>
       </c>
       <c r="B807" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2208</v>
+        <v>1136</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>2209</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="808">
@@ -20262,10 +20163,10 @@
         <v>2213</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>1136</v>
+        <v>2214</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>1137</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="810">
@@ -20273,13 +20174,13 @@
         <v>2088</v>
       </c>
       <c r="B810" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="D810" s="2" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="811">
@@ -20287,13 +20188,13 @@
         <v>2088</v>
       </c>
       <c r="B811" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="D811" s="2" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="812">
@@ -20301,13 +20202,13 @@
         <v>2088</v>
       </c>
       <c r="B812" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="D812" s="2" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="813">
@@ -20315,13 +20216,13 @@
         <v>2088</v>
       </c>
       <c r="B813" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C813" s="2" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="814">
@@ -20329,13 +20230,13 @@
         <v>2088</v>
       </c>
       <c r="B814" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D814" s="2" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="815">
@@ -20343,13 +20244,13 @@
         <v>2088</v>
       </c>
       <c r="B815" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="D815" s="2" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="816">
@@ -20357,13 +20258,13 @@
         <v>2088</v>
       </c>
       <c r="B816" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="C816" s="2" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="D816" s="2" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="817">
@@ -20371,13 +20272,13 @@
         <v>2088</v>
       </c>
       <c r="B817" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="C817" s="2" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="D817" s="2" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="818">
@@ -20385,13 +20286,13 @@
         <v>2088</v>
       </c>
       <c r="B818" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>2239</v>
+        <v>955</v>
       </c>
       <c r="D818" s="2" t="s">
-        <v>2240</v>
+        <v>325</v>
       </c>
     </row>
     <row r="819">
@@ -20416,10 +20317,10 @@
         <v>2244</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>2245</v>
+        <v>2100</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>2246</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="821">
@@ -20427,13 +20328,13 @@
         <v>2088</v>
       </c>
       <c r="B821" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D821" s="2" t="s">
         <v>2247</v>
-      </c>
-      <c r="C821" s="2" t="s">
-        <v>2248</v>
-      </c>
-      <c r="D821" s="2" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="822">
@@ -20441,13 +20342,13 @@
         <v>2088</v>
       </c>
       <c r="B822" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D822" s="2" t="s">
         <v>2250</v>
-      </c>
-      <c r="C822" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="D822" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="823">
@@ -20458,10 +20359,10 @@
         <v>2251</v>
       </c>
       <c r="C823" s="2" t="s">
-        <v>2100</v>
+        <v>2156</v>
       </c>
       <c r="D823" s="2" t="s">
-        <v>2101</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="824">
@@ -20486,10 +20387,10 @@
         <v>2255</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>2256</v>
+        <v>2153</v>
       </c>
       <c r="D825" s="2" t="s">
-        <v>2257</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="826">
@@ -20497,13 +20398,13 @@
         <v>2088</v>
       </c>
       <c r="B826" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C826" s="2" t="s">
-        <v>2160</v>
+        <v>2100</v>
       </c>
       <c r="D826" s="2" t="s">
-        <v>2161</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="827">
@@ -20511,13 +20412,13 @@
         <v>2088</v>
       </c>
       <c r="B827" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C827" s="2" t="s">
-        <v>2260</v>
+        <v>1231</v>
       </c>
       <c r="D827" s="2" t="s">
-        <v>2261</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="828">
@@ -20525,13 +20426,13 @@
         <v>2088</v>
       </c>
       <c r="B828" t="s">
-        <v>2262</v>
+        <v>2258</v>
       </c>
       <c r="C828" s="2" t="s">
-        <v>2157</v>
+        <v>2259</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>2158</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="829">
@@ -20539,13 +20440,13 @@
         <v>2088</v>
       </c>
       <c r="B829" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D829" s="2" t="s">
         <v>2263</v>
-      </c>
-      <c r="C829" s="2" t="s">
-        <v>2100</v>
-      </c>
-      <c r="D829" s="2" t="s">
-        <v>2101</v>
       </c>
     </row>
     <row r="830">
@@ -20556,10 +20457,10 @@
         <v>2264</v>
       </c>
       <c r="C830" s="2" t="s">
-        <v>1231</v>
+        <v>2265</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>1592</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="831">
@@ -20567,13 +20468,13 @@
         <v>2088</v>
       </c>
       <c r="B831" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="C831" s="2" t="s">
-        <v>2266</v>
+        <v>245</v>
       </c>
       <c r="D831" s="2" t="s">
-        <v>2267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="832">
@@ -20612,10 +20513,10 @@
         <v>2274</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>245</v>
+        <v>2275</v>
       </c>
       <c r="D834" s="2" t="s">
-        <v>246</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="835">
@@ -20623,13 +20524,13 @@
         <v>2088</v>
       </c>
       <c r="B835" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="C835" s="2" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="836">
@@ -20637,13 +20538,13 @@
         <v>2088</v>
       </c>
       <c r="B836" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="C836" s="2" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="837">
@@ -20651,13 +20552,13 @@
         <v>2088</v>
       </c>
       <c r="B837" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="C837" s="2" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="838">
@@ -20665,13 +20566,13 @@
         <v>2088</v>
       </c>
       <c r="B838" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="C838" s="2" t="s">
-        <v>2285</v>
+        <v>2211</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>2286</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="839">
@@ -20710,10 +20611,10 @@
         <v>2293</v>
       </c>
       <c r="C841" s="2" t="s">
-        <v>2215</v>
+        <v>2294</v>
       </c>
       <c r="D841" s="2" t="s">
-        <v>2216</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="842">
@@ -20721,13 +20622,13 @@
         <v>2088</v>
       </c>
       <c r="B842" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="843">
@@ -20735,13 +20636,13 @@
         <v>2088</v>
       </c>
       <c r="B843" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="C843" s="2" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="D843" s="2" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="844">
@@ -20749,13 +20650,13 @@
         <v>2088</v>
       </c>
       <c r="B844" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="C844" s="2" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D844" s="2" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="845">
@@ -20763,13 +20664,13 @@
         <v>2088</v>
       </c>
       <c r="B845" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="C845" s="2" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="D845" s="2" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="846">
@@ -20777,13 +20678,13 @@
         <v>2088</v>
       </c>
       <c r="B846" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="C846" s="2" t="s">
-        <v>2298</v>
+        <v>2309</v>
       </c>
       <c r="D846" s="2" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="847">
@@ -20791,13 +20692,13 @@
         <v>2088</v>
       </c>
       <c r="B847" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="C847" s="2" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="848">
@@ -20805,13 +20706,13 @@
         <v>2088</v>
       </c>
       <c r="B848" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
       <c r="C848" s="2" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="D848" s="2" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="849">
@@ -20819,13 +20720,13 @@
         <v>2088</v>
       </c>
       <c r="B849" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="C849" s="2" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="D849" s="2" t="s">
-        <v>2315</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="850">
@@ -20833,13 +20734,13 @@
         <v>2088</v>
       </c>
       <c r="B850" t="s">
-        <v>2316</v>
+        <v>2320</v>
       </c>
       <c r="C850" s="2" t="s">
-        <v>2317</v>
+        <v>2321</v>
       </c>
       <c r="D850" s="2" t="s">
-        <v>2318</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="851">
@@ -20847,13 +20748,13 @@
         <v>2088</v>
       </c>
       <c r="B851" t="s">
-        <v>2319</v>
+        <v>2323</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>2320</v>
+        <v>1122</v>
       </c>
       <c r="D851" s="2" t="s">
-        <v>2321</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="852">
@@ -20861,13 +20762,13 @@
         <v>2088</v>
       </c>
       <c r="B852" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="C852" s="2" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D852" s="2" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="853">
@@ -20875,13 +20776,13 @@
         <v>2088</v>
       </c>
       <c r="B853" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="C853" s="2" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D853" s="2" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="854">
@@ -20889,13 +20790,13 @@
         <v>2088</v>
       </c>
       <c r="B854" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="C854" s="2" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="D854" s="2" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="855">
@@ -20903,13 +20804,13 @@
         <v>2088</v>
       </c>
       <c r="B855" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="C855" s="2" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="D855" s="2" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="856">
@@ -20917,13 +20818,13 @@
         <v>2088</v>
       </c>
       <c r="B856" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D856" s="2" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="857">
@@ -20931,13 +20832,13 @@
         <v>2088</v>
       </c>
       <c r="B857" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="D857" s="2" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="858">
@@ -20945,13 +20846,13 @@
         <v>2088</v>
       </c>
       <c r="B858" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="C858" s="2" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D858" s="2" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="859">
@@ -20959,13 +20860,13 @@
         <v>2088</v>
       </c>
       <c r="B859" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="C859" s="2" t="s">
-        <v>1122</v>
+        <v>2346</v>
       </c>
       <c r="D859" s="2" t="s">
-        <v>1123</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="860">
@@ -20973,13 +20874,13 @@
         <v>2088</v>
       </c>
       <c r="B860" t="s">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>2345</v>
+        <v>1491</v>
       </c>
       <c r="D860" s="2" t="s">
-        <v>2346</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="861">
@@ -20987,13 +20888,13 @@
         <v>2088</v>
       </c>
       <c r="B861" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="C861" s="2" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="D861" s="2" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="862">
@@ -21001,13 +20902,13 @@
         <v>2088</v>
       </c>
       <c r="B862" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="D862" s="2" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="863">
@@ -21015,13 +20916,13 @@
         <v>2088</v>
       </c>
       <c r="B863" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>2354</v>
+        <v>1345</v>
       </c>
       <c r="D863" s="2" t="s">
-        <v>2355</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="864">
@@ -21032,10 +20933,10 @@
         <v>2356</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>2357</v>
+        <v>1216</v>
       </c>
       <c r="D864" s="2" t="s">
-        <v>2358</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="865">
@@ -21043,13 +20944,13 @@
         <v>2088</v>
       </c>
       <c r="B865" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>2360</v>
+        <v>1219</v>
       </c>
       <c r="D865" s="2" t="s">
-        <v>2361</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="866">
@@ -21057,13 +20958,13 @@
         <v>2088</v>
       </c>
       <c r="B866" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>2363</v>
+        <v>1089</v>
       </c>
       <c r="D866" s="2" t="s">
-        <v>2364</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="867">
@@ -21071,13 +20972,13 @@
         <v>2088</v>
       </c>
       <c r="B867" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
       <c r="C867" s="2" t="s">
-        <v>2366</v>
+        <v>1092</v>
       </c>
       <c r="D867" s="2" t="s">
-        <v>2367</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="868">
@@ -21085,13 +20986,13 @@
         <v>2088</v>
       </c>
       <c r="B868" t="s">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>1491</v>
+        <v>2019</v>
       </c>
       <c r="D868" s="2" t="s">
-        <v>1492</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="869">
@@ -21099,13 +21000,13 @@
         <v>2088</v>
       </c>
       <c r="B869" t="s">
-        <v>2369</v>
+        <v>2361</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>2370</v>
+        <v>2249</v>
       </c>
       <c r="D869" s="2" t="s">
-        <v>2371</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="870">
@@ -21113,13 +21014,13 @@
         <v>2088</v>
       </c>
       <c r="B870" t="s">
-        <v>2372</v>
+        <v>2362</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>2373</v>
+        <v>2363</v>
       </c>
       <c r="D870" s="2" t="s">
-        <v>2374</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="871">
@@ -21127,13 +21028,13 @@
         <v>2088</v>
       </c>
       <c r="B871" t="s">
-        <v>2375</v>
+        <v>2365</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>1345</v>
+        <v>2366</v>
       </c>
       <c r="D871" s="2" t="s">
-        <v>1346</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="872">
@@ -21141,13 +21042,13 @@
         <v>2088</v>
       </c>
       <c r="B872" t="s">
-        <v>2376</v>
+        <v>2368</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>1216</v>
+        <v>2369</v>
       </c>
       <c r="D872" s="2" t="s">
-        <v>1217</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="873">
@@ -21155,13 +21056,13 @@
         <v>2088</v>
       </c>
       <c r="B873" t="s">
-        <v>2377</v>
+        <v>2371</v>
       </c>
       <c r="C873" s="2" t="s">
-        <v>1219</v>
+        <v>2372</v>
       </c>
       <c r="D873" s="2" t="s">
-        <v>1220</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="874">
@@ -21169,13 +21070,13 @@
         <v>2088</v>
       </c>
       <c r="B874" t="s">
-        <v>2378</v>
+        <v>2374</v>
       </c>
       <c r="C874" s="2" t="s">
-        <v>1089</v>
+        <v>2375</v>
       </c>
       <c r="D874" s="2" t="s">
-        <v>1090</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="875">
@@ -21183,13 +21084,13 @@
         <v>2088</v>
       </c>
       <c r="B875" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C875" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D875" s="2" t="s">
         <v>2379</v>
-      </c>
-      <c r="C875" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D875" s="2" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="876">
@@ -21200,10 +21101,10 @@
         <v>2380</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>2019</v>
+        <v>2381</v>
       </c>
       <c r="D876" s="2" t="s">
-        <v>2020</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="877">
@@ -21211,13 +21112,13 @@
         <v>2088</v>
       </c>
       <c r="B877" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="C877" s="2" t="s">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="D877" s="2" t="s">
-        <v>2257</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="878">
@@ -21225,13 +21126,13 @@
         <v>2088</v>
       </c>
       <c r="B878" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="C878" s="2" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="D878" s="2" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="879">
@@ -21239,13 +21140,13 @@
         <v>2088</v>
       </c>
       <c r="B879" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="C879" s="2" t="s">
-        <v>1176</v>
+        <v>2388</v>
       </c>
       <c r="D879" s="2" t="s">
-        <v>1177</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="880">
@@ -21253,13 +21154,13 @@
         <v>2088</v>
       </c>
       <c r="B880" t="s">
-        <v>2386</v>
+        <v>2390</v>
       </c>
       <c r="C880" s="2" t="s">
-        <v>1179</v>
+        <v>2391</v>
       </c>
       <c r="D880" s="2" t="s">
-        <v>1180</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="881">
@@ -21267,13 +21168,13 @@
         <v>2088</v>
       </c>
       <c r="B881" t="s">
-        <v>2387</v>
+        <v>2393</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>1182</v>
+        <v>2394</v>
       </c>
       <c r="D881" s="2" t="s">
-        <v>1183</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="882">
@@ -21281,13 +21182,13 @@
         <v>2088</v>
       </c>
       <c r="B882" t="s">
-        <v>2388</v>
+        <v>2396</v>
       </c>
       <c r="C882" s="2" t="s">
-        <v>1185</v>
+        <v>2397</v>
       </c>
       <c r="D882" s="2" t="s">
-        <v>1186</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="883">
@@ -21295,13 +21196,13 @@
         <v>2088</v>
       </c>
       <c r="B883" t="s">
-        <v>2389</v>
+        <v>2399</v>
       </c>
       <c r="C883" s="2" t="s">
-        <v>2390</v>
+        <v>2400</v>
       </c>
       <c r="D883" s="2" t="s">
-        <v>2391</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="884">
@@ -21309,13 +21210,13 @@
         <v>2088</v>
       </c>
       <c r="B884" t="s">
-        <v>2392</v>
+        <v>2402</v>
       </c>
       <c r="C884" s="2" t="s">
-        <v>2393</v>
+        <v>2403</v>
       </c>
       <c r="D884" s="2" t="s">
-        <v>2394</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="885">
@@ -21323,13 +21224,13 @@
         <v>2088</v>
       </c>
       <c r="B885" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="C885" s="2" t="s">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="D885" s="2" t="s">
-        <v>2397</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="886">
@@ -21337,13 +21238,13 @@
         <v>2088</v>
       </c>
       <c r="B886" t="s">
-        <v>2398</v>
+        <v>2408</v>
       </c>
       <c r="C886" s="2" t="s">
-        <v>2399</v>
+        <v>2409</v>
       </c>
       <c r="D886" s="2" t="s">
-        <v>2400</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="887">
@@ -21351,13 +21252,13 @@
         <v>2088</v>
       </c>
       <c r="B887" t="s">
-        <v>2401</v>
+        <v>2411</v>
       </c>
       <c r="C887" s="2" t="s">
-        <v>2402</v>
+        <v>2412</v>
       </c>
       <c r="D887" s="2" t="s">
-        <v>2403</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="888">
@@ -21365,13 +21266,13 @@
         <v>2088</v>
       </c>
       <c r="B888" t="s">
-        <v>2404</v>
+        <v>2414</v>
       </c>
       <c r="C888" s="2" t="s">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="D888" s="2" t="s">
-        <v>2406</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="889">
@@ -21379,13 +21280,13 @@
         <v>2088</v>
       </c>
       <c r="B889" t="s">
-        <v>2407</v>
+        <v>2417</v>
       </c>
       <c r="C889" s="2" t="s">
-        <v>2408</v>
+        <v>2418</v>
       </c>
       <c r="D889" s="2" t="s">
-        <v>2409</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="890">
@@ -21393,13 +21294,13 @@
         <v>2088</v>
       </c>
       <c r="B890" t="s">
-        <v>2410</v>
+        <v>2419</v>
       </c>
       <c r="C890" s="2" t="s">
-        <v>2411</v>
+        <v>2420</v>
       </c>
       <c r="D890" s="2" t="s">
-        <v>2412</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="891">
@@ -21407,13 +21308,13 @@
         <v>2088</v>
       </c>
       <c r="B891" t="s">
-        <v>2413</v>
+        <v>2422</v>
       </c>
       <c r="C891" s="2" t="s">
-        <v>2414</v>
+        <v>2423</v>
       </c>
       <c r="D891" s="2" t="s">
-        <v>2415</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="892">
@@ -21421,13 +21322,13 @@
         <v>2088</v>
       </c>
       <c r="B892" t="s">
-        <v>2416</v>
+        <v>2425</v>
       </c>
       <c r="C892" s="2" t="s">
-        <v>2112</v>
+        <v>2426</v>
       </c>
       <c r="D892" s="2" t="s">
-        <v>2113</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="893">
@@ -21435,13 +21336,13 @@
         <v>2088</v>
       </c>
       <c r="B893" t="s">
-        <v>2417</v>
+        <v>2428</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>2418</v>
+        <v>2429</v>
       </c>
       <c r="D893" s="2" t="s">
-        <v>2419</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="894">
@@ -21449,13 +21350,13 @@
         <v>2088</v>
       </c>
       <c r="B894" t="s">
-        <v>2420</v>
+        <v>2431</v>
       </c>
       <c r="C894" s="2" t="s">
-        <v>2421</v>
+        <v>2432</v>
       </c>
       <c r="D894" s="2" t="s">
-        <v>2422</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="895">
@@ -21463,13 +21364,13 @@
         <v>2088</v>
       </c>
       <c r="B895" t="s">
-        <v>2423</v>
+        <v>2434</v>
       </c>
       <c r="C895" s="2" t="s">
-        <v>2424</v>
+        <v>2435</v>
       </c>
       <c r="D895" s="2" t="s">
-        <v>2425</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="896">
@@ -21477,13 +21378,13 @@
         <v>2088</v>
       </c>
       <c r="B896" t="s">
-        <v>2426</v>
+        <v>2437</v>
       </c>
       <c r="C896" s="2" t="s">
-        <v>2427</v>
+        <v>2438</v>
       </c>
       <c r="D896" s="2" t="s">
-        <v>2428</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="897">
@@ -21491,13 +21392,13 @@
         <v>2088</v>
       </c>
       <c r="B897" t="s">
-        <v>2429</v>
+        <v>2440</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>2430</v>
+        <v>2441</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>2431</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="898">
@@ -21505,13 +21406,13 @@
         <v>2088</v>
       </c>
       <c r="B898" t="s">
-        <v>2432</v>
+        <v>2443</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>2433</v>
+        <v>2444</v>
       </c>
       <c r="D898" s="2" t="s">
-        <v>2434</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="899">
@@ -21519,13 +21420,13 @@
         <v>2088</v>
       </c>
       <c r="B899" t="s">
-        <v>2435</v>
+        <v>2446</v>
       </c>
       <c r="C899" s="2" t="s">
-        <v>2436</v>
+        <v>2447</v>
       </c>
       <c r="D899" s="2" t="s">
-        <v>2437</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="900">
@@ -21533,13 +21434,13 @@
         <v>2088</v>
       </c>
       <c r="B900" t="s">
-        <v>2438</v>
+        <v>2449</v>
       </c>
       <c r="C900" s="2" t="s">
-        <v>2439</v>
+        <v>2450</v>
       </c>
       <c r="D900" s="2" t="s">
-        <v>2440</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="901">
@@ -21547,13 +21448,13 @@
         <v>2088</v>
       </c>
       <c r="B901" t="s">
-        <v>2441</v>
+        <v>2452</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>2442</v>
+        <v>2453</v>
       </c>
       <c r="D901" s="2" t="s">
-        <v>2443</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="902">
@@ -21561,13 +21462,13 @@
         <v>2088</v>
       </c>
       <c r="B902" t="s">
-        <v>2444</v>
+        <v>2455</v>
       </c>
       <c r="C902" s="2" t="s">
-        <v>2445</v>
+        <v>2456</v>
       </c>
       <c r="D902" s="2" t="s">
-        <v>2446</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="903">
@@ -21575,13 +21476,13 @@
         <v>2088</v>
       </c>
       <c r="B903" t="s">
-        <v>2447</v>
+        <v>2458</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>2448</v>
+        <v>2459</v>
       </c>
       <c r="D903" s="2" t="s">
-        <v>2449</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="904">
@@ -21589,13 +21490,13 @@
         <v>2088</v>
       </c>
       <c r="B904" t="s">
-        <v>2450</v>
+        <v>2461</v>
       </c>
       <c r="C904" s="2" t="s">
-        <v>2451</v>
+        <v>2462</v>
       </c>
       <c r="D904" s="2" t="s">
-        <v>1907</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="905">
@@ -21603,13 +21504,13 @@
         <v>2088</v>
       </c>
       <c r="B905" t="s">
-        <v>2452</v>
+        <v>2464</v>
       </c>
       <c r="C905" s="2" t="s">
-        <v>2453</v>
+        <v>2465</v>
       </c>
       <c r="D905" s="2" t="s">
-        <v>2454</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="906">
@@ -21617,13 +21518,13 @@
         <v>2088</v>
       </c>
       <c r="B906" t="s">
-        <v>2455</v>
+        <v>2467</v>
       </c>
       <c r="C906" s="2" t="s">
-        <v>2456</v>
+        <v>2468</v>
       </c>
       <c r="D906" s="2" t="s">
-        <v>2457</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="907">
@@ -21631,13 +21532,13 @@
         <v>2088</v>
       </c>
       <c r="B907" t="s">
-        <v>2458</v>
+        <v>2470</v>
       </c>
       <c r="C907" s="2" t="s">
-        <v>2459</v>
+        <v>2471</v>
       </c>
       <c r="D907" s="2" t="s">
-        <v>2460</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="908">
@@ -21645,13 +21546,13 @@
         <v>2088</v>
       </c>
       <c r="B908" t="s">
-        <v>2461</v>
+        <v>2473</v>
       </c>
       <c r="C908" s="2" t="s">
-        <v>2462</v>
+        <v>2474</v>
       </c>
       <c r="D908" s="2" t="s">
-        <v>2463</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="909">
@@ -21659,13 +21560,13 @@
         <v>2088</v>
       </c>
       <c r="B909" t="s">
-        <v>2464</v>
+        <v>2476</v>
       </c>
       <c r="C909" s="2" t="s">
-        <v>2465</v>
+        <v>2477</v>
       </c>
       <c r="D909" s="2" t="s">
-        <v>2466</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="910">
@@ -21673,13 +21574,13 @@
         <v>2088</v>
       </c>
       <c r="B910" t="s">
-        <v>2467</v>
+        <v>2479</v>
       </c>
       <c r="C910" s="2" t="s">
-        <v>2468</v>
+        <v>2480</v>
       </c>
       <c r="D910" s="2" t="s">
-        <v>2469</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="911">
@@ -21687,13 +21588,13 @@
         <v>2088</v>
       </c>
       <c r="B911" t="s">
-        <v>2470</v>
+        <v>2482</v>
       </c>
       <c r="C911" s="2" t="s">
-        <v>2471</v>
+        <v>2483</v>
       </c>
       <c r="D911" s="2" t="s">
-        <v>2472</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="912">
@@ -21701,13 +21602,13 @@
         <v>2088</v>
       </c>
       <c r="B912" t="s">
-        <v>2473</v>
+        <v>2485</v>
       </c>
       <c r="C912" s="2" t="s">
-        <v>2474</v>
+        <v>2486</v>
       </c>
       <c r="D912" s="2" t="s">
-        <v>2475</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="913">
@@ -21715,13 +21616,13 @@
         <v>2088</v>
       </c>
       <c r="B913" t="s">
-        <v>2476</v>
+        <v>2488</v>
       </c>
       <c r="C913" s="2" t="s">
-        <v>2477</v>
+        <v>2489</v>
       </c>
       <c r="D913" s="2" t="s">
-        <v>2478</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="914">
@@ -21729,13 +21630,13 @@
         <v>2088</v>
       </c>
       <c r="B914" t="s">
-        <v>2479</v>
+        <v>2491</v>
       </c>
       <c r="C914" s="2" t="s">
-        <v>2480</v>
+        <v>2492</v>
       </c>
       <c r="D914" s="2" t="s">
-        <v>2481</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="915">
@@ -21743,13 +21644,13 @@
         <v>2088</v>
       </c>
       <c r="B915" t="s">
-        <v>2482</v>
+        <v>2494</v>
       </c>
       <c r="C915" s="2" t="s">
-        <v>2483</v>
+        <v>622</v>
       </c>
       <c r="D915" s="2" t="s">
-        <v>2484</v>
+        <v>623</v>
       </c>
     </row>
     <row r="916">
@@ -21757,13 +21658,13 @@
         <v>2088</v>
       </c>
       <c r="B916" t="s">
-        <v>2485</v>
+        <v>2495</v>
       </c>
       <c r="C916" s="2" t="s">
-        <v>2486</v>
+        <v>2496</v>
       </c>
       <c r="D916" s="2" t="s">
-        <v>2487</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="917">
@@ -21771,13 +21672,13 @@
         <v>2088</v>
       </c>
       <c r="B917" t="s">
-        <v>2488</v>
+        <v>2498</v>
       </c>
       <c r="C917" s="2" t="s">
-        <v>2489</v>
+        <v>2499</v>
       </c>
       <c r="D917" s="2" t="s">
-        <v>2490</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="918">
@@ -21785,13 +21686,13 @@
         <v>2088</v>
       </c>
       <c r="B918" t="s">
-        <v>2491</v>
+        <v>2501</v>
       </c>
       <c r="C918" s="2" t="s">
-        <v>2492</v>
+        <v>2480</v>
       </c>
       <c r="D918" s="2" t="s">
-        <v>2493</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="919">
@@ -21799,13 +21700,13 @@
         <v>2088</v>
       </c>
       <c r="B919" t="s">
-        <v>2494</v>
+        <v>2502</v>
       </c>
       <c r="C919" s="2" t="s">
-        <v>2495</v>
+        <v>2483</v>
       </c>
       <c r="D919" s="2" t="s">
-        <v>2496</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="920">
@@ -21813,13 +21714,13 @@
         <v>2088</v>
       </c>
       <c r="B920" t="s">
-        <v>2497</v>
+        <v>2503</v>
       </c>
       <c r="C920" s="2" t="s">
-        <v>2498</v>
+        <v>2504</v>
       </c>
       <c r="D920" s="2" t="s">
-        <v>2499</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="921">
@@ -21827,13 +21728,13 @@
         <v>2088</v>
       </c>
       <c r="B921" t="s">
-        <v>2500</v>
+        <v>2506</v>
       </c>
       <c r="C921" s="2" t="s">
-        <v>2501</v>
+        <v>2507</v>
       </c>
       <c r="D921" s="2" t="s">
-        <v>2502</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="922">
@@ -21841,13 +21742,13 @@
         <v>2088</v>
       </c>
       <c r="B922" t="s">
-        <v>2503</v>
+        <v>2509</v>
       </c>
       <c r="C922" s="2" t="s">
-        <v>2504</v>
+        <v>2510</v>
       </c>
       <c r="D922" s="2" t="s">
-        <v>2505</v>
+        <v>751</v>
       </c>
     </row>
     <row r="923">
@@ -21855,13 +21756,13 @@
         <v>2088</v>
       </c>
       <c r="B923" t="s">
-        <v>2506</v>
+        <v>2511</v>
       </c>
       <c r="C923" s="2" t="s">
-        <v>2507</v>
+        <v>2512</v>
       </c>
       <c r="D923" s="2" t="s">
-        <v>2508</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="924">
@@ -21869,13 +21770,13 @@
         <v>2088</v>
       </c>
       <c r="B924" t="s">
-        <v>2509</v>
+        <v>2514</v>
       </c>
       <c r="C924" s="2" t="s">
-        <v>2510</v>
+        <v>2515</v>
       </c>
       <c r="D924" s="2" t="s">
-        <v>2511</v>
+        <v>757</v>
       </c>
     </row>
     <row r="925">
@@ -21883,13 +21784,13 @@
         <v>2088</v>
       </c>
       <c r="B925" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="C925" s="2" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="D925" s="2" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="926">
@@ -21897,13 +21798,13 @@
         <v>2088</v>
       </c>
       <c r="B926" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="C926" s="2" t="s">
-        <v>2516</v>
+        <v>1906</v>
       </c>
       <c r="D926" s="2" t="s">
-        <v>2517</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="927">
@@ -21911,13 +21812,13 @@
         <v>2088</v>
       </c>
       <c r="B927" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="C927" s="2" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="D927" s="2" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="928">
@@ -21925,223 +21826,223 @@
         <v>2088</v>
       </c>
       <c r="B928" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="C928" s="2" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="D928" s="2" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B929" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="C929" s="2" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="D929" s="2" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B930" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="C930" s="2" t="s">
-        <v>622</v>
+        <v>1231</v>
       </c>
       <c r="D930" s="2" t="s">
-        <v>623</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B931" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="C931" s="2" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="D931" s="2" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B932" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="C932" s="2" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="D932" s="2" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B933" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="C933" s="2" t="s">
-        <v>2513</v>
+        <v>2537</v>
       </c>
       <c r="D933" s="2" t="s">
-        <v>2514</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B934" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="C934" s="2" t="s">
-        <v>2516</v>
+        <v>691</v>
       </c>
       <c r="D934" s="2" t="s">
-        <v>2517</v>
+        <v>692</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B935" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="C935" s="2" t="s">
-        <v>2537</v>
+        <v>728</v>
       </c>
       <c r="D935" s="2" t="s">
-        <v>2538</v>
+        <v>729</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B936" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="C936" s="2" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="D936" s="2" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B937" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="C937" s="2" t="s">
-        <v>2543</v>
+        <v>710</v>
       </c>
       <c r="D937" s="2" t="s">
-        <v>751</v>
+        <v>711</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B938" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C938" s="2" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D938" s="2" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B939" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C939" s="2" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D939" s="2" t="s">
-        <v>757</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B940" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="C940" s="2" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="D940" s="2" t="s">
-        <v>2551</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B941" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="C941" s="2" t="s">
-        <v>1906</v>
+        <v>2554</v>
       </c>
       <c r="D941" s="2" t="s">
-        <v>1907</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B942" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="C942" s="2" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="D942" s="2" t="s">
-        <v>2555</v>
+        <v>705</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>2088</v>
+        <v>38</v>
       </c>
       <c r="B943" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="C943" s="2" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="D943" s="2" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="944">
@@ -22149,13 +22050,13 @@
         <v>38</v>
       </c>
       <c r="B944" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="C944" s="2" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="D944" s="2" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="945">
@@ -22163,13 +22064,13 @@
         <v>38</v>
       </c>
       <c r="B945" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="C945" s="2" t="s">
-        <v>1231</v>
+        <v>2564</v>
       </c>
       <c r="D945" s="2" t="s">
-        <v>1592</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="946">
@@ -22177,13 +22078,13 @@
         <v>38</v>
       </c>
       <c r="B946" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="C946" s="2" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="D946" s="2" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="947">
@@ -22191,13 +22092,13 @@
         <v>38</v>
       </c>
       <c r="B947" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="C947" s="2" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="D947" s="2" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="948">
@@ -22205,13 +22106,13 @@
         <v>38</v>
       </c>
       <c r="B948" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="C948" s="2" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="D948" s="2" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="949">
@@ -22219,13 +22120,13 @@
         <v>38</v>
       </c>
       <c r="B949" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="C949" s="2" t="s">
-        <v>691</v>
+        <v>2576</v>
       </c>
       <c r="D949" s="2" t="s">
-        <v>692</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="950">
@@ -22233,13 +22134,13 @@
         <v>38</v>
       </c>
       <c r="B950" t="s">
-        <v>2573</v>
+        <v>2578</v>
       </c>
       <c r="C950" s="2" t="s">
-        <v>728</v>
+        <v>2579</v>
       </c>
       <c r="D950" s="2" t="s">
-        <v>729</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="951">
@@ -22247,13 +22148,13 @@
         <v>38</v>
       </c>
       <c r="B951" t="s">
-        <v>2574</v>
+        <v>2581</v>
       </c>
       <c r="C951" s="2" t="s">
-        <v>2575</v>
+        <v>2582</v>
       </c>
       <c r="D951" s="2" t="s">
-        <v>2576</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="952">
@@ -22261,13 +22162,13 @@
         <v>38</v>
       </c>
       <c r="B952" t="s">
-        <v>2577</v>
+        <v>2584</v>
       </c>
       <c r="C952" s="2" t="s">
-        <v>710</v>
+        <v>139</v>
       </c>
       <c r="D952" s="2" t="s">
-        <v>711</v>
+        <v>140</v>
       </c>
     </row>
     <row r="953">
@@ -22275,13 +22176,13 @@
         <v>38</v>
       </c>
       <c r="B953" t="s">
-        <v>2578</v>
+        <v>2585</v>
       </c>
       <c r="C953" s="2" t="s">
-        <v>2579</v>
+        <v>2586</v>
       </c>
       <c r="D953" s="2" t="s">
-        <v>2580</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="954">
@@ -22289,13 +22190,13 @@
         <v>38</v>
       </c>
       <c r="B954" t="s">
-        <v>2581</v>
+        <v>2588</v>
       </c>
       <c r="C954" s="2" t="s">
-        <v>2582</v>
+        <v>2589</v>
       </c>
       <c r="D954" s="2" t="s">
-        <v>2583</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="955">
@@ -22303,13 +22204,13 @@
         <v>38</v>
       </c>
       <c r="B955" t="s">
-        <v>2584</v>
+        <v>2591</v>
       </c>
       <c r="C955" s="2" t="s">
-        <v>2585</v>
+        <v>2592</v>
       </c>
       <c r="D955" s="2" t="s">
-        <v>1672</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="956">
@@ -22317,13 +22218,13 @@
         <v>38</v>
       </c>
       <c r="B956" t="s">
-        <v>2586</v>
+        <v>2594</v>
       </c>
       <c r="C956" s="2" t="s">
-        <v>2587</v>
+        <v>2595</v>
       </c>
       <c r="D956" s="2" t="s">
-        <v>1675</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="957">
@@ -22331,13 +22232,13 @@
         <v>38</v>
       </c>
       <c r="B957" t="s">
-        <v>2588</v>
+        <v>2597</v>
       </c>
       <c r="C957" s="2" t="s">
-        <v>2589</v>
+        <v>2598</v>
       </c>
       <c r="D957" s="2" t="s">
-        <v>705</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="958">
@@ -22345,13 +22246,13 @@
         <v>38</v>
       </c>
       <c r="B958" t="s">
-        <v>2590</v>
+        <v>2600</v>
       </c>
       <c r="C958" s="2" t="s">
-        <v>2591</v>
+        <v>2601</v>
       </c>
       <c r="D958" s="2" t="s">
-        <v>2592</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="959">
@@ -22359,13 +22260,13 @@
         <v>38</v>
       </c>
       <c r="B959" t="s">
-        <v>2593</v>
+        <v>2603</v>
       </c>
       <c r="C959" s="2" t="s">
-        <v>2594</v>
+        <v>2604</v>
       </c>
       <c r="D959" s="2" t="s">
-        <v>2595</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="960">
@@ -22373,13 +22274,13 @@
         <v>38</v>
       </c>
       <c r="B960" t="s">
-        <v>2596</v>
+        <v>2606</v>
       </c>
       <c r="C960" s="2" t="s">
-        <v>2597</v>
+        <v>710</v>
       </c>
       <c r="D960" s="2" t="s">
-        <v>2598</v>
+        <v>711</v>
       </c>
     </row>
     <row r="961">
@@ -22387,13 +22288,13 @@
         <v>38</v>
       </c>
       <c r="B961" t="s">
-        <v>2599</v>
+        <v>2607</v>
       </c>
       <c r="C961" s="2" t="s">
-        <v>2600</v>
+        <v>2608</v>
       </c>
       <c r="D961" s="2" t="s">
-        <v>2601</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="962">
@@ -22401,13 +22302,13 @@
         <v>38</v>
       </c>
       <c r="B962" t="s">
-        <v>2602</v>
+        <v>2610</v>
       </c>
       <c r="C962" s="2" t="s">
-        <v>2603</v>
+        <v>2611</v>
       </c>
       <c r="D962" s="2" t="s">
-        <v>2604</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="963">
@@ -22415,13 +22316,13 @@
         <v>38</v>
       </c>
       <c r="B963" t="s">
-        <v>2605</v>
+        <v>2613</v>
       </c>
       <c r="C963" s="2" t="s">
-        <v>2606</v>
+        <v>2614</v>
       </c>
       <c r="D963" s="2" t="s">
-        <v>2607</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="964">
@@ -22429,13 +22330,13 @@
         <v>38</v>
       </c>
       <c r="B964" t="s">
-        <v>2608</v>
+        <v>2616</v>
       </c>
       <c r="C964" s="2" t="s">
-        <v>2609</v>
+        <v>2617</v>
       </c>
       <c r="D964" s="2" t="s">
-        <v>2610</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="965">
@@ -22443,13 +22344,13 @@
         <v>38</v>
       </c>
       <c r="B965" t="s">
-        <v>2611</v>
+        <v>2619</v>
       </c>
       <c r="C965" s="2" t="s">
-        <v>2612</v>
+        <v>2620</v>
       </c>
       <c r="D965" s="2" t="s">
-        <v>2613</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="966">
@@ -22457,13 +22358,13 @@
         <v>38</v>
       </c>
       <c r="B966" t="s">
-        <v>2614</v>
+        <v>2622</v>
       </c>
       <c r="C966" s="2" t="s">
-        <v>2615</v>
+        <v>2623</v>
       </c>
       <c r="D966" s="2" t="s">
-        <v>2616</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="967">
@@ -22471,13 +22372,13 @@
         <v>38</v>
       </c>
       <c r="B967" t="s">
-        <v>2617</v>
+        <v>2625</v>
       </c>
       <c r="C967" s="2" t="s">
-        <v>139</v>
+        <v>2626</v>
       </c>
       <c r="D967" s="2" t="s">
-        <v>140</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="968">
@@ -22485,13 +22386,13 @@
         <v>38</v>
       </c>
       <c r="B968" t="s">
-        <v>2618</v>
+        <v>2628</v>
       </c>
       <c r="C968" s="2" t="s">
-        <v>2619</v>
+        <v>2629</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>2620</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="969">
@@ -22499,13 +22400,13 @@
         <v>38</v>
       </c>
       <c r="B969" t="s">
-        <v>2621</v>
+        <v>2631</v>
       </c>
       <c r="C969" s="2" t="s">
-        <v>2622</v>
+        <v>2632</v>
       </c>
       <c r="D969" s="2" t="s">
-        <v>2623</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="970">
@@ -22513,13 +22414,13 @@
         <v>38</v>
       </c>
       <c r="B970" t="s">
-        <v>2624</v>
+        <v>2634</v>
       </c>
       <c r="C970" s="2" t="s">
-        <v>2625</v>
+        <v>2635</v>
       </c>
       <c r="D970" s="2" t="s">
-        <v>2626</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="971">
@@ -22527,13 +22428,13 @@
         <v>38</v>
       </c>
       <c r="B971" t="s">
-        <v>2627</v>
+        <v>2637</v>
       </c>
       <c r="C971" s="2" t="s">
-        <v>2628</v>
+        <v>2638</v>
       </c>
       <c r="D971" s="2" t="s">
-        <v>2629</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="972">
@@ -22541,13 +22442,13 @@
         <v>38</v>
       </c>
       <c r="B972" t="s">
-        <v>2630</v>
+        <v>2640</v>
       </c>
       <c r="C972" s="2" t="s">
-        <v>2631</v>
+        <v>2641</v>
       </c>
       <c r="D972" s="2" t="s">
-        <v>2632</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="973">
@@ -22555,13 +22456,13 @@
         <v>38</v>
       </c>
       <c r="B973" t="s">
-        <v>2633</v>
+        <v>2643</v>
       </c>
       <c r="C973" s="2" t="s">
-        <v>2634</v>
+        <v>2644</v>
       </c>
       <c r="D973" s="2" t="s">
-        <v>2635</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="974">
@@ -22569,13 +22470,13 @@
         <v>38</v>
       </c>
       <c r="B974" t="s">
-        <v>2636</v>
+        <v>2646</v>
       </c>
       <c r="C974" s="2" t="s">
-        <v>2637</v>
+        <v>2647</v>
       </c>
       <c r="D974" s="2" t="s">
-        <v>2638</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="975">
@@ -22583,223 +22484,223 @@
         <v>38</v>
       </c>
       <c r="B975" t="s">
-        <v>2639</v>
+        <v>2649</v>
       </c>
       <c r="C975" s="2" t="s">
-        <v>710</v>
+        <v>2650</v>
       </c>
       <c r="D975" s="2" t="s">
-        <v>711</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B976" t="s">
-        <v>2640</v>
+        <v>2652</v>
       </c>
       <c r="C976" s="2" t="s">
-        <v>2641</v>
+        <v>2653</v>
       </c>
       <c r="D976" s="2" t="s">
-        <v>2642</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B977" t="s">
-        <v>2643</v>
+        <v>2655</v>
       </c>
       <c r="C977" s="2" t="s">
-        <v>2644</v>
+        <v>2656</v>
       </c>
       <c r="D977" s="2" t="s">
-        <v>2645</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B978" t="s">
-        <v>2646</v>
+        <v>2658</v>
       </c>
       <c r="C978" s="2" t="s">
-        <v>2647</v>
+        <v>2659</v>
       </c>
       <c r="D978" s="2" t="s">
-        <v>2648</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B979" t="s">
-        <v>2649</v>
+        <v>2661</v>
       </c>
       <c r="C979" s="2" t="s">
-        <v>2650</v>
+        <v>2662</v>
       </c>
       <c r="D979" s="2" t="s">
-        <v>2651</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B980" t="s">
-        <v>2652</v>
+        <v>2664</v>
       </c>
       <c r="C980" s="2" t="s">
-        <v>2653</v>
+        <v>192</v>
       </c>
       <c r="D980" s="2" t="s">
-        <v>2654</v>
+        <v>193</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B981" t="s">
-        <v>2655</v>
+        <v>2665</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>2656</v>
+        <v>2666</v>
       </c>
       <c r="D981" s="2" t="s">
-        <v>2657</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B982" t="s">
-        <v>2658</v>
+        <v>2668</v>
       </c>
       <c r="C982" s="2" t="s">
-        <v>2659</v>
+        <v>2669</v>
       </c>
       <c r="D982" s="2" t="s">
-        <v>2660</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B983" t="s">
-        <v>2661</v>
+        <v>2671</v>
       </c>
       <c r="C983" s="2" t="s">
-        <v>2662</v>
+        <v>2672</v>
       </c>
       <c r="D983" s="2" t="s">
-        <v>2663</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B984" t="s">
-        <v>2664</v>
+        <v>2674</v>
       </c>
       <c r="C984" s="2" t="s">
-        <v>2665</v>
+        <v>2675</v>
       </c>
       <c r="D984" s="2" t="s">
-        <v>2666</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B985" t="s">
-        <v>2667</v>
+        <v>2677</v>
       </c>
       <c r="C985" s="2" t="s">
-        <v>2668</v>
+        <v>2678</v>
       </c>
       <c r="D985" s="2" t="s">
-        <v>2669</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B986" t="s">
-        <v>2670</v>
+        <v>2680</v>
       </c>
       <c r="C986" s="2" t="s">
-        <v>2671</v>
+        <v>2681</v>
       </c>
       <c r="D986" s="2" t="s">
-        <v>2672</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B987" t="s">
-        <v>2673</v>
+        <v>2683</v>
       </c>
       <c r="C987" s="2" t="s">
-        <v>2674</v>
+        <v>2684</v>
       </c>
       <c r="D987" s="2" t="s">
-        <v>2675</v>
+        <v>77</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B988" t="s">
-        <v>2676</v>
+        <v>2685</v>
       </c>
       <c r="C988" s="2" t="s">
-        <v>2677</v>
+        <v>2686</v>
       </c>
       <c r="D988" s="2" t="s">
-        <v>2678</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B989" t="s">
-        <v>2679</v>
+        <v>2688</v>
       </c>
       <c r="C989" s="2" t="s">
-        <v>2680</v>
+        <v>2689</v>
       </c>
       <c r="D989" s="2" t="s">
-        <v>2681</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B990" t="s">
-        <v>2682</v>
+        <v>2691</v>
       </c>
       <c r="C990" s="2" t="s">
-        <v>2683</v>
+        <v>2692</v>
       </c>
       <c r="D990" s="2" t="s">
-        <v>2684</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="991">
@@ -22807,13 +22708,13 @@
         <v>41</v>
       </c>
       <c r="B991" t="s">
-        <v>2685</v>
+        <v>2694</v>
       </c>
       <c r="C991" s="2" t="s">
-        <v>2686</v>
+        <v>2695</v>
       </c>
       <c r="D991" s="2" t="s">
-        <v>2687</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="992">
@@ -22821,13 +22722,13 @@
         <v>41</v>
       </c>
       <c r="B992" t="s">
-        <v>2688</v>
+        <v>2696</v>
       </c>
       <c r="C992" s="2" t="s">
-        <v>2689</v>
+        <v>2697</v>
       </c>
       <c r="D992" s="2" t="s">
-        <v>2690</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="993">
@@ -22835,13 +22736,13 @@
         <v>41</v>
       </c>
       <c r="B993" t="s">
-        <v>2691</v>
+        <v>2699</v>
       </c>
       <c r="C993" s="2" t="s">
-        <v>2692</v>
+        <v>2700</v>
       </c>
       <c r="D993" s="2" t="s">
-        <v>2693</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="994">
@@ -22849,13 +22750,13 @@
         <v>41</v>
       </c>
       <c r="B994" t="s">
-        <v>2694</v>
+        <v>2702</v>
       </c>
       <c r="C994" s="2" t="s">
-        <v>2695</v>
+        <v>2703</v>
       </c>
       <c r="D994" s="2" t="s">
-        <v>2696</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="995">
@@ -22863,13 +22764,13 @@
         <v>41</v>
       </c>
       <c r="B995" t="s">
-        <v>2697</v>
+        <v>2705</v>
       </c>
       <c r="C995" s="2" t="s">
-        <v>192</v>
+        <v>2706</v>
       </c>
       <c r="D995" s="2" t="s">
-        <v>193</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="996">
@@ -22877,13 +22778,13 @@
         <v>41</v>
       </c>
       <c r="B996" t="s">
-        <v>2698</v>
+        <v>2708</v>
       </c>
       <c r="C996" s="2" t="s">
-        <v>2699</v>
+        <v>1086</v>
       </c>
       <c r="D996" s="2" t="s">
-        <v>2700</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="997">
@@ -22891,13 +22792,13 @@
         <v>41</v>
       </c>
       <c r="B997" t="s">
-        <v>2701</v>
+        <v>2709</v>
       </c>
       <c r="C997" s="2" t="s">
-        <v>2702</v>
+        <v>419</v>
       </c>
       <c r="D997" s="2" t="s">
-        <v>2703</v>
+        <v>420</v>
       </c>
     </row>
     <row r="998">
@@ -22905,13 +22806,13 @@
         <v>41</v>
       </c>
       <c r="B998" t="s">
-        <v>2704</v>
+        <v>2710</v>
       </c>
       <c r="C998" s="2" t="s">
-        <v>2705</v>
+        <v>2711</v>
       </c>
       <c r="D998" s="2" t="s">
-        <v>2706</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="999">
@@ -22919,13 +22820,13 @@
         <v>41</v>
       </c>
       <c r="B999" t="s">
-        <v>2707</v>
+        <v>2713</v>
       </c>
       <c r="C999" s="2" t="s">
-        <v>2708</v>
+        <v>1105</v>
       </c>
       <c r="D999" s="2" t="s">
-        <v>2709</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1000">
@@ -22933,13 +22834,13 @@
         <v>41</v>
       </c>
       <c r="B1000" t="s">
-        <v>2710</v>
+        <v>2714</v>
       </c>
       <c r="C1000" s="2" t="s">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="D1000" s="2" t="s">
-        <v>2712</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1001">
@@ -22947,13 +22848,13 @@
         <v>41</v>
       </c>
       <c r="B1001" t="s">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="C1001" s="2" t="s">
-        <v>2714</v>
+        <v>2718</v>
       </c>
       <c r="D1001" s="2" t="s">
-        <v>2715</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="1002">
@@ -22961,13 +22862,13 @@
         <v>41</v>
       </c>
       <c r="B1002" t="s">
-        <v>2716</v>
+        <v>2720</v>
       </c>
       <c r="C1002" s="2" t="s">
-        <v>2717</v>
+        <v>2721</v>
       </c>
       <c r="D1002" s="2" t="s">
-        <v>77</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="1003">
@@ -22975,13 +22876,13 @@
         <v>41</v>
       </c>
       <c r="B1003" t="s">
-        <v>2718</v>
+        <v>2723</v>
       </c>
       <c r="C1003" s="2" t="s">
-        <v>2719</v>
+        <v>2724</v>
       </c>
       <c r="D1003" s="2" t="s">
-        <v>2720</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1004">
@@ -22989,13 +22890,13 @@
         <v>41</v>
       </c>
       <c r="B1004" t="s">
-        <v>2721</v>
+        <v>2726</v>
       </c>
       <c r="C1004" s="2" t="s">
-        <v>2722</v>
+        <v>2727</v>
       </c>
       <c r="D1004" s="2" t="s">
-        <v>2723</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="1005">
@@ -23003,13 +22904,13 @@
         <v>41</v>
       </c>
       <c r="B1005" t="s">
-        <v>2724</v>
+        <v>2729</v>
       </c>
       <c r="C1005" s="2" t="s">
-        <v>2725</v>
+        <v>2730</v>
       </c>
       <c r="D1005" s="2" t="s">
-        <v>2726</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="1006">
@@ -23017,13 +22918,13 @@
         <v>41</v>
       </c>
       <c r="B1006" t="s">
-        <v>2727</v>
+        <v>2732</v>
       </c>
       <c r="C1006" s="2" t="s">
-        <v>2728</v>
+        <v>2733</v>
       </c>
       <c r="D1006" s="2" t="s">
-        <v>2726</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="1007">
@@ -23031,13 +22932,13 @@
         <v>41</v>
       </c>
       <c r="B1007" t="s">
-        <v>2729</v>
+        <v>2735</v>
       </c>
       <c r="C1007" s="2" t="s">
-        <v>2730</v>
+        <v>2736</v>
       </c>
       <c r="D1007" s="2" t="s">
-        <v>2731</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="1008">
@@ -23045,13 +22946,13 @@
         <v>41</v>
       </c>
       <c r="B1008" t="s">
-        <v>2732</v>
+        <v>2738</v>
       </c>
       <c r="C1008" s="2" t="s">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="D1008" s="2" t="s">
-        <v>2734</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="1009">
@@ -23059,13 +22960,13 @@
         <v>41</v>
       </c>
       <c r="B1009" t="s">
-        <v>2735</v>
+        <v>2741</v>
       </c>
       <c r="C1009" s="2" t="s">
-        <v>2736</v>
+        <v>2742</v>
       </c>
       <c r="D1009" s="2" t="s">
-        <v>2737</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="1010">
@@ -23073,13 +22974,13 @@
         <v>41</v>
       </c>
       <c r="B1010" t="s">
-        <v>2738</v>
+        <v>2744</v>
       </c>
       <c r="C1010" s="2" t="s">
-        <v>2739</v>
+        <v>2745</v>
       </c>
       <c r="D1010" s="2" t="s">
-        <v>2740</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="1011">
@@ -23087,13 +22988,13 @@
         <v>41</v>
       </c>
       <c r="B1011" t="s">
-        <v>2741</v>
+        <v>2747</v>
       </c>
       <c r="C1011" s="2" t="s">
-        <v>1086</v>
+        <v>2748</v>
       </c>
       <c r="D1011" s="2" t="s">
-        <v>1087</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="1012">
@@ -23101,13 +23002,13 @@
         <v>41</v>
       </c>
       <c r="B1012" t="s">
-        <v>2742</v>
+        <v>2750</v>
       </c>
       <c r="C1012" s="2" t="s">
-        <v>419</v>
+        <v>2751</v>
       </c>
       <c r="D1012" s="2" t="s">
-        <v>420</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="1013">
@@ -23115,13 +23016,13 @@
         <v>41</v>
       </c>
       <c r="B1013" t="s">
-        <v>2743</v>
+        <v>2753</v>
       </c>
       <c r="C1013" s="2" t="s">
-        <v>2744</v>
+        <v>2754</v>
       </c>
       <c r="D1013" s="2" t="s">
-        <v>2745</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="1014">
@@ -23129,13 +23030,13 @@
         <v>41</v>
       </c>
       <c r="B1014" t="s">
-        <v>2746</v>
+        <v>2756</v>
       </c>
       <c r="C1014" s="2" t="s">
-        <v>1105</v>
+        <v>2656</v>
       </c>
       <c r="D1014" s="2" t="s">
-        <v>1106</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="1015">
@@ -23143,13 +23044,13 @@
         <v>41</v>
       </c>
       <c r="B1015" t="s">
-        <v>2747</v>
+        <v>2757</v>
       </c>
       <c r="C1015" s="2" t="s">
-        <v>2748</v>
+        <v>419</v>
       </c>
       <c r="D1015" s="2" t="s">
-        <v>2749</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1016">
@@ -23157,13 +23058,13 @@
         <v>41</v>
       </c>
       <c r="B1016" t="s">
-        <v>2750</v>
+        <v>2758</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>2751</v>
+        <v>2759</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>2752</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="1017">
@@ -23171,13 +23072,13 @@
         <v>41</v>
       </c>
       <c r="B1017" t="s">
-        <v>2753</v>
+        <v>2761</v>
       </c>
       <c r="C1017" s="2" t="s">
-        <v>2754</v>
+        <v>2762</v>
       </c>
       <c r="D1017" s="2" t="s">
-        <v>2755</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="1018">
@@ -23185,13 +23086,13 @@
         <v>41</v>
       </c>
       <c r="B1018" t="s">
-        <v>2756</v>
+        <v>2764</v>
       </c>
       <c r="C1018" s="2" t="s">
-        <v>2757</v>
+        <v>2765</v>
       </c>
       <c r="D1018" s="2" t="s">
-        <v>2758</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="1019">
@@ -23199,13 +23100,13 @@
         <v>41</v>
       </c>
       <c r="B1019" t="s">
-        <v>2759</v>
+        <v>2767</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>2760</v>
+        <v>2768</v>
       </c>
       <c r="D1019" s="2" t="s">
-        <v>2761</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="1020">
@@ -23213,13 +23114,13 @@
         <v>41</v>
       </c>
       <c r="B1020" t="s">
-        <v>2762</v>
+        <v>2770</v>
       </c>
       <c r="C1020" s="2" t="s">
-        <v>2763</v>
+        <v>431</v>
       </c>
       <c r="D1020" s="2" t="s">
-        <v>2764</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1021">
@@ -23227,13 +23128,13 @@
         <v>41</v>
       </c>
       <c r="B1021" t="s">
-        <v>2765</v>
+        <v>2771</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>2766</v>
+        <v>257</v>
       </c>
       <c r="D1021" s="2" t="s">
-        <v>2767</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1022">
@@ -23241,13 +23142,13 @@
         <v>41</v>
       </c>
       <c r="B1022" t="s">
-        <v>2768</v>
+        <v>2772</v>
       </c>
       <c r="C1022" s="2" t="s">
-        <v>2769</v>
+        <v>2773</v>
       </c>
       <c r="D1022" s="2" t="s">
-        <v>2770</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="1023">
@@ -23255,13 +23156,13 @@
         <v>41</v>
       </c>
       <c r="B1023" t="s">
-        <v>2771</v>
+        <v>2775</v>
       </c>
       <c r="C1023" s="2" t="s">
-        <v>2772</v>
+        <v>2776</v>
       </c>
       <c r="D1023" s="2" t="s">
-        <v>2773</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="1024">
@@ -23269,13 +23170,13 @@
         <v>41</v>
       </c>
       <c r="B1024" t="s">
-        <v>2774</v>
+        <v>2778</v>
       </c>
       <c r="C1024" s="2" t="s">
-        <v>2775</v>
+        <v>2779</v>
       </c>
       <c r="D1024" s="2" t="s">
-        <v>2776</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="1025">
@@ -23283,13 +23184,13 @@
         <v>41</v>
       </c>
       <c r="B1025" t="s">
-        <v>2777</v>
+        <v>2781</v>
       </c>
       <c r="C1025" s="2" t="s">
-        <v>2778</v>
+        <v>2724</v>
       </c>
       <c r="D1025" s="2" t="s">
-        <v>2779</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1026">
@@ -23297,13 +23198,13 @@
         <v>41</v>
       </c>
       <c r="B1026" t="s">
-        <v>2780</v>
+        <v>2782</v>
       </c>
       <c r="C1026" s="2" t="s">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="D1026" s="2" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="1027">
@@ -23311,13 +23212,13 @@
         <v>41</v>
       </c>
       <c r="B1027" t="s">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="C1027" s="2" t="s">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="D1027" s="2" t="s">
-        <v>2785</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="1028">
@@ -23325,13 +23226,13 @@
         <v>41</v>
       </c>
       <c r="B1028" t="s">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="C1028" s="2" t="s">
-        <v>2787</v>
+        <v>2789</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>2788</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="1029">
@@ -23339,13 +23240,13 @@
         <v>41</v>
       </c>
       <c r="B1029" t="s">
-        <v>2789</v>
+        <v>2791</v>
       </c>
       <c r="C1029" s="2" t="s">
-        <v>2689</v>
+        <v>2792</v>
       </c>
       <c r="D1029" s="2" t="s">
-        <v>2690</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="1030">
@@ -23353,13 +23254,13 @@
         <v>41</v>
       </c>
       <c r="B1030" t="s">
-        <v>2790</v>
+        <v>2794</v>
       </c>
       <c r="C1030" s="2" t="s">
-        <v>419</v>
+        <v>2303</v>
       </c>
       <c r="D1030" s="2" t="s">
-        <v>420</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="1031">
@@ -23367,13 +23268,13 @@
         <v>41</v>
       </c>
       <c r="B1031" t="s">
-        <v>2791</v>
+        <v>2795</v>
       </c>
       <c r="C1031" s="2" t="s">
-        <v>2792</v>
+        <v>2796</v>
       </c>
       <c r="D1031" s="2" t="s">
-        <v>2793</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="1032">
@@ -23381,13 +23282,13 @@
         <v>41</v>
       </c>
       <c r="B1032" t="s">
-        <v>2794</v>
+        <v>2798</v>
       </c>
       <c r="C1032" s="2" t="s">
-        <v>2795</v>
+        <v>2799</v>
       </c>
       <c r="D1032" s="2" t="s">
-        <v>2796</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1033">
@@ -23395,13 +23296,13 @@
         <v>41</v>
       </c>
       <c r="B1033" t="s">
-        <v>2797</v>
+        <v>2801</v>
       </c>
       <c r="C1033" s="2" t="s">
-        <v>2798</v>
+        <v>2802</v>
       </c>
       <c r="D1033" s="2" t="s">
-        <v>2799</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="1034">
@@ -23409,13 +23310,13 @@
         <v>41</v>
       </c>
       <c r="B1034" t="s">
-        <v>2800</v>
+        <v>2804</v>
       </c>
       <c r="C1034" s="2" t="s">
-        <v>2801</v>
+        <v>2805</v>
       </c>
       <c r="D1034" s="2" t="s">
-        <v>2802</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="1035">
@@ -23423,587 +23324,377 @@
         <v>41</v>
       </c>
       <c r="B1035" t="s">
-        <v>2803</v>
+        <v>2807</v>
       </c>
       <c r="C1035" s="2" t="s">
-        <v>431</v>
+        <v>2808</v>
       </c>
       <c r="D1035" s="2" t="s">
-        <v>432</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1036" t="s">
-        <v>2804</v>
+        <v>2811</v>
       </c>
       <c r="C1036" s="2" t="s">
-        <v>257</v>
+        <v>2812</v>
       </c>
       <c r="D1036" s="2" t="s">
-        <v>258</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1037" t="s">
-        <v>2805</v>
+        <v>2814</v>
       </c>
       <c r="C1037" s="2" t="s">
-        <v>2806</v>
+        <v>419</v>
       </c>
       <c r="D1037" s="2" t="s">
-        <v>2807</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1038" t="s">
-        <v>2808</v>
+        <v>2815</v>
       </c>
       <c r="C1038" s="2" t="s">
-        <v>2809</v>
+        <v>878</v>
       </c>
       <c r="D1038" s="2" t="s">
-        <v>2810</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1039" t="s">
-        <v>2811</v>
+        <v>2817</v>
       </c>
       <c r="C1039" s="2" t="s">
-        <v>2812</v>
+        <v>2818</v>
       </c>
       <c r="D1039" s="2" t="s">
-        <v>2813</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1040" t="s">
-        <v>2814</v>
+        <v>2820</v>
       </c>
       <c r="C1040" s="2" t="s">
-        <v>2757</v>
+        <v>2821</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>2758</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1041" t="s">
-        <v>2815</v>
+        <v>2823</v>
       </c>
       <c r="C1041" s="2" t="s">
-        <v>2816</v>
+        <v>2824</v>
       </c>
       <c r="D1041" s="2" t="s">
-        <v>2817</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1042" t="s">
-        <v>2818</v>
+        <v>2826</v>
       </c>
       <c r="C1042" s="2" t="s">
-        <v>2819</v>
+        <v>2827</v>
       </c>
       <c r="D1042" s="2" t="s">
-        <v>2820</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1043" t="s">
-        <v>2821</v>
+        <v>2829</v>
       </c>
       <c r="C1043" s="2" t="s">
-        <v>2822</v>
+        <v>2830</v>
       </c>
       <c r="D1043" s="2" t="s">
-        <v>2823</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1044" t="s">
-        <v>2824</v>
+        <v>2832</v>
       </c>
       <c r="C1044" s="2" t="s">
-        <v>2825</v>
+        <v>2833</v>
       </c>
       <c r="D1044" s="2" t="s">
-        <v>2826</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1045" t="s">
-        <v>2827</v>
+        <v>2835</v>
       </c>
       <c r="C1045" s="2" t="s">
-        <v>2323</v>
+        <v>2836</v>
       </c>
       <c r="D1045" s="2" t="s">
-        <v>2324</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1046" t="s">
-        <v>2828</v>
+        <v>2838</v>
       </c>
       <c r="C1046" s="2" t="s">
-        <v>2829</v>
+        <v>2839</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>2830</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1047" t="s">
-        <v>2831</v>
+        <v>2841</v>
       </c>
       <c r="C1047" s="2" t="s">
-        <v>2832</v>
+        <v>2842</v>
       </c>
       <c r="D1047" s="2" t="s">
-        <v>2833</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1048" t="s">
-        <v>2834</v>
+        <v>2844</v>
       </c>
       <c r="C1048" s="2" t="s">
-        <v>2835</v>
+        <v>2845</v>
       </c>
       <c r="D1048" s="2" t="s">
-        <v>2836</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1049" t="s">
-        <v>2837</v>
+        <v>2847</v>
       </c>
       <c r="C1049" s="2" t="s">
-        <v>2838</v>
+        <v>2848</v>
       </c>
       <c r="D1049" s="2" t="s">
-        <v>2839</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="s">
-        <v>41</v>
+        <v>2810</v>
       </c>
       <c r="B1050" t="s">
-        <v>2840</v>
+        <v>2850</v>
       </c>
       <c r="C1050" s="2" t="s">
-        <v>2841</v>
+        <v>2851</v>
       </c>
       <c r="D1050" s="2" t="s">
-        <v>2842</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="s">
-        <v>2843</v>
+        <v>2810</v>
       </c>
       <c r="B1051" t="s">
-        <v>2844</v>
+        <v>2853</v>
       </c>
       <c r="C1051" s="2" t="s">
-        <v>2845</v>
+        <v>2854</v>
       </c>
       <c r="D1051" s="2" t="s">
-        <v>2846</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1052" t="s">
-        <v>2847</v>
+        <v>2857</v>
       </c>
       <c r="C1052" s="2" t="s">
-        <v>419</v>
+        <v>2858</v>
       </c>
       <c r="D1052" s="2" t="s">
-        <v>420</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1053" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="C1053" s="2" t="s">
-        <v>878</v>
+        <v>2861</v>
       </c>
       <c r="D1053" s="2" t="s">
-        <v>2849</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1054" t="s">
-        <v>2850</v>
+        <v>2863</v>
       </c>
       <c r="C1054" s="2" t="s">
-        <v>2851</v>
+        <v>2864</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>2852</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1055" t="s">
-        <v>2853</v>
+        <v>2866</v>
       </c>
       <c r="C1055" s="2" t="s">
-        <v>2854</v>
+        <v>2867</v>
       </c>
       <c r="D1055" s="2" t="s">
-        <v>2855</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1056" t="s">
-        <v>2856</v>
+        <v>2869</v>
       </c>
       <c r="C1056" s="2" t="s">
-        <v>2857</v>
+        <v>2870</v>
       </c>
       <c r="D1056" s="2" t="s">
-        <v>2858</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1057" t="s">
-        <v>2859</v>
+        <v>2872</v>
       </c>
       <c r="C1057" s="2" t="s">
-        <v>2860</v>
+        <v>2873</v>
       </c>
       <c r="D1057" s="2" t="s">
-        <v>2861</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1058" t="s">
-        <v>2862</v>
+        <v>2875</v>
       </c>
       <c r="C1058" s="2" t="s">
-        <v>2863</v>
+        <v>2876</v>
       </c>
       <c r="D1058" s="2" t="s">
-        <v>2864</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1059" t="s">
-        <v>2865</v>
+        <v>2878</v>
       </c>
       <c r="C1059" s="2" t="s">
-        <v>2866</v>
+        <v>2879</v>
       </c>
       <c r="D1059" s="2" t="s">
-        <v>2867</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1060" t="s">
-        <v>2868</v>
+        <v>2881</v>
       </c>
       <c r="C1060" s="2" t="s">
-        <v>2869</v>
+        <v>2882</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>2870</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="s">
-        <v>2843</v>
+        <v>2856</v>
       </c>
       <c r="B1061" t="s">
-        <v>2871</v>
+        <v>2884</v>
       </c>
       <c r="C1061" s="2" t="s">
-        <v>2872</v>
+        <v>2885</v>
       </c>
       <c r="D1061" s="2" t="s">
-        <v>2873</v>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>2874</v>
-      </c>
-      <c r="C1062" s="2" t="s">
-        <v>2875</v>
-      </c>
-      <c r="D1062" s="2" t="s">
-        <v>2876</v>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>2877</v>
-      </c>
-      <c r="C1063" s="2" t="s">
-        <v>2878</v>
-      </c>
-      <c r="D1063" s="2" t="s">
-        <v>2879</v>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>2880</v>
-      </c>
-      <c r="C1064" s="2" t="s">
-        <v>2881</v>
-      </c>
-      <c r="D1064" s="2" t="s">
-        <v>2882</v>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>2883</v>
-      </c>
-      <c r="C1065" s="2" t="s">
-        <v>2884</v>
-      </c>
-      <c r="D1065" s="2" t="s">
-        <v>2885</v>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B1066" t="s">
         <v>2886</v>
-      </c>
-      <c r="C1066" s="2" t="s">
-        <v>2887</v>
-      </c>
-      <c r="D1066" s="2" t="s">
-        <v>2888</v>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>2890</v>
-      </c>
-      <c r="C1067" s="2" t="s">
-        <v>2891</v>
-      </c>
-      <c r="D1067" s="2" t="s">
-        <v>2892</v>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>2893</v>
-      </c>
-      <c r="C1068" s="2" t="s">
-        <v>2894</v>
-      </c>
-      <c r="D1068" s="2" t="s">
-        <v>2895</v>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>2896</v>
-      </c>
-      <c r="C1069" s="2" t="s">
-        <v>2897</v>
-      </c>
-      <c r="D1069" s="2" t="s">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>2899</v>
-      </c>
-      <c r="C1070" s="2" t="s">
-        <v>2900</v>
-      </c>
-      <c r="D1070" s="2" t="s">
-        <v>2901</v>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>2902</v>
-      </c>
-      <c r="C1071" s="2" t="s">
-        <v>2903</v>
-      </c>
-      <c r="D1071" s="2" t="s">
-        <v>2904</v>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>2905</v>
-      </c>
-      <c r="C1072" s="2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="D1072" s="2" t="s">
-        <v>2907</v>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>2908</v>
-      </c>
-      <c r="C1073" s="2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="D1073" s="2" t="s">
-        <v>2910</v>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>2911</v>
-      </c>
-      <c r="C1074" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="D1074" s="2" t="s">
-        <v>2913</v>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>2914</v>
-      </c>
-      <c r="C1075" s="2" t="s">
-        <v>2915</v>
-      </c>
-      <c r="D1075" s="2" t="s">
-        <v>2916</v>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>2917</v>
-      </c>
-      <c r="C1076" s="2" t="s">
-        <v>2918</v>
-      </c>
-      <c r="D1076" s="2" t="s">
-        <v>2919</v>
       </c>
     </row>
   </sheetData>
@@ -24018,32 +23709,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2920</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2921</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2922</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2923</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2924</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2925</v>
+        <v>2892</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hebrew-review.xlsx
+++ b/docs/hebrew-review.xlsx
@@ -974,6 +974,15 @@
     <t>לא נדרש חשבון. אפשר לסייר באירועי דמו מלאים בנתונים.</t>
   </si>
   <si>
+    <t>landing.previewNote</t>
+  </si>
+  <si>
+    <t>A preview of Event Planner. Everything you see is sample data, kept only in your browser.</t>
+  </si>
+  <si>
+    <t>תצוגה מקדימה של Event Planner. כל מה שרואים כאן הוא נתוני דוגמה, שנשמרים רק בדפדפן שלכם.</t>
+  </si>
+  <si>
     <t>landing.features.link</t>
   </si>
   <si>
@@ -8779,7 +8788,7 @@
     <t>{{name}}, {{count}} and similar marks are filled in by the application; keep them in the correction.</t>
   </si>
   <si>
-    <t>1060 texts in all.</t>
+    <t>1061 texts in all.</t>
   </si>
 </sst>
 </file>
@@ -10405,10 +10414,10 @@
         <v>322</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113">
@@ -10416,13 +10425,13 @@
         <v>298</v>
       </c>
       <c r="B113" t="s">
+        <v>325</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="114">
@@ -10590,7 +10599,7 @@
         <v>360</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="126">
@@ -10598,10 +10607,10 @@
         <v>298</v>
       </c>
       <c r="B126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>363</v>
@@ -10707,21 +10716,21 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" t="s">
         <v>385</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B135" t="s">
         <v>389</v>
@@ -10730,26 +10739,26 @@
         <v>390</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B136" t="s">
+        <v>392</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D136" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B137" t="s">
         <v>394</v>
@@ -10763,7 +10772,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B138" t="s">
         <v>397</v>
@@ -10777,7 +10786,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B139" t="s">
         <v>400</v>
@@ -10791,7 +10800,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B140" t="s">
         <v>403</v>
@@ -10805,7 +10814,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B141" t="s">
         <v>406</v>
@@ -10819,7 +10828,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B142" t="s">
         <v>409</v>
@@ -10833,7 +10842,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B143" t="s">
         <v>412</v>
@@ -10847,7 +10856,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B144" t="s">
         <v>415</v>
@@ -10861,7 +10870,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B145" t="s">
         <v>418</v>
@@ -10875,7 +10884,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B146" t="s">
         <v>421</v>
@@ -10889,7 +10898,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B147" t="s">
         <v>424</v>
@@ -10903,7 +10912,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B148" t="s">
         <v>427</v>
@@ -10917,7 +10926,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B149" t="s">
         <v>430</v>
@@ -10931,7 +10940,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B150" t="s">
         <v>433</v>
@@ -10945,7 +10954,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B151" t="s">
         <v>436</v>
@@ -10959,7 +10968,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B152" t="s">
         <v>439</v>
@@ -10973,7 +10982,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B153" t="s">
         <v>442</v>
@@ -10987,7 +10996,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B154" t="s">
         <v>445</v>
@@ -11001,7 +11010,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B155" t="s">
         <v>448</v>
@@ -11015,7 +11024,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B156" t="s">
         <v>451</v>
@@ -11029,7 +11038,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B157" t="s">
         <v>454</v>
@@ -11043,7 +11052,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B158" t="s">
         <v>457</v>
@@ -11057,7 +11066,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B159" t="s">
         <v>460</v>
@@ -11071,7 +11080,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B160" t="s">
         <v>463</v>
@@ -11085,7 +11094,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B161" t="s">
         <v>466</v>
@@ -11099,7 +11108,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B162" t="s">
         <v>469</v>
@@ -11113,7 +11122,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B163" t="s">
         <v>472</v>
@@ -11127,7 +11136,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B164" t="s">
         <v>475</v>
@@ -11141,7 +11150,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B165" t="s">
         <v>478</v>
@@ -11155,7 +11164,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B166" t="s">
         <v>481</v>
@@ -11169,7 +11178,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B167" t="s">
         <v>484</v>
@@ -11183,7 +11192,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B168" t="s">
         <v>487</v>
@@ -11197,7 +11206,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B169" t="s">
         <v>490</v>
@@ -11211,7 +11220,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B170" t="s">
         <v>493</v>
@@ -11225,7 +11234,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B171" t="s">
         <v>496</v>
@@ -11239,7 +11248,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B172" t="s">
         <v>499</v>
@@ -11253,7 +11262,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B173" t="s">
         <v>502</v>
@@ -11267,21 +11276,21 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>388</v>
+      </c>
+      <c r="B174" t="s">
         <v>505</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="D174" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B175" t="s">
         <v>509</v>
@@ -11295,7 +11304,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B176" t="s">
         <v>512</v>
@@ -11309,7 +11318,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B177" t="s">
         <v>515</v>
@@ -11323,13 +11332,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
+        <v>508</v>
+      </c>
+      <c r="B178" t="s">
         <v>518</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>520</v>
@@ -11337,13 +11346,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B179" t="s">
+        <v>522</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>523</v>
@@ -11351,7 +11360,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B180" t="s">
         <v>524</v>
@@ -11365,7 +11374,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B181" t="s">
         <v>527</v>
@@ -11379,7 +11388,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B182" t="s">
         <v>530</v>
@@ -11393,7 +11402,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B183" t="s">
         <v>533</v>
@@ -11407,7 +11416,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B184" t="s">
         <v>536</v>
@@ -11421,7 +11430,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B185" t="s">
         <v>539</v>
@@ -11435,7 +11444,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B186" t="s">
         <v>542</v>
@@ -11449,7 +11458,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B187" t="s">
         <v>545</v>
@@ -11463,7 +11472,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B188" t="s">
         <v>548</v>
@@ -11477,7 +11486,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B189" t="s">
         <v>551</v>
@@ -11491,7 +11500,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B190" t="s">
         <v>554</v>
@@ -11505,7 +11514,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B191" t="s">
         <v>557</v>
@@ -11519,7 +11528,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B192" t="s">
         <v>560</v>
@@ -11533,7 +11542,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B193" t="s">
         <v>563</v>
@@ -11547,7 +11556,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B194" t="s">
         <v>566</v>
@@ -11561,7 +11570,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>20</v>
+        <v>521</v>
       </c>
       <c r="B195" t="s">
         <v>569</v>
@@ -11679,10 +11688,10 @@
         <v>593</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="204">
@@ -11690,13 +11699,13 @@
         <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="205">
@@ -11735,10 +11744,10 @@
         <v>603</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="208">
@@ -11746,13 +11755,13 @@
         <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>585</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="209">
@@ -11760,10 +11769,10 @@
         <v>20</v>
       </c>
       <c r="B209" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>609</v>
@@ -11794,7 +11803,7 @@
         <v>614</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="212">
@@ -11802,10 +11811,10 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>617</v>
@@ -11962,7 +11971,7 @@
         <v>649</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="224">
@@ -11970,13 +11979,13 @@
         <v>20</v>
       </c>
       <c r="B224" t="s">
+        <v>651</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="225">
@@ -11984,13 +11993,13 @@
         <v>20</v>
       </c>
       <c r="B225" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="226">
@@ -12197,10 +12206,10 @@
         <v>696</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="241">
@@ -12208,13 +12217,13 @@
         <v>20</v>
       </c>
       <c r="B241" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="242">
@@ -12435,10 +12444,10 @@
         <v>745</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="258">
@@ -12446,13 +12455,13 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
+        <v>748</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="C258" s="2" t="s">
+      <c r="D258" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="259">
@@ -12611,7 +12620,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B270" t="s">
         <v>782</v>
@@ -12690,7 +12699,7 @@
         <v>798</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>363</v>
+        <v>799</v>
       </c>
     </row>
     <row r="276">
@@ -12698,13 +12707,13 @@
         <v>23</v>
       </c>
       <c r="B276" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>801</v>
+        <v>366</v>
       </c>
     </row>
     <row r="277">
@@ -12774,7 +12783,7 @@
         <v>815</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>372</v>
+        <v>816</v>
       </c>
     </row>
     <row r="282">
@@ -12782,13 +12791,13 @@
         <v>23</v>
       </c>
       <c r="B282" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>818</v>
+        <v>375</v>
       </c>
     </row>
     <row r="283">
@@ -12998,7 +13007,7 @@
         <v>862</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>824</v>
+        <v>863</v>
       </c>
     </row>
     <row r="298">
@@ -13006,13 +13015,13 @@
         <v>23</v>
       </c>
       <c r="B298" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
     </row>
     <row r="299">
@@ -13051,10 +13060,10 @@
         <v>872</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>26</v>
+        <v>873</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>27</v>
+        <v>874</v>
       </c>
     </row>
     <row r="302">
@@ -13062,13 +13071,13 @@
         <v>23</v>
       </c>
       <c r="B302" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>874</v>
+        <v>26</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>875</v>
+        <v>27</v>
       </c>
     </row>
     <row r="303">
@@ -13079,10 +13088,10 @@
         <v>876</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>360</v>
+        <v>877</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>360</v>
+        <v>878</v>
       </c>
     </row>
     <row r="304">
@@ -13090,13 +13099,13 @@
         <v>23</v>
       </c>
       <c r="B304" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>878</v>
+        <v>363</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>879</v>
+        <v>363</v>
       </c>
     </row>
     <row r="305">
@@ -13107,10 +13116,10 @@
         <v>880</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>26</v>
+        <v>881</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>27</v>
+        <v>882</v>
       </c>
     </row>
     <row r="306">
@@ -13118,13 +13127,13 @@
         <v>23</v>
       </c>
       <c r="B306" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>882</v>
+        <v>26</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>883</v>
+        <v>27</v>
       </c>
     </row>
     <row r="307">
@@ -13135,10 +13144,10 @@
         <v>884</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>365</v>
+        <v>885</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>366</v>
+        <v>886</v>
       </c>
     </row>
     <row r="308">
@@ -13146,13 +13155,13 @@
         <v>23</v>
       </c>
       <c r="B308" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="309">
@@ -13160,13 +13169,13 @@
         <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>887</v>
+        <v>374</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>813</v>
+        <v>375</v>
       </c>
     </row>
     <row r="310">
@@ -13174,13 +13183,13 @@
         <v>23</v>
       </c>
       <c r="B310" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>806</v>
+        <v>890</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
     </row>
     <row r="311">
@@ -13188,13 +13197,13 @@
         <v>23</v>
       </c>
       <c r="B311" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>890</v>
+        <v>809</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>891</v>
+        <v>810</v>
       </c>
     </row>
     <row r="312">
@@ -13261,10 +13270,10 @@
         <v>904</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>817</v>
+        <v>905</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>818</v>
+        <v>906</v>
       </c>
     </row>
     <row r="317">
@@ -13272,13 +13281,13 @@
         <v>23</v>
       </c>
       <c r="B317" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>906</v>
+        <v>820</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>907</v>
+        <v>821</v>
       </c>
     </row>
     <row r="318">
@@ -13292,7 +13301,7 @@
         <v>909</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="319">
@@ -13300,10 +13309,10 @@
         <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>912</v>
@@ -13446,7 +13455,7 @@
         <v>941</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="330">
@@ -13454,10 +13463,10 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>944</v>
@@ -13516,7 +13525,7 @@
         <v>955</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>325</v>
+        <v>956</v>
       </c>
     </row>
     <row r="335">
@@ -13524,13 +13533,13 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>958</v>
+        <v>328</v>
       </c>
     </row>
     <row r="336">
@@ -13569,10 +13578,10 @@
         <v>965</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>139</v>
+        <v>966</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="339">
@@ -13580,10 +13589,10 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>968</v>
+        <v>139</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>969</v>
@@ -13619,7 +13628,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B342" t="s">
         <v>976</v>
@@ -13723,10 +13732,10 @@
         <v>997</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>798</v>
+        <v>998</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>363</v>
+        <v>999</v>
       </c>
     </row>
     <row r="350">
@@ -13734,13 +13743,13 @@
         <v>26</v>
       </c>
       <c r="B350" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>801</v>
+        <v>366</v>
       </c>
     </row>
     <row r="351">
@@ -13748,13 +13757,13 @@
         <v>26</v>
       </c>
       <c r="B351" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>890</v>
+        <v>803</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1000</v>
+        <v>804</v>
       </c>
     </row>
     <row r="352">
@@ -13762,13 +13771,13 @@
         <v>26</v>
       </c>
       <c r="B352" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>365</v>
+        <v>893</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>366</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="353">
@@ -13776,13 +13785,13 @@
         <v>26</v>
       </c>
       <c r="B353" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>887</v>
+        <v>368</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>813</v>
+        <v>369</v>
       </c>
     </row>
     <row r="354">
@@ -13790,13 +13799,13 @@
         <v>26</v>
       </c>
       <c r="B354" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>371</v>
+        <v>890</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>372</v>
+        <v>816</v>
       </c>
     </row>
     <row r="355">
@@ -13804,13 +13813,13 @@
         <v>26</v>
       </c>
       <c r="B355" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1005</v>
+        <v>374</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>1006</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356">
@@ -13835,10 +13844,10 @@
         <v>1010</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>26</v>
+        <v>1011</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>27</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="358">
@@ -13846,13 +13855,13 @@
         <v>26</v>
       </c>
       <c r="B358" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1012</v>
+        <v>26</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>1013</v>
+        <v>27</v>
       </c>
     </row>
     <row r="359">
@@ -13863,10 +13872,10 @@
         <v>1014</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>890</v>
+        <v>1015</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>891</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="360">
@@ -13874,13 +13883,13 @@
         <v>26</v>
       </c>
       <c r="B360" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>806</v>
+        <v>893</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>1016</v>
+        <v>894</v>
       </c>
     </row>
     <row r="361">
@@ -13888,13 +13897,13 @@
         <v>26</v>
       </c>
       <c r="B361" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>365</v>
+        <v>809</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="362">
@@ -13902,13 +13911,13 @@
         <v>26</v>
       </c>
       <c r="B362" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>887</v>
+        <v>368</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="363">
@@ -13916,13 +13925,13 @@
         <v>26</v>
       </c>
       <c r="B363" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>371</v>
+        <v>890</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="364">
@@ -13930,10 +13939,10 @@
         <v>26</v>
       </c>
       <c r="B364" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1024</v>
+        <v>374</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>1025</v>
@@ -13947,10 +13956,10 @@
         <v>1026</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>365</v>
+        <v>1027</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="366">
@@ -13958,13 +13967,13 @@
         <v>26</v>
       </c>
       <c r="B366" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>887</v>
+        <v>368</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="367">
@@ -13972,13 +13981,13 @@
         <v>26</v>
       </c>
       <c r="B367" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>371</v>
+        <v>890</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="368">
@@ -13986,13 +13995,13 @@
         <v>26</v>
       </c>
       <c r="B368" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1030</v>
+        <v>374</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="369">
@@ -14017,10 +14026,10 @@
         <v>1035</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>867</v>
+        <v>1036</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="371">
@@ -14028,10 +14037,10 @@
         <v>26</v>
       </c>
       <c r="B371" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1038</v>
+        <v>870</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>1039</v>
@@ -14325,10 +14334,10 @@
         <v>1100</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>867</v>
+        <v>1101</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="393">
@@ -14336,13 +14345,13 @@
         <v>26</v>
       </c>
       <c r="B393" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>800</v>
+        <v>870</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>801</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="394">
@@ -14350,13 +14359,13 @@
         <v>26</v>
       </c>
       <c r="B394" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1053</v>
+        <v>803</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1054</v>
+        <v>804</v>
       </c>
     </row>
     <row r="395">
@@ -14364,13 +14373,13 @@
         <v>26</v>
       </c>
       <c r="B395" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1105</v>
+        <v>1056</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>1106</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="396">
@@ -14381,10 +14390,10 @@
         <v>1107</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1065</v>
+        <v>1108</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1066</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="397">
@@ -14392,13 +14401,13 @@
         <v>26</v>
       </c>
       <c r="B397" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>26</v>
+        <v>1068</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>27</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="398">
@@ -14406,13 +14415,13 @@
         <v>26</v>
       </c>
       <c r="B398" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1110</v>
+        <v>26</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1111</v>
+        <v>27</v>
       </c>
     </row>
     <row r="399">
@@ -14482,7 +14491,7 @@
         <v>1125</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="404">
@@ -14490,10 +14499,10 @@
         <v>26</v>
       </c>
       <c r="B404" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>1128</v>
@@ -14577,10 +14586,10 @@
         <v>1144</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>622</v>
+        <v>1145</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>623</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="411">
@@ -14588,13 +14597,13 @@
         <v>26</v>
       </c>
       <c r="B411" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1146</v>
+        <v>625</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>1147</v>
+        <v>626</v>
       </c>
     </row>
     <row r="412">
@@ -14801,10 +14810,10 @@
         <v>1190</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="427">
@@ -14812,13 +14821,13 @@
         <v>26</v>
       </c>
       <c r="B427" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C427" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="C427" s="2" t="s">
+      <c r="D427" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="D427" s="2" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="428">
@@ -14857,10 +14866,10 @@
         <v>1200</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="431">
@@ -14868,13 +14877,13 @@
         <v>26</v>
       </c>
       <c r="B431" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="432">
@@ -14927,10 +14936,10 @@
         <v>1213</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>992</v>
+        <v>1214</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>993</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="436">
@@ -14938,13 +14947,13 @@
         <v>26</v>
       </c>
       <c r="B436" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1133</v>
+        <v>995</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1134</v>
+        <v>996</v>
       </c>
     </row>
     <row r="437">
@@ -14952,13 +14961,13 @@
         <v>26</v>
       </c>
       <c r="B437" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1216</v>
+        <v>1136</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1217</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="438">
@@ -15011,10 +15020,10 @@
         <v>1227</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1095</v>
+        <v>1228</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1096</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="442">
@@ -15022,13 +15031,13 @@
         <v>26</v>
       </c>
       <c r="B442" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>713</v>
+        <v>1098</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>714</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="443">
@@ -15036,13 +15045,13 @@
         <v>26</v>
       </c>
       <c r="B443" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>992</v>
+        <v>716</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>993</v>
+        <v>717</v>
       </c>
     </row>
     <row r="444">
@@ -15050,13 +15059,13 @@
         <v>26</v>
       </c>
       <c r="B444" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1231</v>
+        <v>995</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1232</v>
+        <v>996</v>
       </c>
     </row>
     <row r="445">
@@ -15109,10 +15118,10 @@
         <v>1242</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>230</v>
+        <v>1243</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>231</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="449">
@@ -15120,13 +15129,13 @@
         <v>26</v>
       </c>
       <c r="B449" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="450">
@@ -15134,13 +15143,13 @@
         <v>26</v>
       </c>
       <c r="B450" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>743</v>
+        <v>233</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>744</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="451">
@@ -15148,13 +15157,13 @@
         <v>26</v>
       </c>
       <c r="B451" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1247</v>
+        <v>746</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1248</v>
+        <v>747</v>
       </c>
     </row>
     <row r="452">
@@ -15165,10 +15174,10 @@
         <v>1249</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1065</v>
+        <v>1250</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1066</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="453">
@@ -15176,13 +15185,13 @@
         <v>26</v>
       </c>
       <c r="B453" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1251</v>
+        <v>1068</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1252</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="454">
@@ -15193,10 +15202,10 @@
         <v>1253</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1053</v>
+        <v>1254</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1054</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="455">
@@ -15204,13 +15213,13 @@
         <v>26</v>
       </c>
       <c r="B455" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1255</v>
+        <v>1056</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1256</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="456">
@@ -15291,10 +15300,10 @@
         <v>1272</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1142</v>
+        <v>1273</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1143</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="462">
@@ -15302,13 +15311,13 @@
         <v>26</v>
       </c>
       <c r="B462" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1274</v>
+        <v>1145</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1275</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="463">
@@ -15319,10 +15328,10 @@
         <v>1276</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>817</v>
+        <v>1277</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>818</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="464">
@@ -15330,13 +15339,13 @@
         <v>26</v>
       </c>
       <c r="B464" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1278</v>
+        <v>820</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1279</v>
+        <v>821</v>
       </c>
     </row>
     <row r="465">
@@ -15473,10 +15482,10 @@
         <v>1307</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>622</v>
+        <v>1308</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>623</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="475">
@@ -15484,13 +15493,13 @@
         <v>26</v>
       </c>
       <c r="B475" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1309</v>
+        <v>625</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1310</v>
+        <v>626</v>
       </c>
     </row>
     <row r="476">
@@ -15585,10 +15594,10 @@
         <v>1329</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>893</v>
+        <v>1330</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>894</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="483">
@@ -15596,13 +15605,13 @@
         <v>26</v>
       </c>
       <c r="B483" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1331</v>
+        <v>896</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1332</v>
+        <v>897</v>
       </c>
     </row>
     <row r="484">
@@ -15641,10 +15650,10 @@
         <v>1339</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>777</v>
+        <v>1340</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>778</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="487">
@@ -15652,13 +15661,13 @@
         <v>26</v>
       </c>
       <c r="B487" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1341</v>
+        <v>780</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1342</v>
+        <v>781</v>
       </c>
     </row>
     <row r="488">
@@ -15669,10 +15678,10 @@
         <v>1343</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>26</v>
+        <v>1344</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>27</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="489">
@@ -15680,13 +15689,13 @@
         <v>26</v>
       </c>
       <c r="B489" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1345</v>
+        <v>26</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1346</v>
+        <v>27</v>
       </c>
     </row>
     <row r="490">
@@ -15697,10 +15706,10 @@
         <v>1347</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1216</v>
+        <v>1348</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1217</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="491">
@@ -15708,7 +15717,7 @@
         <v>26</v>
       </c>
       <c r="B491" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>1219</v>
@@ -15722,13 +15731,13 @@
         <v>26</v>
       </c>
       <c r="B492" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1089</v>
+        <v>1222</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1090</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="493">
@@ -15736,7 +15745,7 @@
         <v>26</v>
       </c>
       <c r="B493" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>1092</v>
@@ -15750,7 +15759,7 @@
         <v>26</v>
       </c>
       <c r="B494" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>1095</v>
@@ -15764,13 +15773,13 @@
         <v>26</v>
       </c>
       <c r="B495" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>817</v>
+        <v>1098</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>818</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="496">
@@ -15778,13 +15787,13 @@
         <v>26</v>
       </c>
       <c r="B496" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1101</v>
+        <v>821</v>
       </c>
     </row>
     <row r="497">
@@ -15792,13 +15801,13 @@
         <v>26</v>
       </c>
       <c r="B497" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>800</v>
+        <v>870</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>801</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="498">
@@ -15806,13 +15815,13 @@
         <v>26</v>
       </c>
       <c r="B498" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1053</v>
+        <v>803</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1054</v>
+        <v>804</v>
       </c>
     </row>
     <row r="499">
@@ -15820,13 +15829,13 @@
         <v>26</v>
       </c>
       <c r="B499" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="500">
@@ -15834,13 +15843,13 @@
         <v>26</v>
       </c>
       <c r="B500" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1358</v>
+        <v>1068</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>981</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="501">
@@ -15848,13 +15857,13 @@
         <v>26</v>
       </c>
       <c r="B501" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1361</v>
+        <v>984</v>
       </c>
     </row>
     <row r="502">
@@ -16229,10 +16238,10 @@
         <v>1440</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1216</v>
+        <v>1441</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1217</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="529">
@@ -16240,7 +16249,7 @@
         <v>26</v>
       </c>
       <c r="B529" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>1219</v>
@@ -16254,7 +16263,7 @@
         <v>26</v>
       </c>
       <c r="B530" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>1222</v>
@@ -16268,13 +16277,13 @@
         <v>26</v>
       </c>
       <c r="B531" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1095</v>
+        <v>1225</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1096</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="532">
@@ -16282,13 +16291,13 @@
         <v>26</v>
       </c>
       <c r="B532" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>1066</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="533">
@@ -16296,13 +16305,13 @@
         <v>26</v>
       </c>
       <c r="B533" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1446</v>
+        <v>1068</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1447</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="534">
@@ -16733,10 +16742,10 @@
         <v>1538</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1515</v>
+        <v>1539</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1516</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="565">
@@ -16744,13 +16753,13 @@
         <v>26</v>
       </c>
       <c r="B565" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1540</v>
+        <v>1518</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1541</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="566">
@@ -16761,10 +16770,10 @@
         <v>1542</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1518</v>
+        <v>1543</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1519</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="567">
@@ -16772,13 +16781,13 @@
         <v>26</v>
       </c>
       <c r="B567" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1544</v>
+        <v>1521</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1545</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="568">
@@ -16904,7 +16913,7 @@
         <v>1571</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1006</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="577">
@@ -16912,13 +16921,13 @@
         <v>26</v>
       </c>
       <c r="B577" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1574</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="578">
@@ -16929,29 +16938,29 @@
         <v>1575</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1506</v>
+        <v>1576</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1577</v>
+        <v>26</v>
       </c>
       <c r="B579" t="s">
         <v>1578</v>
       </c>
       <c r="C579" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>1579</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B580" t="s">
         <v>1581</v>
@@ -16965,7 +16974,7 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B581" t="s">
         <v>1584</v>
@@ -16979,7 +16988,7 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B582" t="s">
         <v>1587</v>
@@ -16993,41 +17002,41 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B583" t="s">
         <v>1590</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1402</v>
+        <v>1591</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>1403</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B584" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1231</v>
+        <v>1405</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>1592</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B585" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1594</v>
+        <v>1234</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>1595</v>
@@ -17035,7 +17044,7 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B586" t="s">
         <v>1596</v>
@@ -17049,7 +17058,7 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B587" t="s">
         <v>1599</v>
@@ -17063,7 +17072,7 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B588" t="s">
         <v>1602</v>
@@ -17077,7 +17086,7 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B589" t="s">
         <v>1605</v>
@@ -17091,7 +17100,7 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B590" t="s">
         <v>1608</v>
@@ -17105,7 +17114,7 @@
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B591" t="s">
         <v>1611</v>
@@ -17119,7 +17128,7 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B592" t="s">
         <v>1614</v>
@@ -17133,7 +17142,7 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B593" t="s">
         <v>1617</v>
@@ -17147,7 +17156,7 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B594" t="s">
         <v>1620</v>
@@ -17161,7 +17170,7 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B595" t="s">
         <v>1623</v>
@@ -17175,7 +17184,7 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B596" t="s">
         <v>1626</v>
@@ -17189,7 +17198,7 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B597" t="s">
         <v>1629</v>
@@ -17203,7 +17212,7 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B598" t="s">
         <v>1632</v>
@@ -17217,7 +17226,7 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B599" t="s">
         <v>1635</v>
@@ -17231,7 +17240,7 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B600" t="s">
         <v>1638</v>
@@ -17245,7 +17254,7 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B601" t="s">
         <v>1641</v>
@@ -17259,7 +17268,7 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B602" t="s">
         <v>1644</v>
@@ -17273,7 +17282,7 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B603" t="s">
         <v>1647</v>
@@ -17287,7 +17296,7 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B604" t="s">
         <v>1650</v>
@@ -17301,7 +17310,7 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B605" t="s">
         <v>1653</v>
@@ -17315,7 +17324,7 @@
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B606" t="s">
         <v>1656</v>
@@ -17329,7 +17338,7 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B607" t="s">
         <v>1659</v>
@@ -17343,7 +17352,7 @@
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B608" t="s">
         <v>1662</v>
@@ -17357,7 +17366,7 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B609" t="s">
         <v>1665</v>
@@ -17371,7 +17380,7 @@
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B610" t="s">
         <v>1668</v>
@@ -17380,26 +17389,26 @@
         <v>1669</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>692</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B611" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>1672</v>
+        <v>695</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B612" t="s">
         <v>1673</v>
@@ -17413,7 +17422,7 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B613" t="s">
         <v>1676</v>
@@ -17427,7 +17436,7 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B614" t="s">
         <v>1679</v>
@@ -17436,26 +17445,26 @@
         <v>1680</v>
       </c>
       <c r="D614" s="2" t="s">
-        <v>1403</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B615" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D615" s="2" t="s">
-        <v>1683</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B616" t="s">
         <v>1684</v>
@@ -17469,7 +17478,7 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B617" t="s">
         <v>1687</v>
@@ -17483,7 +17492,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B618" t="s">
         <v>1690</v>
@@ -17497,7 +17506,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B619" t="s">
         <v>1693</v>
@@ -17511,7 +17520,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B620" t="s">
         <v>1696</v>
@@ -17525,7 +17534,7 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B621" t="s">
         <v>1699</v>
@@ -17539,7 +17548,7 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B622" t="s">
         <v>1702</v>
@@ -17553,7 +17562,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B623" t="s">
         <v>1705</v>
@@ -17567,7 +17576,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B624" t="s">
         <v>1708</v>
@@ -17581,7 +17590,7 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B625" t="s">
         <v>1711</v>
@@ -17595,7 +17604,7 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B626" t="s">
         <v>1714</v>
@@ -17609,7 +17618,7 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B627" t="s">
         <v>1717</v>
@@ -17623,7 +17632,7 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B628" t="s">
         <v>1720</v>
@@ -17637,7 +17646,7 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B629" t="s">
         <v>1723</v>
@@ -17651,77 +17660,77 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B630" t="s">
         <v>1726</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1092</v>
+        <v>1727</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>1093</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B631" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>878</v>
+        <v>1095</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>879</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B632" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1680</v>
+        <v>881</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1729</v>
+        <v>882</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B633" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1105</v>
+        <v>1683</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>1106</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B634" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1732</v>
+        <v>1108</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>1733</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B635" t="s">
         <v>1734</v>
@@ -17735,7 +17744,7 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B636" t="s">
         <v>1737</v>
@@ -17749,7 +17758,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B637" t="s">
         <v>1740</v>
@@ -17763,7 +17772,7 @@
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B638" t="s">
         <v>1743</v>
@@ -17772,26 +17781,26 @@
         <v>1744</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>514</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B639" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>1747</v>
+        <v>517</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B640" t="s">
         <v>1748</v>
@@ -17805,7 +17814,7 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B641" t="s">
         <v>1751</v>
@@ -17819,7 +17828,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B642" t="s">
         <v>1754</v>
@@ -17833,35 +17842,35 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B643" t="s">
         <v>1757</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>941</v>
+        <v>1758</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>941</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B644" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1759</v>
+        <v>944</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>1760</v>
+        <v>944</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B645" t="s">
         <v>1761</v>
@@ -17875,7 +17884,7 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B646" t="s">
         <v>1764</v>
@@ -17889,7 +17898,7 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B647" t="s">
         <v>1767</v>
@@ -17903,7 +17912,7 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B648" t="s">
         <v>1770</v>
@@ -17917,7 +17926,7 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B649" t="s">
         <v>1773</v>
@@ -17931,7 +17940,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B650" t="s">
         <v>1776</v>
@@ -17945,7 +17954,7 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B651" t="s">
         <v>1779</v>
@@ -17959,7 +17968,7 @@
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B652" t="s">
         <v>1782</v>
@@ -17968,21 +17977,21 @@
         <v>1783</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>1589</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>139</v>
+        <v>1580</v>
       </c>
       <c r="B653" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>1786</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="654">
@@ -17993,10 +18002,10 @@
         <v>1787</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1231</v>
+        <v>1788</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>1592</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="655">
@@ -18004,13 +18013,13 @@
         <v>139</v>
       </c>
       <c r="B655" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1789</v>
+        <v>1234</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>1790</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="656">
@@ -18091,10 +18100,10 @@
         <v>1806</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1402</v>
+        <v>1807</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>1403</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="662">
@@ -18102,13 +18111,13 @@
         <v>139</v>
       </c>
       <c r="B662" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1808</v>
+        <v>1405</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>1809</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="663">
@@ -18136,7 +18145,7 @@
         <v>1814</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>1809</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="665">
@@ -18144,13 +18153,13 @@
         <v>139</v>
       </c>
       <c r="B665" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="666">
@@ -18444,7 +18453,7 @@
         <v>1879</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>751</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="687">
@@ -18452,10 +18461,10 @@
         <v>139</v>
       </c>
       <c r="B687" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>754</v>
@@ -18466,10 +18475,10 @@
         <v>139</v>
       </c>
       <c r="B688" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="D688" s="2" t="s">
         <v>757</v>
@@ -18480,13 +18489,13 @@
         <v>139</v>
       </c>
       <c r="B689" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>1886</v>
+        <v>760</v>
       </c>
     </row>
     <row r="690">
@@ -18763,10 +18772,10 @@
         <v>1944</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>698</v>
+        <v>1945</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>699</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="710">
@@ -18774,7 +18783,7 @@
         <v>139</v>
       </c>
       <c r="B710" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>701</v>
@@ -18788,13 +18797,13 @@
         <v>139</v>
       </c>
       <c r="B711" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>728</v>
+        <v>704</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>729</v>
+        <v>705</v>
       </c>
     </row>
     <row r="712">
@@ -18802,13 +18811,13 @@
         <v>139</v>
       </c>
       <c r="B712" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1948</v>
+        <v>731</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>1949</v>
+        <v>732</v>
       </c>
     </row>
     <row r="713">
@@ -18948,7 +18957,7 @@
         <v>1978</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>1403</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="723">
@@ -18956,13 +18965,13 @@
         <v>139</v>
       </c>
       <c r="B723" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>1981</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="724">
@@ -19001,10 +19010,10 @@
         <v>1988</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>365</v>
+        <v>1989</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>366</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="727">
@@ -19012,13 +19021,13 @@
         <v>139</v>
       </c>
       <c r="B727" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D727" s="2" t="s">
-        <v>1990</v>
+        <v>369</v>
       </c>
     </row>
     <row r="728">
@@ -19026,13 +19035,13 @@
         <v>139</v>
       </c>
       <c r="B728" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>887</v>
+        <v>374</v>
       </c>
       <c r="D728" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="729">
@@ -19040,10 +19049,10 @@
         <v>139</v>
       </c>
       <c r="B729" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1994</v>
+        <v>890</v>
       </c>
       <c r="D729" s="2" t="s">
         <v>1995</v>
@@ -19121,49 +19130,49 @@
     </row>
     <row r="735">
       <c r="A735" t="s">
+        <v>139</v>
+      </c>
+      <c r="B735" t="s">
         <v>2011</v>
       </c>
-      <c r="B735" t="s">
+      <c r="C735" s="2" t="s">
         <v>2012</v>
       </c>
-      <c r="C735" s="2" t="s">
+      <c r="D735" s="2" t="s">
         <v>2013</v>
-      </c>
-      <c r="D735" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B736" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1222</v>
+        <v>2016</v>
       </c>
       <c r="D736" s="2" t="s">
-        <v>1223</v>
+        <v>420</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B737" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>2016</v>
+        <v>1225</v>
       </c>
       <c r="D737" s="2" t="s">
-        <v>2017</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B738" t="s">
         <v>2018</v>
@@ -19177,7 +19186,7 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B739" t="s">
         <v>2021</v>
@@ -19191,7 +19200,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B740" t="s">
         <v>2024</v>
@@ -19205,7 +19214,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B741" t="s">
         <v>2027</v>
@@ -19219,7 +19228,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B742" t="s">
         <v>2030</v>
@@ -19233,7 +19242,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B743" t="s">
         <v>2033</v>
@@ -19247,7 +19256,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B744" t="s">
         <v>2036</v>
@@ -19261,7 +19270,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B745" t="s">
         <v>2039</v>
@@ -19275,7 +19284,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B746" t="s">
         <v>2042</v>
@@ -19289,41 +19298,41 @@
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B747" t="s">
         <v>2045</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>428</v>
+        <v>2046</v>
       </c>
       <c r="D747" s="2" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B748" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>230</v>
+        <v>431</v>
       </c>
       <c r="D748" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B749" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2050</v>
+        <v>230</v>
       </c>
       <c r="D749" s="2" t="s">
         <v>2051</v>
@@ -19331,7 +19340,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B750" t="s">
         <v>2052</v>
@@ -19345,7 +19354,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B751" t="s">
         <v>2055</v>
@@ -19359,7 +19368,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B752" t="s">
         <v>2058</v>
@@ -19373,7 +19382,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B753" t="s">
         <v>2061</v>
@@ -19387,7 +19396,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B754" t="s">
         <v>2064</v>
@@ -19401,7 +19410,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B755" t="s">
         <v>2067</v>
@@ -19415,7 +19424,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B756" t="s">
         <v>2070</v>
@@ -19429,7 +19438,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B757" t="s">
         <v>2073</v>
@@ -19443,7 +19452,7 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B758" t="s">
         <v>2076</v>
@@ -19457,7 +19466,7 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B759" t="s">
         <v>2079</v>
@@ -19471,7 +19480,7 @@
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B760" t="s">
         <v>2082</v>
@@ -19485,7 +19494,7 @@
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B761" t="s">
         <v>2085</v>
@@ -19499,49 +19508,49 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B762" t="s">
         <v>2088</v>
       </c>
-      <c r="B762" t="s">
+      <c r="C762" s="2" t="s">
         <v>2089</v>
       </c>
-      <c r="C762" s="2" t="s">
+      <c r="D762" s="2" t="s">
         <v>2090</v>
-      </c>
-      <c r="D762" s="2" t="s">
-        <v>2091</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B763" t="s">
         <v>2092</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>1059</v>
+        <v>2093</v>
       </c>
       <c r="D763" s="2" t="s">
-        <v>1060</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B764" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>2094</v>
+        <v>1062</v>
       </c>
       <c r="D764" s="2" t="s">
-        <v>2095</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B765" t="s">
         <v>2096</v>
@@ -19555,7 +19564,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B766" t="s">
         <v>2099</v>
@@ -19569,7 +19578,7 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B767" t="s">
         <v>2102</v>
@@ -19583,7 +19592,7 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B768" t="s">
         <v>2105</v>
@@ -19597,7 +19606,7 @@
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B769" t="s">
         <v>2108</v>
@@ -19611,7 +19620,7 @@
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B770" t="s">
         <v>2111</v>
@@ -19625,7 +19634,7 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B771" t="s">
         <v>2114</v>
@@ -19639,7 +19648,7 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B772" t="s">
         <v>2117</v>
@@ -19653,35 +19662,35 @@
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B773" t="s">
         <v>2120</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>820</v>
+        <v>2121</v>
       </c>
       <c r="D773" s="2" t="s">
-        <v>821</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B774" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2122</v>
+        <v>823</v>
       </c>
       <c r="D774" s="2" t="s">
-        <v>2123</v>
+        <v>824</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B775" t="s">
         <v>2124</v>
@@ -19695,7 +19704,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B776" t="s">
         <v>2127</v>
@@ -19709,7 +19718,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B777" t="s">
         <v>2130</v>
@@ -19723,7 +19732,7 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B778" t="s">
         <v>2133</v>
@@ -19737,7 +19746,7 @@
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B779" t="s">
         <v>2136</v>
@@ -19751,7 +19760,7 @@
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B780" t="s">
         <v>2139</v>
@@ -19765,7 +19774,7 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B781" t="s">
         <v>2142</v>
@@ -19779,7 +19788,7 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B782" t="s">
         <v>2145</v>
@@ -19793,55 +19802,55 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B783" t="s">
         <v>2148</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2109</v>
+        <v>2149</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>2110</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B784" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="D784" s="2" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B785" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>2151</v>
+        <v>2112</v>
       </c>
       <c r="D785" s="2" t="s">
-        <v>2151</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B786" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="D786" s="2" t="s">
         <v>2154</v>
@@ -19849,7 +19858,7 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B787" t="s">
         <v>2155</v>
@@ -19863,7 +19872,7 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B788" t="s">
         <v>2158</v>
@@ -19877,7 +19886,7 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B789" t="s">
         <v>2161</v>
@@ -19891,49 +19900,49 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B790" t="s">
         <v>2164</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>878</v>
+        <v>2165</v>
       </c>
       <c r="D790" s="2" t="s">
-        <v>879</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B791" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>1105</v>
+        <v>881</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>1106</v>
+        <v>882</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B792" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>2167</v>
+        <v>1108</v>
       </c>
       <c r="D792" s="2" t="s">
-        <v>2168</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B793" t="s">
         <v>2169</v>
@@ -19947,35 +19956,35 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B794" t="s">
         <v>2172</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>2153</v>
+        <v>2173</v>
       </c>
       <c r="D794" s="2" t="s">
-        <v>2154</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B795" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>2174</v>
+        <v>2156</v>
       </c>
       <c r="D795" s="2" t="s">
-        <v>2175</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B796" t="s">
         <v>2176</v>
@@ -19989,7 +19998,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B797" t="s">
         <v>2179</v>
@@ -20003,7 +20012,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B798" t="s">
         <v>2182</v>
@@ -20017,7 +20026,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B799" t="s">
         <v>2185</v>
@@ -20031,7 +20040,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B800" t="s">
         <v>2188</v>
@@ -20045,7 +20054,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B801" t="s">
         <v>2191</v>
@@ -20059,7 +20068,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B802" t="s">
         <v>2194</v>
@@ -20073,7 +20082,7 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B803" t="s">
         <v>2197</v>
@@ -20087,7 +20096,7 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B804" t="s">
         <v>2200</v>
@@ -20101,7 +20110,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B805" t="s">
         <v>2203</v>
@@ -20115,7 +20124,7 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B806" t="s">
         <v>2206</v>
@@ -20129,35 +20138,35 @@
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B807" t="s">
         <v>2209</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>1136</v>
+        <v>2210</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>1137</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B808" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>2211</v>
+        <v>1139</v>
       </c>
       <c r="D808" s="2" t="s">
-        <v>2212</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B809" t="s">
         <v>2213</v>
@@ -20171,7 +20180,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B810" t="s">
         <v>2216</v>
@@ -20185,7 +20194,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B811" t="s">
         <v>2219</v>
@@ -20199,7 +20208,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B812" t="s">
         <v>2222</v>
@@ -20213,7 +20222,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B813" t="s">
         <v>2225</v>
@@ -20227,7 +20236,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B814" t="s">
         <v>2228</v>
@@ -20241,7 +20250,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B815" t="s">
         <v>2231</v>
@@ -20255,7 +20264,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B816" t="s">
         <v>2234</v>
@@ -20269,7 +20278,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B817" t="s">
         <v>2237</v>
@@ -20283,63 +20292,63 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B818" t="s">
         <v>2240</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>955</v>
+        <v>2241</v>
       </c>
       <c r="D818" s="2" t="s">
-        <v>325</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B819" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>2242</v>
+        <v>958</v>
       </c>
       <c r="D819" s="2" t="s">
-        <v>2243</v>
+        <v>328</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B820" t="s">
         <v>2244</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>2100</v>
+        <v>2245</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>2101</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B821" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>2246</v>
+        <v>2103</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2247</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B822" t="s">
         <v>2248</v>
@@ -20353,91 +20362,91 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B823" t="s">
         <v>2251</v>
       </c>
       <c r="C823" s="2" t="s">
-        <v>2156</v>
+        <v>2252</v>
       </c>
       <c r="D823" s="2" t="s">
-        <v>2157</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B824" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>2253</v>
+        <v>2159</v>
       </c>
       <c r="D824" s="2" t="s">
-        <v>2254</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B825" t="s">
         <v>2255</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>2153</v>
+        <v>2256</v>
       </c>
       <c r="D825" s="2" t="s">
-        <v>2154</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B826" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="C826" s="2" t="s">
-        <v>2100</v>
+        <v>2156</v>
       </c>
       <c r="D826" s="2" t="s">
-        <v>2101</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B827" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="C827" s="2" t="s">
-        <v>1231</v>
+        <v>2103</v>
       </c>
       <c r="D827" s="2" t="s">
-        <v>1592</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B828" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C828" s="2" t="s">
-        <v>2259</v>
+        <v>1234</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>2260</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B829" t="s">
         <v>2261</v>
@@ -20451,7 +20460,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B830" t="s">
         <v>2264</v>
@@ -20465,35 +20474,35 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B831" t="s">
         <v>2267</v>
       </c>
       <c r="C831" s="2" t="s">
-        <v>245</v>
+        <v>2268</v>
       </c>
       <c r="D831" s="2" t="s">
-        <v>246</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B832" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="C832" s="2" t="s">
-        <v>2269</v>
+        <v>245</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>2270</v>
+        <v>246</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B833" t="s">
         <v>2271</v>
@@ -20507,7 +20516,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B834" t="s">
         <v>2274</v>
@@ -20521,7 +20530,7 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B835" t="s">
         <v>2277</v>
@@ -20535,7 +20544,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B836" t="s">
         <v>2280</v>
@@ -20549,7 +20558,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B837" t="s">
         <v>2283</v>
@@ -20563,35 +20572,35 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B838" t="s">
         <v>2286</v>
       </c>
       <c r="C838" s="2" t="s">
-        <v>2211</v>
+        <v>2287</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>2212</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B839" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="C839" s="2" t="s">
-        <v>2288</v>
+        <v>2214</v>
       </c>
       <c r="D839" s="2" t="s">
-        <v>2289</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B840" t="s">
         <v>2290</v>
@@ -20605,7 +20614,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B841" t="s">
         <v>2293</v>
@@ -20619,7 +20628,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B842" t="s">
         <v>2296</v>
@@ -20633,7 +20642,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B843" t="s">
         <v>2299</v>
@@ -20647,7 +20656,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B844" t="s">
         <v>2302</v>
@@ -20661,7 +20670,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B845" t="s">
         <v>2305</v>
@@ -20675,7 +20684,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B846" t="s">
         <v>2308</v>
@@ -20689,7 +20698,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B847" t="s">
         <v>2311</v>
@@ -20703,7 +20712,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B848" t="s">
         <v>2314</v>
@@ -20717,7 +20726,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B849" t="s">
         <v>2317</v>
@@ -20731,7 +20740,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B850" t="s">
         <v>2320</v>
@@ -20745,35 +20754,35 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B851" t="s">
         <v>2323</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>1122</v>
+        <v>2324</v>
       </c>
       <c r="D851" s="2" t="s">
-        <v>1123</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B852" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="C852" s="2" t="s">
-        <v>2325</v>
+        <v>1125</v>
       </c>
       <c r="D852" s="2" t="s">
-        <v>2326</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B853" t="s">
         <v>2327</v>
@@ -20787,7 +20796,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B854" t="s">
         <v>2330</v>
@@ -20801,7 +20810,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B855" t="s">
         <v>2333</v>
@@ -20815,7 +20824,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B856" t="s">
         <v>2336</v>
@@ -20829,7 +20838,7 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B857" t="s">
         <v>2339</v>
@@ -20843,7 +20852,7 @@
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B858" t="s">
         <v>2342</v>
@@ -20857,7 +20866,7 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B859" t="s">
         <v>2345</v>
@@ -20871,35 +20880,35 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B860" t="s">
         <v>2348</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>1491</v>
+        <v>2349</v>
       </c>
       <c r="D860" s="2" t="s">
-        <v>1492</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B861" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="C861" s="2" t="s">
-        <v>2350</v>
+        <v>1494</v>
       </c>
       <c r="D861" s="2" t="s">
-        <v>2351</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B862" t="s">
         <v>2352</v>
@@ -20913,38 +20922,38 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B863" t="s">
         <v>2355</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>1345</v>
+        <v>2356</v>
       </c>
       <c r="D863" s="2" t="s">
-        <v>1346</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B864" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>1216</v>
+        <v>1348</v>
       </c>
       <c r="D864" s="2" t="s">
-        <v>1217</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B865" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>1219</v>
@@ -20955,24 +20964,24 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B866" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>1089</v>
+        <v>1222</v>
       </c>
       <c r="D866" s="2" t="s">
-        <v>1090</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B867" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="C867" s="2" t="s">
         <v>1092</v>
@@ -20983,49 +20992,49 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B868" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>2019</v>
+        <v>1095</v>
       </c>
       <c r="D868" s="2" t="s">
-        <v>2020</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B869" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>2249</v>
+        <v>2022</v>
       </c>
       <c r="D869" s="2" t="s">
-        <v>2250</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B870" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>2363</v>
+        <v>2252</v>
       </c>
       <c r="D870" s="2" t="s">
-        <v>2364</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B871" t="s">
         <v>2365</v>
@@ -21039,7 +21048,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B872" t="s">
         <v>2368</v>
@@ -21053,7 +21062,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B873" t="s">
         <v>2371</v>
@@ -21067,7 +21076,7 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B874" t="s">
         <v>2374</v>
@@ -21081,7 +21090,7 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B875" t="s">
         <v>2377</v>
@@ -21095,7 +21104,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B876" t="s">
         <v>2380</v>
@@ -21109,35 +21118,35 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B877" t="s">
         <v>2383</v>
       </c>
       <c r="C877" s="2" t="s">
-        <v>2112</v>
+        <v>2384</v>
       </c>
       <c r="D877" s="2" t="s">
-        <v>2113</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B878" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="C878" s="2" t="s">
-        <v>2385</v>
+        <v>2115</v>
       </c>
       <c r="D878" s="2" t="s">
-        <v>2386</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B879" t="s">
         <v>2387</v>
@@ -21151,7 +21160,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B880" t="s">
         <v>2390</v>
@@ -21165,7 +21174,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B881" t="s">
         <v>2393</v>
@@ -21179,7 +21188,7 @@
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B882" t="s">
         <v>2396</v>
@@ -21193,7 +21202,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B883" t="s">
         <v>2399</v>
@@ -21207,7 +21216,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B884" t="s">
         <v>2402</v>
@@ -21221,7 +21230,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B885" t="s">
         <v>2405</v>
@@ -21235,7 +21244,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B886" t="s">
         <v>2408</v>
@@ -21249,7 +21258,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B887" t="s">
         <v>2411</v>
@@ -21263,7 +21272,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B888" t="s">
         <v>2414</v>
@@ -21277,7 +21286,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B889" t="s">
         <v>2417</v>
@@ -21286,26 +21295,26 @@
         <v>2418</v>
       </c>
       <c r="D889" s="2" t="s">
-        <v>1907</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B890" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="C890" s="2" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="D890" s="2" t="s">
-        <v>2421</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B891" t="s">
         <v>2422</v>
@@ -21319,7 +21328,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B892" t="s">
         <v>2425</v>
@@ -21333,7 +21342,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B893" t="s">
         <v>2428</v>
@@ -21347,7 +21356,7 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B894" t="s">
         <v>2431</v>
@@ -21361,7 +21370,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B895" t="s">
         <v>2434</v>
@@ -21375,7 +21384,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B896" t="s">
         <v>2437</v>
@@ -21389,7 +21398,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B897" t="s">
         <v>2440</v>
@@ -21403,7 +21412,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B898" t="s">
         <v>2443</v>
@@ -21417,7 +21426,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B899" t="s">
         <v>2446</v>
@@ -21431,7 +21440,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B900" t="s">
         <v>2449</v>
@@ -21445,7 +21454,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B901" t="s">
         <v>2452</v>
@@ -21459,7 +21468,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B902" t="s">
         <v>2455</v>
@@ -21473,7 +21482,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B903" t="s">
         <v>2458</v>
@@ -21487,7 +21496,7 @@
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B904" t="s">
         <v>2461</v>
@@ -21501,7 +21510,7 @@
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B905" t="s">
         <v>2464</v>
@@ -21515,7 +21524,7 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B906" t="s">
         <v>2467</v>
@@ -21529,7 +21538,7 @@
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B907" t="s">
         <v>2470</v>
@@ -21543,7 +21552,7 @@
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B908" t="s">
         <v>2473</v>
@@ -21557,7 +21566,7 @@
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B909" t="s">
         <v>2476</v>
@@ -21571,7 +21580,7 @@
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B910" t="s">
         <v>2479</v>
@@ -21585,7 +21594,7 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B911" t="s">
         <v>2482</v>
@@ -21599,7 +21608,7 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B912" t="s">
         <v>2485</v>
@@ -21613,7 +21622,7 @@
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B913" t="s">
         <v>2488</v>
@@ -21627,7 +21636,7 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B914" t="s">
         <v>2491</v>
@@ -21641,35 +21650,35 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B915" t="s">
         <v>2494</v>
       </c>
       <c r="C915" s="2" t="s">
-        <v>622</v>
+        <v>2495</v>
       </c>
       <c r="D915" s="2" t="s">
-        <v>623</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B916" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="C916" s="2" t="s">
-        <v>2496</v>
+        <v>625</v>
       </c>
       <c r="D916" s="2" t="s">
-        <v>2497</v>
+        <v>626</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B917" t="s">
         <v>2498</v>
@@ -21683,24 +21692,24 @@
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B918" t="s">
         <v>2501</v>
       </c>
       <c r="C918" s="2" t="s">
-        <v>2480</v>
+        <v>2502</v>
       </c>
       <c r="D918" s="2" t="s">
-        <v>2481</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B919" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="C919" s="2" t="s">
         <v>2483</v>
@@ -21711,21 +21720,21 @@
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B920" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="C920" s="2" t="s">
-        <v>2504</v>
+        <v>2486</v>
       </c>
       <c r="D920" s="2" t="s">
-        <v>2505</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B921" t="s">
         <v>2506</v>
@@ -21739,7 +21748,7 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B922" t="s">
         <v>2509</v>
@@ -21748,26 +21757,26 @@
         <v>2510</v>
       </c>
       <c r="D922" s="2" t="s">
-        <v>751</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B923" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="C923" s="2" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="D923" s="2" t="s">
-        <v>2513</v>
+        <v>754</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B924" t="s">
         <v>2514</v>
@@ -21776,54 +21785,54 @@
         <v>2515</v>
       </c>
       <c r="D924" s="2" t="s">
-        <v>757</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B925" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="C925" s="2" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="D925" s="2" t="s">
-        <v>2518</v>
+        <v>760</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B926" t="s">
         <v>2519</v>
       </c>
       <c r="C926" s="2" t="s">
-        <v>1906</v>
+        <v>2520</v>
       </c>
       <c r="D926" s="2" t="s">
-        <v>1907</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B927" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="C927" s="2" t="s">
-        <v>2521</v>
+        <v>1909</v>
       </c>
       <c r="D927" s="2" t="s">
-        <v>2522</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B928" t="s">
         <v>2523</v>
@@ -21837,7 +21846,7 @@
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>38</v>
+        <v>2091</v>
       </c>
       <c r="B929" t="s">
         <v>2526</v>
@@ -21857,10 +21866,10 @@
         <v>2529</v>
       </c>
       <c r="C930" s="2" t="s">
-        <v>1231</v>
+        <v>2530</v>
       </c>
       <c r="D930" s="2" t="s">
-        <v>1592</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="931">
@@ -21868,13 +21877,13 @@
         <v>38</v>
       </c>
       <c r="B931" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="C931" s="2" t="s">
-        <v>2531</v>
+        <v>1234</v>
       </c>
       <c r="D931" s="2" t="s">
-        <v>2532</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="932">
@@ -21913,10 +21922,10 @@
         <v>2539</v>
       </c>
       <c r="C934" s="2" t="s">
-        <v>691</v>
+        <v>2540</v>
       </c>
       <c r="D934" s="2" t="s">
-        <v>692</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="935">
@@ -21924,13 +21933,13 @@
         <v>38</v>
       </c>
       <c r="B935" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="C935" s="2" t="s">
-        <v>728</v>
+        <v>694</v>
       </c>
       <c r="D935" s="2" t="s">
-        <v>729</v>
+        <v>695</v>
       </c>
     </row>
     <row r="936">
@@ -21938,13 +21947,13 @@
         <v>38</v>
       </c>
       <c r="B936" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="C936" s="2" t="s">
-        <v>2542</v>
+        <v>731</v>
       </c>
       <c r="D936" s="2" t="s">
-        <v>2543</v>
+        <v>732</v>
       </c>
     </row>
     <row r="937">
@@ -21955,10 +21964,10 @@
         <v>2544</v>
       </c>
       <c r="C937" s="2" t="s">
-        <v>710</v>
+        <v>2545</v>
       </c>
       <c r="D937" s="2" t="s">
-        <v>711</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="938">
@@ -21966,13 +21975,13 @@
         <v>38</v>
       </c>
       <c r="B938" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="C938" s="2" t="s">
-        <v>2546</v>
+        <v>713</v>
       </c>
       <c r="D938" s="2" t="s">
-        <v>2547</v>
+        <v>714</v>
       </c>
     </row>
     <row r="939">
@@ -22000,7 +22009,7 @@
         <v>2552</v>
       </c>
       <c r="D940" s="2" t="s">
-        <v>1672</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="941">
@@ -22008,10 +22017,10 @@
         <v>38</v>
       </c>
       <c r="B941" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="C941" s="2" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="D941" s="2" t="s">
         <v>1675</v>
@@ -22022,13 +22031,13 @@
         <v>38</v>
       </c>
       <c r="B942" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C942" s="2" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="D942" s="2" t="s">
-        <v>705</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="943">
@@ -22036,13 +22045,13 @@
         <v>38</v>
       </c>
       <c r="B943" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="C943" s="2" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="D943" s="2" t="s">
-        <v>2559</v>
+        <v>708</v>
       </c>
     </row>
     <row r="944">
@@ -22165,10 +22174,10 @@
         <v>2584</v>
       </c>
       <c r="C952" s="2" t="s">
-        <v>139</v>
+        <v>2585</v>
       </c>
       <c r="D952" s="2" t="s">
-        <v>140</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="953">
@@ -22176,13 +22185,13 @@
         <v>38</v>
       </c>
       <c r="B953" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="C953" s="2" t="s">
-        <v>2586</v>
+        <v>139</v>
       </c>
       <c r="D953" s="2" t="s">
-        <v>2587</v>
+        <v>140</v>
       </c>
     </row>
     <row r="954">
@@ -22277,10 +22286,10 @@
         <v>2606</v>
       </c>
       <c r="C960" s="2" t="s">
-        <v>710</v>
+        <v>2607</v>
       </c>
       <c r="D960" s="2" t="s">
-        <v>711</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="961">
@@ -22288,13 +22297,13 @@
         <v>38</v>
       </c>
       <c r="B961" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="C961" s="2" t="s">
-        <v>2608</v>
+        <v>713</v>
       </c>
       <c r="D961" s="2" t="s">
-        <v>2609</v>
+        <v>714</v>
       </c>
     </row>
     <row r="962">
@@ -22495,7 +22504,7 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B976" t="s">
         <v>2652</v>
@@ -22557,10 +22566,10 @@
         <v>2664</v>
       </c>
       <c r="C980" s="2" t="s">
-        <v>192</v>
+        <v>2665</v>
       </c>
       <c r="D980" s="2" t="s">
-        <v>193</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="981">
@@ -22568,13 +22577,13 @@
         <v>41</v>
       </c>
       <c r="B981" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>2666</v>
+        <v>192</v>
       </c>
       <c r="D981" s="2" t="s">
-        <v>2667</v>
+        <v>193</v>
       </c>
     </row>
     <row r="982">
@@ -22658,7 +22667,7 @@
         <v>2684</v>
       </c>
       <c r="D987" s="2" t="s">
-        <v>77</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="988">
@@ -22666,13 +22675,13 @@
         <v>41</v>
       </c>
       <c r="B988" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="C988" s="2" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="D988" s="2" t="s">
-        <v>2687</v>
+        <v>77</v>
       </c>
     </row>
     <row r="989">
@@ -22714,7 +22723,7 @@
         <v>2695</v>
       </c>
       <c r="D991" s="2" t="s">
-        <v>2693</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="992">
@@ -22722,13 +22731,13 @@
         <v>41</v>
       </c>
       <c r="B992" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C992" s="2" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D992" s="2" t="s">
         <v>2696</v>
-      </c>
-      <c r="C992" s="2" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D992" s="2" t="s">
-        <v>2698</v>
       </c>
     </row>
     <row r="993">
@@ -22781,10 +22790,10 @@
         <v>2708</v>
       </c>
       <c r="C996" s="2" t="s">
-        <v>1086</v>
+        <v>2709</v>
       </c>
       <c r="D996" s="2" t="s">
-        <v>1087</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="997">
@@ -22792,13 +22801,13 @@
         <v>41</v>
       </c>
       <c r="B997" t="s">
-        <v>2709</v>
+        <v>2711</v>
       </c>
       <c r="C997" s="2" t="s">
-        <v>419</v>
+        <v>1089</v>
       </c>
       <c r="D997" s="2" t="s">
-        <v>420</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="998">
@@ -22806,13 +22815,13 @@
         <v>41</v>
       </c>
       <c r="B998" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="C998" s="2" t="s">
-        <v>2711</v>
+        <v>422</v>
       </c>
       <c r="D998" s="2" t="s">
-        <v>2712</v>
+        <v>423</v>
       </c>
     </row>
     <row r="999">
@@ -22823,10 +22832,10 @@
         <v>2713</v>
       </c>
       <c r="C999" s="2" t="s">
-        <v>1105</v>
+        <v>2714</v>
       </c>
       <c r="D999" s="2" t="s">
-        <v>1106</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="1000">
@@ -22834,13 +22843,13 @@
         <v>41</v>
       </c>
       <c r="B1000" t="s">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="C1000" s="2" t="s">
-        <v>2715</v>
+        <v>1108</v>
       </c>
       <c r="D1000" s="2" t="s">
-        <v>2716</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1001">
@@ -23033,10 +23042,10 @@
         <v>2756</v>
       </c>
       <c r="C1014" s="2" t="s">
-        <v>2656</v>
+        <v>2757</v>
       </c>
       <c r="D1014" s="2" t="s">
-        <v>2657</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="1015">
@@ -23044,13 +23053,13 @@
         <v>41</v>
       </c>
       <c r="B1015" t="s">
-        <v>2757</v>
+        <v>2759</v>
       </c>
       <c r="C1015" s="2" t="s">
-        <v>419</v>
+        <v>2659</v>
       </c>
       <c r="D1015" s="2" t="s">
-        <v>420</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="1016">
@@ -23058,13 +23067,13 @@
         <v>41</v>
       </c>
       <c r="B1016" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>2759</v>
+        <v>422</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>2760</v>
+        <v>423</v>
       </c>
     </row>
     <row r="1017">
@@ -23117,10 +23126,10 @@
         <v>2770</v>
       </c>
       <c r="C1020" s="2" t="s">
-        <v>431</v>
+        <v>2771</v>
       </c>
       <c r="D1020" s="2" t="s">
-        <v>432</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="1021">
@@ -23128,13 +23137,13 @@
         <v>41</v>
       </c>
       <c r="B1021" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>257</v>
+        <v>434</v>
       </c>
       <c r="D1021" s="2" t="s">
-        <v>258</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1022">
@@ -23142,13 +23151,13 @@
         <v>41</v>
       </c>
       <c r="B1022" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="C1022" s="2" t="s">
-        <v>2773</v>
+        <v>257</v>
       </c>
       <c r="D1022" s="2" t="s">
-        <v>2774</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1023">
@@ -23187,10 +23196,10 @@
         <v>2781</v>
       </c>
       <c r="C1025" s="2" t="s">
-        <v>2724</v>
+        <v>2782</v>
       </c>
       <c r="D1025" s="2" t="s">
-        <v>2725</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="1026">
@@ -23198,13 +23207,13 @@
         <v>41</v>
       </c>
       <c r="B1026" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
       <c r="C1026" s="2" t="s">
-        <v>2783</v>
+        <v>2727</v>
       </c>
       <c r="D1026" s="2" t="s">
-        <v>2784</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="1027">
@@ -23257,10 +23266,10 @@
         <v>2794</v>
       </c>
       <c r="C1030" s="2" t="s">
-        <v>2303</v>
+        <v>2795</v>
       </c>
       <c r="D1030" s="2" t="s">
-        <v>2304</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="1031">
@@ -23268,13 +23277,13 @@
         <v>41</v>
       </c>
       <c r="B1031" t="s">
-        <v>2795</v>
+        <v>2797</v>
       </c>
       <c r="C1031" s="2" t="s">
-        <v>2796</v>
+        <v>2306</v>
       </c>
       <c r="D1031" s="2" t="s">
-        <v>2797</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="1032">
@@ -23335,55 +23344,55 @@
     </row>
     <row r="1036">
       <c r="A1036" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1036" t="s">
         <v>2810</v>
       </c>
-      <c r="B1036" t="s">
+      <c r="C1036" s="2" t="s">
         <v>2811</v>
       </c>
-      <c r="C1036" s="2" t="s">
+      <c r="D1036" s="2" t="s">
         <v>2812</v>
-      </c>
-      <c r="D1036" s="2" t="s">
-        <v>2813</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1037" t="s">
         <v>2814</v>
       </c>
       <c r="C1037" s="2" t="s">
-        <v>419</v>
+        <v>2815</v>
       </c>
       <c r="D1037" s="2" t="s">
-        <v>420</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1038" t="s">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="C1038" s="2" t="s">
-        <v>878</v>
+        <v>422</v>
       </c>
       <c r="D1038" s="2" t="s">
-        <v>2816</v>
+        <v>423</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1039" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="C1039" s="2" t="s">
-        <v>2818</v>
+        <v>881</v>
       </c>
       <c r="D1039" s="2" t="s">
         <v>2819</v>
@@ -23391,7 +23400,7 @@
     </row>
     <row r="1040">
       <c r="A1040" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1040" t="s">
         <v>2820</v>
@@ -23405,7 +23414,7 @@
     </row>
     <row r="1041">
       <c r="A1041" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1041" t="s">
         <v>2823</v>
@@ -23419,7 +23428,7 @@
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1042" t="s">
         <v>2826</v>
@@ -23433,7 +23442,7 @@
     </row>
     <row r="1043">
       <c r="A1043" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1043" t="s">
         <v>2829</v>
@@ -23447,7 +23456,7 @@
     </row>
     <row r="1044">
       <c r="A1044" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1044" t="s">
         <v>2832</v>
@@ -23461,7 +23470,7 @@
     </row>
     <row r="1045">
       <c r="A1045" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1045" t="s">
         <v>2835</v>
@@ -23475,7 +23484,7 @@
     </row>
     <row r="1046">
       <c r="A1046" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1046" t="s">
         <v>2838</v>
@@ -23489,7 +23498,7 @@
     </row>
     <row r="1047">
       <c r="A1047" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1047" t="s">
         <v>2841</v>
@@ -23503,7 +23512,7 @@
     </row>
     <row r="1048">
       <c r="A1048" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1048" t="s">
         <v>2844</v>
@@ -23517,7 +23526,7 @@
     </row>
     <row r="1049">
       <c r="A1049" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1049" t="s">
         <v>2847</v>
@@ -23531,7 +23540,7 @@
     </row>
     <row r="1050">
       <c r="A1050" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1050" t="s">
         <v>2850</v>
@@ -23545,7 +23554,7 @@
     </row>
     <row r="1051">
       <c r="A1051" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="B1051" t="s">
         <v>2853</v>
@@ -23559,21 +23568,21 @@
     </row>
     <row r="1052">
       <c r="A1052" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1052" t="s">
         <v>2856</v>
       </c>
-      <c r="B1052" t="s">
+      <c r="C1052" s="2" t="s">
         <v>2857</v>
       </c>
-      <c r="C1052" s="2" t="s">
+      <c r="D1052" s="2" t="s">
         <v>2858</v>
-      </c>
-      <c r="D1052" s="2" t="s">
-        <v>2859</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1053" t="s">
         <v>2860</v>
@@ -23587,7 +23596,7 @@
     </row>
     <row r="1054">
       <c r="A1054" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1054" t="s">
         <v>2863</v>
@@ -23601,7 +23610,7 @@
     </row>
     <row r="1055">
       <c r="A1055" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1055" t="s">
         <v>2866</v>
@@ -23615,7 +23624,7 @@
     </row>
     <row r="1056">
       <c r="A1056" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1056" t="s">
         <v>2869</v>
@@ -23629,7 +23638,7 @@
     </row>
     <row r="1057">
       <c r="A1057" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1057" t="s">
         <v>2872</v>
@@ -23643,7 +23652,7 @@
     </row>
     <row r="1058">
       <c r="A1058" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1058" t="s">
         <v>2875</v>
@@ -23657,7 +23666,7 @@
     </row>
     <row r="1059">
       <c r="A1059" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1059" t="s">
         <v>2878</v>
@@ -23671,7 +23680,7 @@
     </row>
     <row r="1060">
       <c r="A1060" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1060" t="s">
         <v>2881</v>
@@ -23685,7 +23694,7 @@
     </row>
     <row r="1061">
       <c r="A1061" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="B1061" t="s">
         <v>2884</v>
@@ -23695,6 +23704,20 @@
       </c>
       <c r="D1061" s="2" t="s">
         <v>2886</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>2887</v>
+      </c>
+      <c r="C1062" s="2" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D1062" s="2" t="s">
+        <v>2889</v>
       </c>
     </row>
   </sheetData>
@@ -23709,32 +23732,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2887</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2890</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2891</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
     </row>
   </sheetData>
